--- a/input/reg_leaveParentalHome.xlsx
+++ b/input/reg_leaveParentalHome.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPathsFork\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD259F89-0BAB-4BB9-8E76-65820C3409CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8115590C-3ED5-4E60-8622-C584B5486B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21480" windowHeight="12675" tabRatio="868" activeTab="1" xr2:uid="{CC6E2FEF-D903-4968-A8BC-51F7E3117EFA}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="868" activeTab="1" xr2:uid="{CC6E2FEF-D903-4968-A8BC-51F7E3117EFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>HUB</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Y2021</t>
   </si>
 </sst>
 </file>
@@ -169,12 +175,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,14 +499,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216E112B-B70B-4DAB-88B7-B697E60397AE}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" customWidth="1"/>
+    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -508,7 +515,7 @@
       </c>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -516,7 +523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -524,7 +531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -532,11 +539,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -544,7 +551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -552,11 +559,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
     </row>
@@ -567,17 +574,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E935A8D-515D-4372-A9BA-E81F8E8AE883}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -623,802 +630,1016 @@
         <v>14</v>
       </c>
       <c r="Q1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>-7.8127749993595161E-2</v>
+      <c r="B2" s="5">
+        <v>2.4210393133847097E-2</v>
       </c>
       <c r="C2">
-        <v>2.4833483739479119E-3</v>
+        <v>3.2077809990039776E-3</v>
       </c>
       <c r="D2">
-        <v>-2.3531650958512201E-5</v>
+        <v>-1.1316876605131935E-4</v>
       </c>
       <c r="E2">
-        <v>3.5596677665796999E-7</v>
+        <v>1.415032743029681E-6</v>
       </c>
       <c r="F2">
-        <v>-6.7509677884127275E-4</v>
+        <v>-6.1405948989176943E-4</v>
       </c>
       <c r="G2">
-        <v>-4.4523664203839224E-4</v>
+        <v>-2.0043358460969938E-4</v>
       </c>
       <c r="H2">
-        <v>-9.3789587232790685E-4</v>
+        <v>-1.4830549110630702E-3</v>
       </c>
       <c r="I2">
-        <v>-2.7327323616446384E-4</v>
+        <v>-1.1375236716823815E-3</v>
       </c>
       <c r="J2">
-        <v>6.0294420019665505E-4</v>
+        <v>-2.2532157458921698E-4</v>
       </c>
       <c r="K2">
-        <v>-3.1181963921286105E-4</v>
+        <v>-1.2264103945807837E-3</v>
       </c>
       <c r="L2">
-        <v>-6.1138963643399757E-4</v>
+        <v>-2.0413917000660386E-3</v>
       </c>
       <c r="M2">
-        <v>-4.2246116403799473E-4</v>
+        <v>-1.5779920282146273E-3</v>
       </c>
       <c r="N2">
-        <v>-2.3396758086623653E-4</v>
+        <v>-8.0520151873903888E-4</v>
       </c>
       <c r="O2">
-        <v>2.2664862599007724E-5</v>
+        <v>-7.2754760314824515E-4</v>
       </c>
       <c r="P2">
-        <v>3.5918955462177425E-6</v>
+        <v>6.0629112341232974E-6</v>
       </c>
       <c r="Q2">
-        <v>-1.5314507206155739E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>-2.6502130858151293E-4</v>
+      </c>
+      <c r="R2">
+        <v>7.780703498571044E-4</v>
+      </c>
+      <c r="S2">
+        <v>2.6016829038594041E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>-1.010281929409795E-2</v>
+      <c r="B3" s="5">
+        <v>-9.7704638674818642E-3</v>
       </c>
       <c r="C3">
-        <v>-2.3531650958512201E-5</v>
+        <v>-1.1316876605131935E-4</v>
       </c>
       <c r="D3">
-        <v>1.6398931016778283E-4</v>
+        <v>1.9410209984130231E-4</v>
       </c>
       <c r="E3">
-        <v>-1.8059080194790993E-6</v>
+        <v>-2.1570879729846098E-6</v>
       </c>
       <c r="F3">
-        <v>-1.176795112668639E-4</v>
+        <v>7.9037666887808982E-6</v>
       </c>
       <c r="G3">
-        <v>-8.3805593965519945E-5</v>
+        <v>1.2663299991796018E-4</v>
       </c>
       <c r="H3">
-        <v>7.2904169332132563E-4</v>
+        <v>9.5508862646267101E-4</v>
       </c>
       <c r="I3">
-        <v>2.33555253525632E-4</v>
+        <v>4.171289460348697E-4</v>
       </c>
       <c r="J3">
-        <v>-2.0301704894384745E-4</v>
+        <v>4.4449674781482156E-5</v>
       </c>
       <c r="K3">
-        <v>-6.054982782553614E-6</v>
+        <v>2.9359495567787982E-4</v>
       </c>
       <c r="L3">
-        <v>-5.5960071690848082E-5</v>
+        <v>2.9146068933853212E-4</v>
       </c>
       <c r="M3">
-        <v>-1.7973133475351598E-4</v>
+        <v>3.1767743737139793E-4</v>
       </c>
       <c r="N3">
-        <v>8.9678107468355115E-5</v>
+        <v>5.8426758961878465E-5</v>
       </c>
       <c r="O3">
-        <v>1.5371879147930718E-4</v>
+        <v>1.9631070283859017E-4</v>
       </c>
       <c r="P3">
-        <v>-1.2066099536003818E-5</v>
+        <v>6.8705390397704141E-7</v>
       </c>
       <c r="Q3">
-        <v>-3.1926207850553395E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>2.4663647223517886E-4</v>
+      </c>
+      <c r="R3">
+        <v>3.8540451815181767E-4</v>
+      </c>
+      <c r="S3">
+        <v>-4.4507543392197126E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>4.9947811982693714E-4</v>
+      <c r="B4" s="5">
+        <v>5.0963530848233596E-4</v>
       </c>
       <c r="C4">
-        <v>3.5596677665796999E-7</v>
+        <v>1.415032743029681E-6</v>
       </c>
       <c r="D4">
-        <v>-1.8059080194790993E-6</v>
+        <v>-2.1570879729846098E-6</v>
       </c>
       <c r="E4">
-        <v>2.0328932935482597E-8</v>
+        <v>2.4550977767386957E-8</v>
       </c>
       <c r="F4">
-        <v>1.1399432282577712E-6</v>
+        <v>-2.8354536615708178E-7</v>
       </c>
       <c r="G4">
-        <v>8.3270911270836318E-7</v>
+        <v>-1.4414160778171327E-6</v>
       </c>
       <c r="H4">
-        <v>-7.2001525002319559E-6</v>
+        <v>-9.4393243874891624E-6</v>
       </c>
       <c r="I4">
-        <v>-2.5524795467970782E-6</v>
+        <v>-4.5331253326475387E-6</v>
       </c>
       <c r="J4">
-        <v>2.028441644937423E-6</v>
+        <v>-4.6057860212901029E-7</v>
       </c>
       <c r="K4">
-        <v>3.6105354216506137E-7</v>
+        <v>-2.6587013746380629E-6</v>
       </c>
       <c r="L4">
-        <v>9.3668993093631918E-7</v>
+        <v>-2.7185154008780126E-6</v>
       </c>
       <c r="M4">
-        <v>2.1589188287859694E-6</v>
+        <v>-2.8174854627068318E-6</v>
       </c>
       <c r="N4">
-        <v>-9.1976427505158025E-7</v>
+        <v>-5.8609930291867203E-7</v>
       </c>
       <c r="O4">
-        <v>-1.5475787725445226E-6</v>
+        <v>-1.9870156376583704E-6</v>
       </c>
       <c r="P4">
-        <v>1.1794884775395675E-7</v>
+        <v>-2.6185780541795668E-8</v>
       </c>
       <c r="Q4">
-        <v>3.4302067358376063E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>-2.7402851885344099E-6</v>
+      </c>
+      <c r="R4">
+        <v>-3.9136496008656944E-6</v>
+      </c>
+      <c r="S4">
+        <v>4.8104986947004712E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>6.0859312853924659E-2</v>
+      <c r="B5" s="5">
+        <v>0.14798043435454139</v>
       </c>
       <c r="C5">
-        <v>-6.7509677884127275E-4</v>
+        <v>-6.1405948989176943E-4</v>
       </c>
       <c r="D5">
-        <v>-1.176795112668639E-4</v>
+        <v>7.9037666887808982E-6</v>
       </c>
       <c r="E5">
-        <v>1.1399432282577712E-6</v>
+        <v>-2.8354536615708178E-7</v>
       </c>
       <c r="F5">
-        <v>5.894057981603194E-3</v>
+        <v>6.0242022298372423E-3</v>
       </c>
       <c r="G5">
-        <v>5.0823957989158701E-3</v>
+        <v>4.9796031130125342E-3</v>
       </c>
       <c r="H5">
-        <v>-2.7043727161744175E-3</v>
+        <v>1.2618094498540594E-4</v>
       </c>
       <c r="I5">
-        <v>-5.5846501993344917E-4</v>
+        <v>-6.0997955556260294E-4</v>
       </c>
       <c r="J5">
-        <v>9.158683822396204E-4</v>
+        <v>1.9982305452282862E-4</v>
       </c>
       <c r="K5">
-        <v>-4.8477586079501665E-4</v>
+        <v>6.6421880184105823E-5</v>
       </c>
       <c r="L5">
-        <v>1.35524805748603E-4</v>
+        <v>-7.8642977139397469E-5</v>
       </c>
       <c r="M5">
-        <v>9.2154229558073883E-4</v>
+        <v>5.3192459360171555E-4</v>
       </c>
       <c r="N5">
-        <v>4.6661206432291194E-4</v>
+        <v>-1.5174574141722233E-4</v>
       </c>
       <c r="O5">
-        <v>5.9704613798870548E-4</v>
+        <v>-3.5621544395307743E-4</v>
       </c>
       <c r="P5">
-        <v>-1.3012785454974407E-5</v>
+        <v>2.2341901174853241E-5</v>
       </c>
       <c r="Q5">
-        <v>-1.863657679340003E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>-8.0562031822273717E-5</v>
+      </c>
+      <c r="R5">
+        <v>1.4438994907479659E-4</v>
+      </c>
+      <c r="S5">
+        <v>-4.4581025951299542E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>0.22170828166955489</v>
+      <c r="B6" s="5">
+        <v>0.3343789340313017</v>
       </c>
       <c r="C6">
-        <v>-4.4523664203839224E-4</v>
+        <v>-2.0043358460969938E-4</v>
       </c>
       <c r="D6">
-        <v>-8.3805593965519945E-5</v>
+        <v>1.2663299991796018E-4</v>
       </c>
       <c r="E6">
-        <v>8.3270911270836318E-7</v>
+        <v>-1.4414160778171327E-6</v>
       </c>
       <c r="F6">
-        <v>5.0823957989158701E-3</v>
+        <v>4.9796031130125342E-3</v>
       </c>
       <c r="G6">
-        <v>7.8057054154953044E-3</v>
+        <v>9.1408525169627032E-3</v>
       </c>
       <c r="H6">
-        <v>-2.6092316013499009E-3</v>
+        <v>-1.2271022403682191E-4</v>
       </c>
       <c r="I6">
-        <v>-1.4244781165553182E-3</v>
+        <v>-2.2800643346818916E-3</v>
       </c>
       <c r="J6">
-        <v>9.2365499651585452E-4</v>
+        <v>1.5195398760944633E-3</v>
       </c>
       <c r="K6">
-        <v>-7.2331394073804069E-4</v>
+        <v>5.4176663315402569E-5</v>
       </c>
       <c r="L6">
-        <v>-1.4506917706639226E-4</v>
+        <v>5.01063870498247E-4</v>
       </c>
       <c r="M6">
-        <v>8.8862326980165536E-4</v>
+        <v>5.9790701958282186E-4</v>
       </c>
       <c r="N6">
-        <v>2.3358400585432766E-4</v>
+        <v>-1.3071114307209065E-3</v>
       </c>
       <c r="O6">
-        <v>6.6744393248480876E-4</v>
+        <v>-1.0671149744496278E-3</v>
       </c>
       <c r="P6">
-        <v>-3.6292300873292478E-5</v>
+        <v>2.1219030292347435E-5</v>
       </c>
       <c r="Q6">
-        <v>-2.0621564026231292E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>-2.5041634792958515E-4</v>
+      </c>
+      <c r="R6">
+        <v>2.8429976594942993E-3</v>
+      </c>
+      <c r="S6">
+        <v>-6.8645384876809875E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>0.21187270083826154</v>
+      <c r="B7" s="5">
+        <v>-0.14826259944561873</v>
       </c>
       <c r="C7">
-        <v>-9.3789587232790685E-4</v>
+        <v>-1.4830549110630702E-3</v>
       </c>
       <c r="D7">
-        <v>7.2904169332132563E-4</v>
+        <v>9.5508862646267101E-4</v>
       </c>
       <c r="E7">
-        <v>-7.2001525002319559E-6</v>
+        <v>-9.4393243874891624E-6</v>
       </c>
       <c r="F7">
-        <v>-2.7043727161744175E-3</v>
+        <v>1.2618094498540594E-4</v>
       </c>
       <c r="G7">
-        <v>-2.6092316013499009E-3</v>
+        <v>-1.2271022403682191E-4</v>
       </c>
       <c r="H7">
-        <v>2.1585875338080509E-2</v>
+        <v>2.5222690061419153E-2</v>
       </c>
       <c r="I7">
-        <v>7.5738990107171956E-3</v>
+        <v>1.1998329487742189E-2</v>
       </c>
       <c r="J7">
-        <v>-3.1546373258199388E-3</v>
+        <v>1.8296895702706916E-3</v>
       </c>
       <c r="K7">
-        <v>6.902230168711874E-3</v>
+        <v>1.2000961908912587E-2</v>
       </c>
       <c r="L7">
-        <v>8.114763540969204E-3</v>
+        <v>1.5124683175316386E-2</v>
       </c>
       <c r="M7">
-        <v>7.2966493046323667E-3</v>
+        <v>1.5690602289006424E-2</v>
       </c>
       <c r="N7">
-        <v>7.4169038070450236E-5</v>
+        <v>2.1840933064961243E-3</v>
       </c>
       <c r="O7">
-        <v>1.7912333881950002E-5</v>
+        <v>2.9325011977677923E-3</v>
       </c>
       <c r="P7">
-        <v>-6.5062269181549509E-5</v>
+        <v>-1.2421527055643961E-4</v>
       </c>
       <c r="Q7">
-        <v>-2.1728230058502055E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>2.5852106303957808E-3</v>
+      </c>
+      <c r="R7">
+        <v>2.3207260075820023E-3</v>
+      </c>
+      <c r="S7">
+        <v>-3.6646683352793169E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>1.0526680091470736E-2</v>
+      <c r="B8" s="5">
+        <v>-9.5262686400007426E-3</v>
       </c>
       <c r="C8">
-        <v>-2.7327323616446384E-4</v>
+        <v>-1.1375236716823815E-3</v>
       </c>
       <c r="D8">
-        <v>2.33555253525632E-4</v>
+        <v>4.171289460348697E-4</v>
       </c>
       <c r="E8">
-        <v>-2.5524795467970782E-6</v>
+        <v>-4.5331253326475387E-6</v>
       </c>
       <c r="F8">
-        <v>-5.5846501993344917E-4</v>
+        <v>-6.0997955556260294E-4</v>
       </c>
       <c r="G8">
-        <v>-1.4244781165553182E-3</v>
+        <v>-2.2800643346818916E-3</v>
       </c>
       <c r="H8">
-        <v>7.5738990107171956E-3</v>
+        <v>1.1998329487742189E-2</v>
       </c>
       <c r="I8">
-        <v>7.3910514177886267E-3</v>
+        <v>1.2430351441309984E-2</v>
       </c>
       <c r="J8">
-        <v>-1.999708127677149E-3</v>
+        <v>-7.0220552855431535E-6</v>
       </c>
       <c r="K8">
-        <v>4.1662785779950735E-3</v>
+        <v>8.7680719383729424E-3</v>
       </c>
       <c r="L8">
-        <v>6.0038813334377088E-3</v>
+        <v>1.180239578835255E-2</v>
       </c>
       <c r="M8">
-        <v>5.9421409937781321E-3</v>
+        <v>1.1791618340491051E-2</v>
       </c>
       <c r="N8">
-        <v>4.4764291572977656E-4</v>
+        <v>1.5769282544966525E-3</v>
       </c>
       <c r="O8">
-        <v>2.9764786526977061E-4</v>
+        <v>1.4261592379294676E-3</v>
       </c>
       <c r="P8">
-        <v>-7.5949855618626799E-8</v>
+        <v>2.2194963392698419E-5</v>
       </c>
       <c r="Q8">
-        <v>-1.0928100921285084E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>1.350473370629845E-3</v>
+      </c>
+      <c r="R8">
+        <v>-1.4002592773012211E-4</v>
+      </c>
+      <c r="S8">
+        <v>-2.1104599028311063E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>-2.0554230872614912E-3</v>
+      <c r="B9" s="5">
+        <v>-2.4927222426801659E-2</v>
       </c>
       <c r="C9">
-        <v>6.0294420019665505E-4</v>
+        <v>-2.2532157458921698E-4</v>
       </c>
       <c r="D9">
-        <v>-2.0301704894384745E-4</v>
+        <v>4.4449674781482156E-5</v>
       </c>
       <c r="E9">
-        <v>2.028441644937423E-6</v>
+        <v>-4.6057860212901029E-7</v>
       </c>
       <c r="F9">
-        <v>9.158683822396204E-4</v>
+        <v>1.9982305452282862E-4</v>
       </c>
       <c r="G9">
-        <v>9.2365499651585452E-4</v>
+        <v>1.5195398760944633E-3</v>
       </c>
       <c r="H9">
-        <v>-3.1546373258199388E-3</v>
+        <v>1.8296895702706916E-3</v>
       </c>
       <c r="I9">
-        <v>-1.999708127677149E-3</v>
+        <v>-7.0220552855431535E-6</v>
       </c>
       <c r="J9">
-        <v>8.6437002441922019E-3</v>
+        <v>1.0076460093857553E-2</v>
       </c>
       <c r="K9">
-        <v>2.7883967915014211E-3</v>
+        <v>5.285616531229E-3</v>
       </c>
       <c r="L9">
-        <v>2.0268430415056617E-3</v>
+        <v>5.4963888013992938E-3</v>
       </c>
       <c r="M9">
-        <v>2.1308711511933533E-3</v>
+        <v>5.5155307188211261E-3</v>
       </c>
       <c r="N9">
-        <v>-8.5043210513640645E-4</v>
+        <v>-3.2795763177627304E-4</v>
       </c>
       <c r="O9">
-        <v>-1.3435713669876061E-3</v>
+        <v>-7.499082900644027E-4</v>
       </c>
       <c r="P9">
-        <v>7.0554253164104605E-5</v>
+        <v>-3.4504808326513451E-5</v>
       </c>
       <c r="Q9">
-        <v>1.2191149243129546E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>4.1641089284618141E-5</v>
+      </c>
+      <c r="R9">
+        <v>4.6392163792307456E-4</v>
+      </c>
+      <c r="S9">
+        <v>-5.6932234296030951E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>9.0571586918866617E-2</v>
+      <c r="B10" s="5">
+        <v>2.9793499757227716E-2</v>
       </c>
       <c r="C10">
-        <v>-3.1181963921286105E-4</v>
+        <v>-1.2264103945807837E-3</v>
       </c>
       <c r="D10">
-        <v>-6.054982782553614E-6</v>
+        <v>2.9359495567787982E-4</v>
       </c>
       <c r="E10">
-        <v>3.6105354216506137E-7</v>
+        <v>-2.6587013746380629E-6</v>
       </c>
       <c r="F10">
-        <v>-4.8477586079501665E-4</v>
+        <v>6.6421880184105823E-5</v>
       </c>
       <c r="G10">
-        <v>-7.2331394073804069E-4</v>
+        <v>5.4176663315402569E-5</v>
       </c>
       <c r="H10">
-        <v>6.902230168711874E-3</v>
+        <v>1.2000961908912587E-2</v>
       </c>
       <c r="I10">
-        <v>4.1662785779950735E-3</v>
+        <v>8.7680719383729424E-3</v>
       </c>
       <c r="J10">
-        <v>2.7883967915014211E-3</v>
+        <v>5.285616531229E-3</v>
       </c>
       <c r="K10">
-        <v>9.0487520835998789E-3</v>
+        <v>1.4016520943936708E-2</v>
       </c>
       <c r="L10">
-        <v>8.052942457769342E-3</v>
+        <v>1.4157348861923507E-2</v>
       </c>
       <c r="M10">
-        <v>8.0346561506315518E-3</v>
+        <v>1.4381285762909523E-2</v>
       </c>
       <c r="N10">
-        <v>-2.2952280946109994E-4</v>
+        <v>1.0374649528121413E-3</v>
       </c>
       <c r="O10">
-        <v>-6.7797051253245134E-4</v>
+        <v>8.3682988494513787E-4</v>
       </c>
       <c r="P10">
-        <v>-5.8828228268405398E-6</v>
+        <v>-3.6321482242765245E-5</v>
       </c>
       <c r="Q10">
-        <v>-7.7315483444672225E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>4.6390192096813472E-4</v>
+      </c>
+      <c r="R10">
+        <v>-1.0694123650345369E-4</v>
+      </c>
+      <c r="S10">
+        <v>-2.0909980455632294E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>6.4633097466303538E-2</v>
+      <c r="B11" s="5">
+        <v>-5.6373711099974494E-2</v>
       </c>
       <c r="C11">
-        <v>-6.1138963643399757E-4</v>
+        <v>-2.0413917000660386E-3</v>
       </c>
       <c r="D11">
-        <v>-5.5960071690848082E-5</v>
+        <v>2.9146068933853212E-4</v>
       </c>
       <c r="E11">
-        <v>9.3668993093631918E-7</v>
+        <v>-2.7185154008780126E-6</v>
       </c>
       <c r="F11">
-        <v>1.35524805748603E-4</v>
+        <v>-7.8642977139397469E-5</v>
       </c>
       <c r="G11">
-        <v>-1.4506917706639226E-4</v>
+        <v>5.01063870498247E-4</v>
       </c>
       <c r="H11">
-        <v>8.114763540969204E-3</v>
+        <v>1.5124683175316386E-2</v>
       </c>
       <c r="I11">
-        <v>6.0038813334377088E-3</v>
+        <v>1.180239578835255E-2</v>
       </c>
       <c r="J11">
-        <v>2.0268430415056617E-3</v>
+        <v>5.4963888013992938E-3</v>
       </c>
       <c r="K11">
-        <v>8.052942457769342E-3</v>
+        <v>1.4157348861923507E-2</v>
       </c>
       <c r="L11">
-        <v>1.1550863454911017E-2</v>
+        <v>2.0700170419895077E-2</v>
       </c>
       <c r="M11">
-        <v>9.7405293684317204E-3</v>
+        <v>1.7875822516737836E-2</v>
       </c>
       <c r="N11">
-        <v>4.2618777223274451E-4</v>
+        <v>1.5954882786295942E-3</v>
       </c>
       <c r="O11">
-        <v>-3.6413635833125717E-4</v>
+        <v>1.1010390979155314E-3</v>
       </c>
       <c r="P11">
-        <v>7.5265426403073039E-6</v>
+        <v>-7.1887437970720832E-5</v>
       </c>
       <c r="Q11">
-        <v>-9.2955745895016081E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+        <v>1.1248216542036095E-3</v>
+      </c>
+      <c r="R11">
+        <v>2.3887678123051151E-3</v>
+      </c>
+      <c r="S11">
+        <v>-2.3640760919560577E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>0.14364332523489245</v>
+      <c r="B12" s="5">
+        <v>1.5925790491649896E-3</v>
       </c>
       <c r="C12">
-        <v>-4.2246116403799473E-4</v>
+        <v>-1.5779920282146273E-3</v>
       </c>
       <c r="D12">
-        <v>-1.7973133475351598E-4</v>
+        <v>3.1767743737139793E-4</v>
       </c>
       <c r="E12">
-        <v>2.1589188287859694E-6</v>
+        <v>-2.8174854627068318E-6</v>
       </c>
       <c r="F12">
-        <v>9.2154229558073883E-4</v>
+        <v>5.3192459360171555E-4</v>
       </c>
       <c r="G12">
-        <v>8.8862326980165536E-4</v>
+        <v>5.9790701958282186E-4</v>
       </c>
       <c r="H12">
-        <v>7.2966493046323667E-3</v>
+        <v>1.5690602289006424E-2</v>
       </c>
       <c r="I12">
-        <v>5.9421409937781321E-3</v>
+        <v>1.1791618340491051E-2</v>
       </c>
       <c r="J12">
-        <v>2.1308711511933533E-3</v>
+        <v>5.5155307188211261E-3</v>
       </c>
       <c r="K12">
-        <v>8.0346561506315518E-3</v>
+        <v>1.4381285762909523E-2</v>
       </c>
       <c r="L12">
-        <v>9.7405293684317204E-3</v>
+        <v>1.7875822516737836E-2</v>
       </c>
       <c r="M12">
-        <v>1.4136589069173445E-2</v>
+        <v>2.1983376989805008E-2</v>
       </c>
       <c r="N12">
-        <v>4.9555329571255441E-5</v>
+        <v>2.6749145461421446E-3</v>
       </c>
       <c r="O12">
-        <v>-2.4267253715127505E-4</v>
+        <v>2.0782322072095934E-3</v>
       </c>
       <c r="P12">
-        <v>3.2338719726319749E-5</v>
+        <v>-3.9459077748625994E-5</v>
       </c>
       <c r="Q12">
-        <v>-7.8472444873601607E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>5.9806472305819116E-4</v>
+      </c>
+      <c r="R12">
+        <v>4.0541098672193434E-4</v>
+      </c>
+      <c r="S12">
+        <v>-2.6532209271762499E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B13">
-        <v>-0.20753690803018063</v>
+      <c r="B13" s="5">
+        <v>-0.14466330754227427</v>
       </c>
       <c r="C13">
-        <v>-2.3396758086623653E-4</v>
+        <v>-8.0520151873903888E-4</v>
       </c>
       <c r="D13">
-        <v>8.9678107468355115E-5</v>
+        <v>5.8426758961878465E-5</v>
       </c>
       <c r="E13">
-        <v>-9.1976427505158025E-7</v>
+        <v>-5.8609930291867203E-7</v>
       </c>
       <c r="F13">
-        <v>4.6661206432291194E-4</v>
+        <v>-1.5174574141722233E-4</v>
       </c>
       <c r="G13">
-        <v>2.3358400585432766E-4</v>
+        <v>-1.3071114307209065E-3</v>
       </c>
       <c r="H13">
-        <v>7.4169038070450236E-5</v>
+        <v>2.1840933064961243E-3</v>
       </c>
       <c r="I13">
-        <v>4.4764291572977656E-4</v>
+        <v>1.5769282544966525E-3</v>
       </c>
       <c r="J13">
-        <v>-8.5043210513640645E-4</v>
+        <v>-3.2795763177627304E-4</v>
       </c>
       <c r="K13">
-        <v>-2.2952280946109994E-4</v>
+        <v>1.0374649528121413E-3</v>
       </c>
       <c r="L13">
-        <v>4.2618777223274451E-4</v>
+        <v>1.5954882786295942E-3</v>
       </c>
       <c r="M13">
-        <v>4.9555329571255441E-5</v>
+        <v>2.6749145461421446E-3</v>
       </c>
       <c r="N13">
-        <v>4.4394528974983699E-3</v>
+        <v>5.883308407862501E-3</v>
       </c>
       <c r="O13">
-        <v>2.8066747737984206E-3</v>
+        <v>3.6012077636882714E-3</v>
       </c>
       <c r="P13">
-        <v>-1.6242710671088599E-5</v>
+        <v>3.3438663304352525E-5</v>
       </c>
       <c r="Q13">
-        <v>-4.7267521961742867E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <v>2.5152342624477832E-4</v>
+      </c>
+      <c r="R13">
+        <v>-1.0941257530400622E-3</v>
+      </c>
+      <c r="S13">
+        <v>-6.1938231707639813E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B14">
-        <v>-0.11474350513431544</v>
+      <c r="B14" s="5">
+        <v>-7.3383710973340607E-2</v>
       </c>
       <c r="C14">
-        <v>2.2664862599007724E-5</v>
+        <v>-7.2754760314824515E-4</v>
       </c>
       <c r="D14">
-        <v>1.5371879147930718E-4</v>
+        <v>1.9631070283859017E-4</v>
       </c>
       <c r="E14">
-        <v>-1.5475787725445226E-6</v>
+        <v>-1.9870156376583704E-6</v>
       </c>
       <c r="F14">
-        <v>5.9704613798870548E-4</v>
+        <v>-3.5621544395307743E-4</v>
       </c>
       <c r="G14">
-        <v>6.6744393248480876E-4</v>
+        <v>-1.0671149744496278E-3</v>
       </c>
       <c r="H14">
-        <v>1.7912333881950002E-5</v>
+        <v>2.9325011977677923E-3</v>
       </c>
       <c r="I14">
-        <v>2.9764786526977061E-4</v>
+        <v>1.4261592379294676E-3</v>
       </c>
       <c r="J14">
-        <v>-1.3435713669876061E-3</v>
+        <v>-7.499082900644027E-4</v>
       </c>
       <c r="K14">
-        <v>-6.7797051253245134E-4</v>
+        <v>8.3682988494513787E-4</v>
       </c>
       <c r="L14">
-        <v>-3.6413635833125717E-4</v>
+        <v>1.1010390979155314E-3</v>
       </c>
       <c r="M14">
-        <v>-2.4267253715127505E-4</v>
+        <v>2.0782322072095934E-3</v>
       </c>
       <c r="N14">
-        <v>2.8066747737984206E-3</v>
+        <v>3.6012077636882714E-3</v>
       </c>
       <c r="O14">
-        <v>3.8498655713519259E-3</v>
+        <v>4.8624917095818612E-3</v>
       </c>
       <c r="P14">
-        <v>-1.60025505424359E-5</v>
+        <v>-6.918057560949541E-7</v>
       </c>
       <c r="Q14">
-        <v>-6.0470187830422364E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>8.7123810153963009E-4</v>
+      </c>
+      <c r="R14">
+        <v>-7.3035229924607603E-4</v>
+      </c>
+      <c r="S14">
+        <v>-8.3292959055636349E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>1.6813195333563503E-2</v>
+      <c r="B15" s="5">
+        <v>2.0752595098394559E-2</v>
       </c>
       <c r="C15">
-        <v>3.5918955462177425E-6</v>
+        <v>6.0629112341232974E-6</v>
       </c>
       <c r="D15">
-        <v>-1.2066099536003818E-5</v>
+        <v>6.8705390397704141E-7</v>
       </c>
       <c r="E15">
-        <v>1.1794884775395675E-7</v>
+        <v>-2.6185780541795668E-8</v>
       </c>
       <c r="F15">
-        <v>-1.3012785454974407E-5</v>
+        <v>2.2341901174853241E-5</v>
       </c>
       <c r="G15">
-        <v>-3.6292300873292478E-5</v>
+        <v>2.1219030292347435E-5</v>
       </c>
       <c r="H15">
-        <v>-6.5062269181549509E-5</v>
+        <v>-1.2421527055643961E-4</v>
       </c>
       <c r="I15">
-        <v>-7.5949855618626799E-8</v>
+        <v>2.2194963392698419E-5</v>
       </c>
       <c r="J15">
-        <v>7.0554253164104605E-5</v>
+        <v>-3.4504808326513451E-5</v>
       </c>
       <c r="K15">
-        <v>-5.8828228268405398E-6</v>
+        <v>-3.6321482242765245E-5</v>
       </c>
       <c r="L15">
-        <v>7.5265426403073039E-6</v>
+        <v>-7.1887437970720832E-5</v>
       </c>
       <c r="M15">
-        <v>3.2338719726319749E-5</v>
+        <v>-3.9459077748625994E-5</v>
       </c>
       <c r="N15">
-        <v>-1.6242710671088599E-5</v>
+        <v>3.3438663304352525E-5</v>
       </c>
       <c r="O15">
-        <v>-1.60025505424359E-5</v>
+        <v>-6.918057560949541E-7</v>
       </c>
       <c r="P15">
-        <v>5.6915466411521038E-5</v>
+        <v>3.9492267138794857E-5</v>
       </c>
       <c r="Q15">
-        <v>-5.707451775701592E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>-1.3714553537977369E-4</v>
+      </c>
+      <c r="R15">
+        <v>-1.9989765072287737E-4</v>
+      </c>
+      <c r="S15">
+        <v>-6.1538325739129551E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="5">
+        <v>-0.38964498170701173</v>
+      </c>
+      <c r="C16">
+        <v>-2.6502130858151293E-4</v>
+      </c>
+      <c r="D16">
+        <v>2.4663647223517886E-4</v>
+      </c>
+      <c r="E16">
+        <v>-2.7402851885344099E-6</v>
+      </c>
+      <c r="F16">
+        <v>-8.0562031822273717E-5</v>
+      </c>
+      <c r="G16">
+        <v>-2.5041634792958515E-4</v>
+      </c>
+      <c r="H16">
+        <v>2.5852106303957808E-3</v>
+      </c>
+      <c r="I16">
+        <v>1.350473370629845E-3</v>
+      </c>
+      <c r="J16">
+        <v>4.1641089284618141E-5</v>
+      </c>
+      <c r="K16">
+        <v>4.6390192096813472E-4</v>
+      </c>
+      <c r="L16">
+        <v>1.1248216542036095E-3</v>
+      </c>
+      <c r="M16">
+        <v>5.9806472305819116E-4</v>
+      </c>
+      <c r="N16">
+        <v>2.5152342624477832E-4</v>
+      </c>
+      <c r="O16">
+        <v>8.7123810153963009E-4</v>
+      </c>
+      <c r="P16">
+        <v>-1.3714553537977369E-4</v>
+      </c>
+      <c r="Q16">
+        <v>1.1352507467361451E-2</v>
+      </c>
+      <c r="R16">
+        <v>1.3680926033630184E-3</v>
+      </c>
+      <c r="S16">
+        <v>-4.7498623047532215E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="5">
+        <v>-8.6026458457322583E-2</v>
+      </c>
+      <c r="C17">
+        <v>7.780703498571044E-4</v>
+      </c>
+      <c r="D17">
+        <v>3.8540451815181767E-4</v>
+      </c>
+      <c r="E17">
+        <v>-3.9136496008656944E-6</v>
+      </c>
+      <c r="F17">
+        <v>1.4438994907479659E-4</v>
+      </c>
+      <c r="G17">
+        <v>2.8429976594942993E-3</v>
+      </c>
+      <c r="H17">
+        <v>2.3207260075820023E-3</v>
+      </c>
+      <c r="I17">
+        <v>-1.4002592773012211E-4</v>
+      </c>
+      <c r="J17">
+        <v>4.6392163792307456E-4</v>
+      </c>
+      <c r="K17">
+        <v>-1.0694123650345369E-4</v>
+      </c>
+      <c r="L17">
+        <v>2.3887678123051151E-3</v>
+      </c>
+      <c r="M17">
+        <v>4.0541098672193434E-4</v>
+      </c>
+      <c r="N17">
+        <v>-1.0941257530400622E-3</v>
+      </c>
+      <c r="O17">
+        <v>-7.3035229924607603E-4</v>
+      </c>
+      <c r="P17">
+        <v>-1.9989765072287737E-4</v>
+      </c>
+      <c r="Q17">
+        <v>1.3680926033630184E-3</v>
+      </c>
+      <c r="R17">
+        <v>2.2617126999588181E-2</v>
+      </c>
+      <c r="S17">
+        <v>-7.3175293637910005E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B16">
-        <v>-2.4218697866246486</v>
-      </c>
-      <c r="C16">
-        <v>-1.5314507206155739E-4</v>
-      </c>
-      <c r="D16">
-        <v>-3.1926207850553395E-3</v>
-      </c>
-      <c r="E16">
-        <v>3.4302067358376063E-5</v>
-      </c>
-      <c r="F16">
-        <v>-1.863657679340003E-3</v>
-      </c>
-      <c r="G16">
-        <v>-2.0621564026231292E-3</v>
-      </c>
-      <c r="H16">
-        <v>-2.1728230058502055E-2</v>
-      </c>
-      <c r="I16">
-        <v>-1.0928100921285084E-2</v>
-      </c>
-      <c r="J16">
-        <v>1.2191149243129546E-3</v>
-      </c>
-      <c r="K16">
-        <v>-7.7315483444672225E-3</v>
-      </c>
-      <c r="L16">
-        <v>-9.2955745895016081E-3</v>
-      </c>
-      <c r="M16">
-        <v>-7.8472444873601607E-3</v>
-      </c>
-      <c r="N16">
-        <v>-4.7267521961742867E-3</v>
-      </c>
-      <c r="O16">
-        <v>-6.0470187830422364E-3</v>
-      </c>
-      <c r="P16">
-        <v>-5.707451775701592E-4</v>
-      </c>
-      <c r="Q16">
-        <v>9.2727785173743971E-2</v>
+      <c r="B18" s="5">
+        <v>-2.7157686728987183</v>
+      </c>
+      <c r="C18">
+        <v>2.6016829038594041E-3</v>
+      </c>
+      <c r="D18">
+        <v>-4.4507543392197126E-3</v>
+      </c>
+      <c r="E18">
+        <v>4.8104986947004712E-5</v>
+      </c>
+      <c r="F18">
+        <v>-4.4581025951299542E-3</v>
+      </c>
+      <c r="G18">
+        <v>-6.8645384876809875E-3</v>
+      </c>
+      <c r="H18">
+        <v>-3.6646683352793169E-2</v>
+      </c>
+      <c r="I18">
+        <v>-2.1104599028311063E-2</v>
+      </c>
+      <c r="J18">
+        <v>-5.6932234296030951E-3</v>
+      </c>
+      <c r="K18">
+        <v>-2.0909980455632294E-2</v>
+      </c>
+      <c r="L18">
+        <v>-2.3640760919560577E-2</v>
+      </c>
+      <c r="M18">
+        <v>-2.6532209271762499E-2</v>
+      </c>
+      <c r="N18">
+        <v>-6.1938231707639813E-3</v>
+      </c>
+      <c r="O18">
+        <v>-8.3292959055636349E-3</v>
+      </c>
+      <c r="P18">
+        <v>-6.1538325739129551E-4</v>
+      </c>
+      <c r="Q18">
+        <v>-4.7498623047532215E-3</v>
+      </c>
+      <c r="R18">
+        <v>-7.3175293637910005E-3</v>
+      </c>
+      <c r="S18">
+        <v>0.13902882512292375</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_leaveParentalHome.xlsx
+++ b/input/reg_leaveParentalHome.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2CA7DF-DF72-466B-B299-579B57BD38D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E162B441-726B-4DC4-94FE-FEDB0284BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="PL_P1a" sheetId="3" r:id="rId2"/>
+    <sheet name="IT_P1a" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>Description:</t>
   </si>
@@ -86,53 +86,32 @@
     <t>Y2020</t>
   </si>
   <si>
-    <t>Y2021</t>
-  </si>
-  <si>
     <t>Constant</t>
   </si>
   <si>
-    <t>PL4</t>
-  </si>
-  <si>
-    <t>PL5</t>
-  </si>
-  <si>
-    <t>PL6</t>
-  </si>
-  <si>
-    <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
-  </si>
-  <si>
-    <t>PL10</t>
+    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
+  </si>
+  <si>
+    <t>ITF</t>
+  </si>
+  <si>
+    <t>ITG</t>
+  </si>
+  <si>
+    <t>ITH</t>
+  </si>
+  <si>
+    <t>ITI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -142,104 +121,9 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -252,168 +136,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="26">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -439,33 +162,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,7 +502,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -812,10 +513,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
@@ -832,7 +533,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -842,14 +543,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
@@ -895,7 +596,7 @@
         <v>25</v>
       </c>
       <c r="Q1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R1" t="s">
         <v>19</v>
@@ -906,1244 +607,1126 @@
       <c r="T1" t="s">
         <v>21</v>
       </c>
-      <c r="U1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="25">
-        <v>-3.153886901475092E-2</v>
+      <c r="B2">
+        <v>-0.11665255243619094</v>
       </c>
       <c r="C2">
-        <v>2.7138111712166043E-3</v>
+        <v>3.1072053774141048E-3</v>
       </c>
       <c r="D2">
-        <v>-4.4042173700765126E-5</v>
+        <v>5.3018779782759603E-5</v>
       </c>
       <c r="E2">
-        <v>5.212442662352249E-7</v>
+        <v>-3.8824340580041835E-7</v>
       </c>
       <c r="F2">
-        <v>-1.1998189861514817E-3</v>
+        <v>1.9971902367906674E-4</v>
       </c>
       <c r="G2">
-        <v>-1.5035471558158648E-3</v>
+        <v>2.1342907149638491E-4</v>
       </c>
       <c r="H2">
-        <v>7.4228351539488795E-4</v>
+        <v>6.5297588585840299E-4</v>
       </c>
       <c r="I2">
-        <v>4.9803164240136747E-4</v>
+        <v>2.7761284365612169E-4</v>
       </c>
       <c r="J2">
-        <v>5.2432953270923274E-5</v>
+        <v>1.9996577603494675E-4</v>
       </c>
       <c r="K2">
-        <v>4.1024269281039988E-4</v>
+        <v>2.9751552969763015E-4</v>
       </c>
       <c r="L2">
-        <v>2.7414811055102438E-4</v>
+        <v>-2.9177979542105101E-4</v>
       </c>
       <c r="M2">
-        <v>-6.6563500081986623E-5</v>
+        <v>2.1171902245266101E-4</v>
       </c>
       <c r="N2">
-        <v>-3.6173457267957092E-4</v>
+        <v>1.6792533159027054E-4</v>
       </c>
       <c r="O2">
-        <v>1.0019547275450218E-5</v>
+        <v>-6.6383971844634077E-4</v>
       </c>
       <c r="P2">
-        <v>-2.2551152827917818E-4</v>
+        <v>1.4827892130014485E-4</v>
       </c>
       <c r="Q2">
-        <v>-4.8017637868189239E-4</v>
+        <v>-9.5053186783118391E-5</v>
       </c>
       <c r="R2">
-        <v>1.853372786523339E-5</v>
+        <v>-7.7364248326043373E-6</v>
       </c>
       <c r="S2">
-        <v>-4.2006908702979669E-4</v>
+        <v>-6.5627161746209279E-4</v>
       </c>
       <c r="T2">
-        <v>-4.6247554095766414E-5</v>
-      </c>
-      <c r="U2">
-        <v>-1.3054835906601295E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
+        <v>-3.3823911252607811E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25">
-        <v>1.1165347351412974E-3</v>
+      <c r="B3">
+        <v>1.5959002028928627E-2</v>
       </c>
       <c r="C3">
-        <v>-4.4042173700765126E-5</v>
+        <v>5.3018779782759603E-5</v>
       </c>
       <c r="D3">
-        <v>1.4715148324672997E-4</v>
+        <v>1.9540707253068695E-4</v>
       </c>
       <c r="E3">
-        <v>-1.630684692121317E-6</v>
+        <v>-2.0384986038459955E-6</v>
       </c>
       <c r="F3">
-        <v>1.4006426051449186E-4</v>
+        <v>-1.0346847977282412E-5</v>
       </c>
       <c r="G3">
-        <v>2.0550593255125592E-4</v>
+        <v>-1.1762252871309431E-4</v>
       </c>
       <c r="H3">
-        <v>5.6595805211045319E-4</v>
+        <v>8.2841807353551419E-4</v>
       </c>
       <c r="I3">
-        <v>4.9942544109857949E-7</v>
+        <v>1.0388297784687966E-4</v>
       </c>
       <c r="J3">
-        <v>9.9448508742321247E-5</v>
+        <v>1.0366338802755934E-4</v>
       </c>
       <c r="K3">
-        <v>9.3426551069589805E-5</v>
+        <v>2.0805397281212831E-4</v>
       </c>
       <c r="L3">
-        <v>7.4750750814727828E-6</v>
+        <v>-1.1055136486285214E-5</v>
       </c>
       <c r="M3">
-        <v>6.0544215738963635E-6</v>
+        <v>-9.2400379162897988E-5</v>
       </c>
       <c r="N3">
-        <v>-1.613455948566698E-4</v>
+        <v>-1.3884152318324261E-4</v>
       </c>
       <c r="O3">
-        <v>-5.2838722402124812E-5</v>
+        <v>-2.6588169724675652E-4</v>
       </c>
       <c r="P3">
-        <v>-1.2163936475016344E-4</v>
+        <v>-1.7171163662585268E-4</v>
       </c>
       <c r="Q3">
-        <v>-6.7730808577116291E-5</v>
+        <v>-2.6502242576178798E-4</v>
       </c>
       <c r="R3">
-        <v>-9.9681143497016471E-6</v>
+        <v>-8.9100406146334498E-6</v>
       </c>
       <c r="S3">
-        <v>1.4618694956358938E-4</v>
+        <v>-2.7610964267736214E-4</v>
       </c>
       <c r="T3">
-        <v>4.9821301341587774E-5</v>
-      </c>
-      <c r="U3">
-        <v>-2.9049888381541748E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
+        <v>-4.0679282969788861E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="25">
-        <v>4.8199728365463533E-4</v>
+      <c r="B4">
+        <v>2.9471462899883236E-4</v>
       </c>
       <c r="C4">
-        <v>5.212442662352249E-7</v>
+        <v>-3.8824340580041835E-7</v>
       </c>
       <c r="D4">
-        <v>-1.630684692121317E-6</v>
+        <v>-2.0384986038459955E-6</v>
       </c>
       <c r="E4">
-        <v>1.8524520065848634E-8</v>
+        <v>2.1896228208100444E-8</v>
       </c>
       <c r="F4">
-        <v>-1.5248831375794918E-6</v>
+        <v>5.7084788703991417E-7</v>
       </c>
       <c r="G4">
-        <v>-2.2337569665263269E-6</v>
+        <v>1.316578382667805E-6</v>
       </c>
       <c r="H4">
-        <v>-5.6366614763165203E-6</v>
+        <v>-7.6566532169463463E-6</v>
       </c>
       <c r="I4">
-        <v>-4.2419608677183134E-7</v>
+        <v>-1.3067959153437273E-6</v>
       </c>
       <c r="J4">
-        <v>-1.052023043085295E-6</v>
+        <v>-7.9670026895101053E-7</v>
       </c>
       <c r="K4">
-        <v>-8.6891559200697434E-7</v>
+        <v>-1.6205127887724578E-6</v>
       </c>
       <c r="L4">
-        <v>-5.8357044489944793E-8</v>
+        <v>3.7445727839454096E-7</v>
       </c>
       <c r="M4">
-        <v>-1.8073561290011378E-8</v>
+        <v>1.1793410995312413E-6</v>
       </c>
       <c r="N4">
-        <v>1.7971483341677467E-6</v>
+        <v>1.8024596597384412E-6</v>
       </c>
       <c r="O4">
-        <v>4.9783687837146108E-7</v>
+        <v>2.8894378140545946E-6</v>
       </c>
       <c r="P4">
-        <v>1.3646827261289905E-6</v>
+        <v>1.5359142673637339E-6</v>
       </c>
       <c r="Q4">
-        <v>6.1802787958010054E-7</v>
+        <v>2.438407671292133E-6</v>
       </c>
       <c r="R4">
-        <v>8.0177784533272014E-8</v>
+        <v>4.0657622425960691E-8</v>
       </c>
       <c r="S4">
-        <v>-1.3498100560635599E-6</v>
+        <v>2.809613806166921E-6</v>
       </c>
       <c r="T4">
-        <v>-3.4963450553689366E-7</v>
-      </c>
-      <c r="U4">
-        <v>3.1840598958818253E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+        <v>4.1336281359242754E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="25">
-        <v>6.6155806229693082E-2</v>
+      <c r="B5">
+        <v>8.4153018387571471E-2</v>
       </c>
       <c r="C5">
-        <v>-1.1998189861514817E-3</v>
+        <v>1.9971902367906674E-4</v>
       </c>
       <c r="D5">
-        <v>1.4006426051449186E-4</v>
+        <v>-1.0346847977282412E-5</v>
       </c>
       <c r="E5">
-        <v>-1.5248831375794918E-6</v>
+        <v>5.7084788703991417E-7</v>
       </c>
       <c r="F5">
-        <v>5.0946506351035393E-3</v>
+        <v>7.5342832814023807E-3</v>
       </c>
       <c r="G5">
-        <v>4.3191938795045792E-3</v>
+        <v>5.8743758350544382E-3</v>
       </c>
       <c r="H5">
-        <v>-2.9604614543362576E-4</v>
+        <v>3.9301068216984368E-4</v>
       </c>
       <c r="I5">
-        <v>-3.8248840097788322E-4</v>
+        <v>-8.147106009014657E-4</v>
       </c>
       <c r="J5">
-        <v>-6.1084290097578975E-6</v>
+        <v>1.8619441540778355E-3</v>
       </c>
       <c r="K5">
-        <v>-2.094323869061155E-4</v>
+        <v>1.3965063238404558E-3</v>
       </c>
       <c r="L5">
-        <v>-6.5770750103680579E-4</v>
+        <v>1.5513213744295208E-3</v>
       </c>
       <c r="M5">
-        <v>6.5674232673097982E-4</v>
+        <v>2.8476683861385728E-3</v>
       </c>
       <c r="N5">
-        <v>4.6928891927912558E-4</v>
+        <v>1.2628516551870098E-3</v>
       </c>
       <c r="O5">
-        <v>6.5435371642265762E-4</v>
+        <v>1.7452778991200975E-3</v>
       </c>
       <c r="P5">
-        <v>6.4205897937459166E-4</v>
+        <v>2.2592037170349449E-4</v>
       </c>
       <c r="Q5">
-        <v>3.7195079985539959E-4</v>
+        <v>-2.4121382828014358E-4</v>
       </c>
       <c r="R5">
-        <v>-8.4815273089669659E-5</v>
+        <v>-1.8265244248629289E-4</v>
       </c>
       <c r="S5">
-        <v>1.1365746901166136E-3</v>
+        <v>9.9638628181522083E-4</v>
       </c>
       <c r="T5">
-        <v>7.2621931669947042E-4</v>
-      </c>
-      <c r="U5">
-        <v>-5.0880645528419708E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A6" s="10" t="s">
+        <v>-5.3423360247093279E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="25">
-        <v>0.16163173132467293</v>
+      <c r="B6">
+        <v>5.2612775087819218E-2</v>
       </c>
       <c r="C6">
-        <v>-1.5035471558158648E-3</v>
+        <v>2.1342907149638491E-4</v>
       </c>
       <c r="D6">
-        <v>2.0550593255125592E-4</v>
+        <v>-1.1762252871309431E-4</v>
       </c>
       <c r="E6">
-        <v>-2.2337569665263269E-6</v>
+        <v>1.316578382667805E-6</v>
       </c>
       <c r="F6">
-        <v>4.3191938795045792E-3</v>
+        <v>5.8743758350544382E-3</v>
       </c>
       <c r="G6">
-        <v>7.4778394912455763E-3</v>
+        <v>8.4708141667496767E-3</v>
       </c>
       <c r="H6">
-        <v>-7.1625177546400789E-4</v>
+        <v>-2.7288204424195939E-4</v>
       </c>
       <c r="I6">
-        <v>-4.991908673410108E-4</v>
+        <v>-1.8447962727405035E-3</v>
       </c>
       <c r="J6">
-        <v>1.7984503590435377E-4</v>
+        <v>2.2307637882138564E-3</v>
       </c>
       <c r="K6">
-        <v>4.3036617516158351E-5</v>
+        <v>1.4104440563031469E-3</v>
       </c>
       <c r="L6">
-        <v>7.8368079235106966E-5</v>
+        <v>1.1936431935963047E-3</v>
       </c>
       <c r="M6">
-        <v>1.1816488399494E-3</v>
+        <v>3.4099513425915121E-3</v>
       </c>
       <c r="N6">
-        <v>7.3345767495893712E-4</v>
+        <v>1.6574776638180989E-3</v>
       </c>
       <c r="O6">
-        <v>2.446418363308972E-4</v>
+        <v>9.495491834324403E-4</v>
       </c>
       <c r="P6">
-        <v>3.8885163647510565E-4</v>
+        <v>1.2379578923736121E-3</v>
       </c>
       <c r="Q6">
-        <v>3.0349642241586129E-4</v>
+        <v>4.4738993930741003E-4</v>
       </c>
       <c r="R6">
-        <v>-4.5113381511268269E-5</v>
+        <v>-1.2569327006975626E-4</v>
       </c>
       <c r="S6">
-        <v>7.8465208508262947E-4</v>
+        <v>1.6293921218012769E-3</v>
       </c>
       <c r="T6">
-        <v>4.2273139124957221E-4</v>
-      </c>
-      <c r="U6">
-        <v>-7.2088634383775654E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
+        <v>-3.364111670384847E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="25">
-        <v>-8.5393534937812252E-2</v>
+      <c r="B7">
+        <v>-0.37650018517925599</v>
       </c>
       <c r="C7">
-        <v>7.4228351539488795E-4</v>
+        <v>6.5297588585840299E-4</v>
       </c>
       <c r="D7">
-        <v>5.6595805211045319E-4</v>
+        <v>8.2841807353551419E-4</v>
       </c>
       <c r="E7">
-        <v>-5.6366614763165203E-6</v>
+        <v>-7.6566532169463463E-6</v>
       </c>
       <c r="F7">
-        <v>-2.9604614543362576E-4</v>
+        <v>3.9301068216984368E-4</v>
       </c>
       <c r="G7">
-        <v>-7.1625177546400789E-4</v>
+        <v>-2.7288204424195939E-4</v>
       </c>
       <c r="H7">
-        <v>1.6475082549353988E-2</v>
+        <v>3.4123409077127728E-2</v>
       </c>
       <c r="I7">
-        <v>3.3031895542429074E-3</v>
+        <v>5.5415939115344443E-3</v>
       </c>
       <c r="J7">
-        <v>2.7781280182433989E-4</v>
+        <v>1.4807351369124221E-3</v>
       </c>
       <c r="K7">
-        <v>3.8299952970011091E-3</v>
+        <v>5.2732422650741129E-3</v>
       </c>
       <c r="L7">
-        <v>3.7834760685082694E-3</v>
+        <v>7.105257148090822E-3</v>
       </c>
       <c r="M7">
-        <v>3.7918788744625569E-3</v>
+        <v>7.4877982395360997E-3</v>
       </c>
       <c r="N7">
-        <v>-4.1176120448207284E-4</v>
+        <v>-1.0158582408914974E-4</v>
       </c>
       <c r="O7">
-        <v>9.6194364760185651E-4</v>
+        <v>-1.9493040940848092E-3</v>
       </c>
       <c r="P7">
-        <v>1.5979758605881057E-4</v>
+        <v>-1.6653665831099914E-3</v>
       </c>
       <c r="Q7">
-        <v>-2.7264415967617577E-4</v>
+        <v>-2.5592008068141183E-3</v>
       </c>
       <c r="R7">
-        <v>-1.8423688999543429E-4</v>
+        <v>-2.0138015442662744E-4</v>
       </c>
       <c r="S7">
-        <v>6.4353004501476819E-4</v>
+        <v>-2.2488595407094917E-3</v>
       </c>
       <c r="T7">
-        <v>8.7213267352028584E-4</v>
-      </c>
-      <c r="U7">
-        <v>-1.4154796903401622E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+        <v>-2.3850308120631505E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="25">
-        <v>-0.1156373647504981</v>
+      <c r="B8">
+        <v>-0.10710973726362788</v>
       </c>
       <c r="C8">
-        <v>4.9803164240136747E-4</v>
+        <v>2.7761284365612169E-4</v>
       </c>
       <c r="D8">
-        <v>4.9942544109857949E-7</v>
+        <v>1.0388297784687966E-4</v>
       </c>
       <c r="E8">
-        <v>-4.2419608677183134E-7</v>
+        <v>-1.3067959153437273E-6</v>
       </c>
       <c r="F8">
-        <v>-3.8248840097788322E-4</v>
+        <v>-8.147106009014657E-4</v>
       </c>
       <c r="G8">
-        <v>-4.991908673410108E-4</v>
+        <v>-1.8447962727405035E-3</v>
       </c>
       <c r="H8">
-        <v>3.3031895542429074E-3</v>
+        <v>5.5415939115344443E-3</v>
       </c>
       <c r="I8">
-        <v>5.1746758109491127E-3</v>
+        <v>7.4316845415800803E-3</v>
       </c>
       <c r="J8">
-        <v>4.4020834318086132E-4</v>
+        <v>5.3784358319891633E-5</v>
       </c>
       <c r="K8">
-        <v>2.6932003765974591E-3</v>
+        <v>3.1873406689018808E-3</v>
       </c>
       <c r="L8">
-        <v>3.7774501973610658E-3</v>
+        <v>5.3080861455184298E-3</v>
       </c>
       <c r="M8">
-        <v>3.7998835483519676E-3</v>
+        <v>6.0771010436227613E-3</v>
       </c>
       <c r="N8">
-        <v>-2.5219215524252808E-4</v>
+        <v>-5.2892941473478474E-4</v>
       </c>
       <c r="O8">
-        <v>-1.3796015184592073E-4</v>
+        <v>2.8042670290388588E-4</v>
       </c>
       <c r="P8">
-        <v>-2.1201423218888309E-4</v>
+        <v>-1.4460380100188514E-4</v>
       </c>
       <c r="Q8">
-        <v>-6.9067191456350253E-5</v>
+        <v>-8.3485450364707879E-5</v>
       </c>
       <c r="R8">
-        <v>2.9181857478508856E-5</v>
+        <v>1.1475949648633461E-4</v>
       </c>
       <c r="S8">
-        <v>-4.6899092450789084E-4</v>
+        <v>-1.2760094487212347E-3</v>
       </c>
       <c r="T8">
-        <v>-1.4738017969970034E-4</v>
-      </c>
-      <c r="U8">
-        <v>-3.685556143498778E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
+        <v>-8.592742683163344E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="25">
-        <v>6.3801474439255758E-4</v>
+      <c r="B9">
+        <v>3.5769616167039116E-2</v>
       </c>
       <c r="C9">
-        <v>5.2432953270923274E-5</v>
+        <v>1.9996577603494675E-4</v>
       </c>
       <c r="D9">
-        <v>9.9448508742321247E-5</v>
+        <v>1.0366338802755934E-4</v>
       </c>
       <c r="E9">
-        <v>-1.052023043085295E-6</v>
+        <v>-7.9670026895101053E-7</v>
       </c>
       <c r="F9">
-        <v>-6.1084290097578975E-6</v>
+        <v>1.8619441540778355E-3</v>
       </c>
       <c r="G9">
-        <v>1.7984503590435377E-4</v>
+        <v>2.2307637882138564E-3</v>
       </c>
       <c r="H9">
-        <v>2.7781280182433989E-4</v>
+        <v>1.4807351369124221E-3</v>
       </c>
       <c r="I9">
-        <v>4.4020834318086132E-4</v>
+        <v>5.3784358319891633E-5</v>
       </c>
       <c r="J9">
-        <v>5.0584444733554638E-3</v>
+        <v>9.3100487869486933E-3</v>
       </c>
       <c r="K9">
-        <v>2.9540513335141517E-3</v>
+        <v>5.6929248491320505E-3</v>
       </c>
       <c r="L9">
-        <v>2.9949424131001231E-3</v>
+        <v>5.7130556620046836E-3</v>
       </c>
       <c r="M9">
-        <v>2.9655283668167604E-3</v>
+        <v>5.9944636699121945E-3</v>
       </c>
       <c r="N9">
-        <v>2.4538523073250904E-4</v>
+        <v>4.1844943811320456E-4</v>
       </c>
       <c r="O9">
-        <v>-1.1484099618000541E-4</v>
+        <v>1.5531217400553126E-3</v>
       </c>
       <c r="P9">
-        <v>7.1505888421571689E-5</v>
+        <v>5.1974690662834853E-5</v>
       </c>
       <c r="Q9">
-        <v>-2.186005451505226E-5</v>
+        <v>-9.7095857401441809E-4</v>
       </c>
       <c r="R9">
-        <v>-8.2093578560623443E-6</v>
+        <v>-1.796116370937893E-4</v>
       </c>
       <c r="S9">
-        <v>3.834430402477722E-5</v>
+        <v>7.701805963137155E-4</v>
       </c>
       <c r="T9">
-        <v>1.6041434895860485E-4</v>
-      </c>
-      <c r="U9">
-        <v>-5.1087248433580226E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A10" s="14" t="s">
+        <v>-7.3773887527030114E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="25">
-        <v>2.4786412508065347E-2</v>
+      <c r="B10">
+        <v>3.8106229585599352E-2</v>
       </c>
       <c r="C10">
-        <v>4.1024269281039988E-4</v>
+        <v>2.9751552969763015E-4</v>
       </c>
       <c r="D10">
-        <v>9.3426551069589805E-5</v>
+        <v>2.0805397281212831E-4</v>
       </c>
       <c r="E10">
-        <v>-8.6891559200697434E-7</v>
+        <v>-1.6205127887724578E-6</v>
       </c>
       <c r="F10">
-        <v>-2.094323869061155E-4</v>
+        <v>1.3965063238404558E-3</v>
       </c>
       <c r="G10">
-        <v>4.3036617516158351E-5</v>
+        <v>1.4104440563031469E-3</v>
       </c>
       <c r="H10">
-        <v>3.8299952970011091E-3</v>
+        <v>5.2732422650741129E-3</v>
       </c>
       <c r="I10">
-        <v>2.6932003765974591E-3</v>
+        <v>3.1873406689018808E-3</v>
       </c>
       <c r="J10">
-        <v>2.9540513335141517E-3</v>
+        <v>5.6929248491320505E-3</v>
       </c>
       <c r="K10">
-        <v>7.0922961559190655E-3</v>
+        <v>1.0549208267044087E-2</v>
       </c>
       <c r="L10">
-        <v>4.9480038895770425E-3</v>
+        <v>8.2866188271756205E-3</v>
       </c>
       <c r="M10">
-        <v>4.9865574559693777E-3</v>
+        <v>9.0756886692523638E-3</v>
       </c>
       <c r="N10">
-        <v>4.0865900717980625E-4</v>
+        <v>4.7405251752729227E-4</v>
       </c>
       <c r="O10">
-        <v>1.0235762083410632E-5</v>
+        <v>2.1661542361902462E-3</v>
       </c>
       <c r="P10">
-        <v>4.2351690542027226E-4</v>
+        <v>-2.0619608947031838E-4</v>
       </c>
       <c r="Q10">
-        <v>2.7597988009918405E-4</v>
+        <v>-1.1966821541551983E-3</v>
       </c>
       <c r="R10">
-        <v>2.1945049200659925E-5</v>
+        <v>-1.9558995899237713E-4</v>
       </c>
       <c r="S10">
-        <v>4.6118205992950854E-4</v>
+        <v>4.1501640030809249E-4</v>
       </c>
       <c r="T10">
-        <v>-1.5580521177432742E-4</v>
-      </c>
-      <c r="U10">
-        <v>-8.1820702395561263E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A11" s="15" t="s">
+        <v>-1.241450547843256E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="25">
-        <v>-6.1620942606628808E-2</v>
+      <c r="B11">
+        <v>1.8820203111344021E-2</v>
       </c>
       <c r="C11">
-        <v>2.7414811055102438E-4</v>
+        <v>-2.9177979542105101E-4</v>
       </c>
       <c r="D11">
-        <v>7.4750750814727828E-6</v>
+        <v>-1.1055136486285214E-5</v>
       </c>
       <c r="E11">
-        <v>-5.8357044489944793E-8</v>
+        <v>3.7445727839454096E-7</v>
       </c>
       <c r="F11">
-        <v>-6.5770750103680579E-4</v>
+        <v>1.5513213744295208E-3</v>
       </c>
       <c r="G11">
-        <v>7.8368079235106966E-5</v>
+        <v>1.1936431935963047E-3</v>
       </c>
       <c r="H11">
-        <v>3.7834760685082694E-3</v>
+        <v>7.105257148090822E-3</v>
       </c>
       <c r="I11">
-        <v>3.7774501973610658E-3</v>
+        <v>5.3080861455184298E-3</v>
       </c>
       <c r="J11">
-        <v>2.9949424131001231E-3</v>
+        <v>5.7130556620046836E-3</v>
       </c>
       <c r="K11">
-        <v>4.9480038895770425E-3</v>
+        <v>8.2866188271756205E-3</v>
       </c>
       <c r="L11">
-        <v>8.4533510154428046E-3</v>
+        <v>1.3578480439716659E-2</v>
       </c>
       <c r="M11">
-        <v>5.6968507207030821E-3</v>
+        <v>1.1400266877747405E-2</v>
       </c>
       <c r="N11">
-        <v>-1.9044519004257372E-4</v>
+        <v>6.4350485594438442E-4</v>
       </c>
       <c r="O11">
-        <v>8.410162126311219E-5</v>
+        <v>3.332664544750548E-3</v>
       </c>
       <c r="P11">
-        <v>1.1281810869378335E-4</v>
+        <v>-5.3155510186194484E-4</v>
       </c>
       <c r="Q11">
-        <v>-4.1065402144040055E-4</v>
+        <v>-1.3963484469953419E-3</v>
       </c>
       <c r="R11">
-        <v>1.0704930846318339E-4</v>
+        <v>-7.175216639173981E-5</v>
       </c>
       <c r="S11">
-        <v>-2.7822888421655554E-4</v>
+        <v>9.0241584827686992E-4</v>
       </c>
       <c r="T11">
-        <v>-4.3145386955002578E-4</v>
-      </c>
-      <c r="U11">
-        <v>-7.6764820956070909E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A12" s="16" t="s">
+        <v>-1.0816096040140584E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="25">
-        <v>-0.23733490968972007</v>
+      <c r="B12">
+        <v>-0.20729245419238287</v>
       </c>
       <c r="C12">
-        <v>-6.6563500081986623E-5</v>
+        <v>2.1171902245266101E-4</v>
       </c>
       <c r="D12">
-        <v>6.0544215738963635E-6</v>
+        <v>-9.2400379162897988E-5</v>
       </c>
       <c r="E12">
-        <v>-1.8073561290011378E-8</v>
+        <v>1.1793410995312413E-6</v>
       </c>
       <c r="F12">
-        <v>6.5674232673097982E-4</v>
+        <v>2.8476683861385728E-3</v>
       </c>
       <c r="G12">
-        <v>1.1816488399494E-3</v>
+        <v>3.4099513425915121E-3</v>
       </c>
       <c r="H12">
-        <v>3.7918788744625569E-3</v>
+        <v>7.4877982395360997E-3</v>
       </c>
       <c r="I12">
-        <v>3.7998835483519676E-3</v>
+        <v>6.0771010436227613E-3</v>
       </c>
       <c r="J12">
-        <v>2.9655283668167604E-3</v>
+        <v>5.9944636699121945E-3</v>
       </c>
       <c r="K12">
-        <v>4.9865574559693777E-3</v>
+        <v>9.0756886692523638E-3</v>
       </c>
       <c r="L12">
-        <v>5.6968507207030821E-3</v>
+        <v>1.1400266877747405E-2</v>
       </c>
       <c r="M12">
-        <v>1.0254939504559284E-2</v>
+        <v>1.7445742320793219E-2</v>
       </c>
       <c r="N12">
-        <v>8.2861916074307516E-4</v>
+        <v>1.4287844362998849E-3</v>
       </c>
       <c r="O12">
-        <v>3.3723323913331183E-4</v>
+        <v>3.0681753543927901E-3</v>
       </c>
       <c r="P12">
-        <v>9.1445506918534343E-4</v>
+        <v>-7.546836858702481E-5</v>
       </c>
       <c r="Q12">
-        <v>5.6898231351063845E-4</v>
+        <v>1.82046751185376E-4</v>
       </c>
       <c r="R12">
-        <v>-2.8329956452071792E-5</v>
+        <v>-5.8933168319049995E-5</v>
       </c>
       <c r="S12">
-        <v>-6.9094923631152856E-5</v>
+        <v>2.0450145324684473E-4</v>
       </c>
       <c r="T12">
-        <v>3.950119462962586E-4</v>
-      </c>
-      <c r="U12">
-        <v>-6.9698403962961293E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A13" s="17" t="s">
+        <v>-1.2345642577996694E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="25">
-        <v>-6.6682960772870198E-2</v>
+      <c r="B13">
+        <v>-0.21137282477383562</v>
       </c>
       <c r="C13">
-        <v>-3.6173457267957092E-4</v>
+        <v>1.6792533159027054E-4</v>
       </c>
       <c r="D13">
-        <v>-1.613455948566698E-4</v>
+        <v>-1.3884152318324261E-4</v>
       </c>
       <c r="E13">
-        <v>1.7971483341677467E-6</v>
+        <v>1.8024596597384412E-6</v>
       </c>
       <c r="F13">
-        <v>4.6928891927912558E-4</v>
+        <v>1.2628516551870098E-3</v>
       </c>
       <c r="G13">
-        <v>7.3345767495893712E-4</v>
+        <v>1.6574776638180989E-3</v>
       </c>
       <c r="H13">
-        <v>-4.1176120448207284E-4</v>
+        <v>-1.0158582408914974E-4</v>
       </c>
       <c r="I13">
-        <v>-2.5219215524252808E-4</v>
+        <v>-5.2892941473478474E-4</v>
       </c>
       <c r="J13">
-        <v>2.4538523073250904E-4</v>
+        <v>4.1844943811320456E-4</v>
       </c>
       <c r="K13">
-        <v>4.0865900717980625E-4</v>
+        <v>4.7405251752729227E-4</v>
       </c>
       <c r="L13">
-        <v>-1.9044519004257372E-4</v>
+        <v>6.4350485594438442E-4</v>
       </c>
       <c r="M13">
-        <v>8.2861916074307516E-4</v>
+        <v>1.4287844362998849E-3</v>
       </c>
       <c r="N13">
-        <v>6.7335347934631695E-3</v>
+        <v>6.8279757914291462E-3</v>
       </c>
       <c r="O13">
-        <v>3.1812909278894443E-3</v>
+        <v>3.8230087420125405E-3</v>
       </c>
       <c r="P13">
-        <v>3.1533662761079606E-3</v>
+        <v>3.0587759543058723E-3</v>
       </c>
       <c r="Q13">
-        <v>3.1838342308435586E-3</v>
+        <v>3.2389422085004355E-3</v>
       </c>
       <c r="R13">
-        <v>-1.5853808620587141E-5</v>
+        <v>-1.342885853051428E-4</v>
       </c>
       <c r="S13">
-        <v>-9.9972569458589545E-4</v>
+        <v>8.6147130719185197E-4</v>
       </c>
       <c r="T13">
-        <v>1.7658378578224755E-4</v>
-      </c>
-      <c r="U13">
-        <v>1.5570081549651419E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A14" s="18" t="s">
+        <v>-5.4344618842005609E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="25">
-        <v>-2.9342934621570088E-2</v>
+      <c r="B14">
+        <v>-6.5470798314513967E-2</v>
       </c>
       <c r="C14">
-        <v>1.0019547275450218E-5</v>
+        <v>-6.6383971844634077E-4</v>
       </c>
       <c r="D14">
-        <v>-5.2838722402124812E-5</v>
+        <v>-2.6588169724675652E-4</v>
       </c>
       <c r="E14">
-        <v>4.9783687837146108E-7</v>
+        <v>2.8894378140545946E-6</v>
       </c>
       <c r="F14">
-        <v>6.5435371642265762E-4</v>
+        <v>1.7452778991200975E-3</v>
       </c>
       <c r="G14">
-        <v>2.446418363308972E-4</v>
+        <v>9.495491834324403E-4</v>
       </c>
       <c r="H14">
-        <v>9.6194364760185651E-4</v>
+        <v>-1.9493040940848092E-3</v>
       </c>
       <c r="I14">
-        <v>-1.3796015184592073E-4</v>
+        <v>2.8042670290388588E-4</v>
       </c>
       <c r="J14">
-        <v>-1.1484099618000541E-4</v>
+        <v>1.5531217400553126E-3</v>
       </c>
       <c r="K14">
-        <v>1.0235762083410632E-5</v>
+        <v>2.1661542361902462E-3</v>
       </c>
       <c r="L14">
-        <v>8.410162126311219E-5</v>
+        <v>3.332664544750548E-3</v>
       </c>
       <c r="M14">
-        <v>3.3723323913331183E-4</v>
+        <v>3.0681753543927901E-3</v>
       </c>
       <c r="N14">
-        <v>3.1812909278894443E-3</v>
+        <v>3.8230087420125405E-3</v>
       </c>
       <c r="O14">
-        <v>7.6453821587282233E-3</v>
+        <v>1.2431552252368812E-2</v>
       </c>
       <c r="P14">
-        <v>3.1639708298427005E-3</v>
+        <v>3.0951081467115327E-3</v>
       </c>
       <c r="Q14">
-        <v>3.2706089776939765E-3</v>
+        <v>3.2900605473727062E-3</v>
       </c>
       <c r="R14">
-        <v>-7.3760668143682808E-5</v>
+        <v>-4.4638124408031676E-5</v>
       </c>
       <c r="S14">
-        <v>-7.2350623490558463E-4</v>
+        <v>2.7131022368467764E-3</v>
       </c>
       <c r="T14">
-        <v>2.9206570676786254E-4</v>
-      </c>
-      <c r="U14">
-        <v>-1.101443856693171E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A15" s="19" t="s">
+        <v>-4.6980876883268106E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="25">
-        <v>-1.5270915975767508E-2</v>
+      <c r="B15">
+        <v>-0.10793004989242458</v>
       </c>
       <c r="C15">
-        <v>-2.2551152827917818E-4</v>
+        <v>1.4827892130014485E-4</v>
       </c>
       <c r="D15">
-        <v>-1.2163936475016344E-4</v>
+        <v>-1.7171163662585268E-4</v>
       </c>
       <c r="E15">
-        <v>1.3646827261289905E-6</v>
+        <v>1.5359142673637339E-6</v>
       </c>
       <c r="F15">
-        <v>6.4205897937459166E-4</v>
+        <v>2.2592037170349449E-4</v>
       </c>
       <c r="G15">
-        <v>3.8885163647510565E-4</v>
+        <v>1.2379578923736121E-3</v>
       </c>
       <c r="H15">
-        <v>1.5979758605881057E-4</v>
+        <v>-1.6653665831099914E-3</v>
       </c>
       <c r="I15">
-        <v>-2.1201423218888309E-4</v>
+        <v>-1.4460380100188514E-4</v>
       </c>
       <c r="J15">
-        <v>7.1505888421571689E-5</v>
+        <v>5.1974690662834853E-5</v>
       </c>
       <c r="K15">
-        <v>4.2351690542027226E-4</v>
+        <v>-2.0619608947031838E-4</v>
       </c>
       <c r="L15">
-        <v>1.1281810869378335E-4</v>
+        <v>-5.3155510186194484E-4</v>
       </c>
       <c r="M15">
-        <v>9.1445506918534343E-4</v>
+        <v>-7.546836858702481E-5</v>
       </c>
       <c r="N15">
-        <v>3.1533662761079606E-3</v>
+        <v>3.0587759543058723E-3</v>
       </c>
       <c r="O15">
-        <v>3.1639708298427005E-3</v>
+        <v>3.0951081467115327E-3</v>
       </c>
       <c r="P15">
-        <v>6.1265798638291619E-3</v>
+        <v>7.0406869935320431E-3</v>
       </c>
       <c r="Q15">
-        <v>3.2111241965008873E-3</v>
+        <v>3.4106630666730893E-3</v>
       </c>
       <c r="R15">
-        <v>-2.2787272398849744E-5</v>
+        <v>-3.630839127780137E-5</v>
       </c>
       <c r="S15">
-        <v>-9.1227289582083071E-4</v>
+        <v>1.7739226137818266E-3</v>
       </c>
       <c r="T15">
-        <v>4.1833910480242324E-4</v>
-      </c>
-      <c r="U15">
-        <v>-8.056004747605879E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A16" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="25">
-        <v>-0.27317812704178646</v>
+        <v>1.185415452868357E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>-1.4835959876128364E-2</v>
       </c>
       <c r="C16">
-        <v>-4.8017637868189239E-4</v>
+        <v>-9.5053186783118391E-5</v>
       </c>
       <c r="D16">
-        <v>-6.7730808577116291E-5</v>
+        <v>-2.6502242576178798E-4</v>
       </c>
       <c r="E16">
-        <v>6.1802787958010054E-7</v>
+        <v>2.438407671292133E-6</v>
       </c>
       <c r="F16">
-        <v>3.7195079985539959E-4</v>
+        <v>-2.4121382828014358E-4</v>
       </c>
       <c r="G16">
-        <v>3.0349642241586129E-4</v>
+        <v>4.4738993930741003E-4</v>
       </c>
       <c r="H16">
-        <v>-2.7264415967617577E-4</v>
+        <v>-2.5592008068141183E-3</v>
       </c>
       <c r="I16">
-        <v>-6.9067191456350253E-5</v>
+        <v>-8.3485450364707879E-5</v>
       </c>
       <c r="J16">
-        <v>-2.186005451505226E-5</v>
+        <v>-9.7095857401441809E-4</v>
       </c>
       <c r="K16">
-        <v>2.7597988009918405E-4</v>
+        <v>-1.1966821541551983E-3</v>
       </c>
       <c r="L16">
-        <v>-4.1065402144040055E-4</v>
+        <v>-1.3963484469953419E-3</v>
       </c>
       <c r="M16">
-        <v>5.6898231351063845E-4</v>
+        <v>1.82046751185376E-4</v>
       </c>
       <c r="N16">
-        <v>3.1838342308435586E-3</v>
+        <v>3.2389422085004355E-3</v>
       </c>
       <c r="O16">
-        <v>3.2706089776939765E-3</v>
+        <v>3.2900605473727062E-3</v>
       </c>
       <c r="P16">
-        <v>3.2111241965008873E-3</v>
+        <v>3.4106630666730893E-3</v>
       </c>
       <c r="Q16">
-        <v>4.8186778229817699E-3</v>
+        <v>6.5669970986562522E-3</v>
       </c>
       <c r="R16">
-        <v>-6.9453635294529928E-5</v>
+        <v>5.2417268486885471E-5</v>
       </c>
       <c r="S16">
-        <v>-8.2539478785103074E-4</v>
+        <v>2.408071300868096E-5</v>
       </c>
       <c r="T16">
-        <v>5.9529090450204851E-4</v>
-      </c>
-      <c r="U16">
-        <v>-3.103308346269003E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A17" s="21" t="s">
+        <v>3.2451092601432402E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="25">
-        <v>6.8722464069618195E-3</v>
+      <c r="B17">
+        <v>-1.9921962809700509E-2</v>
       </c>
       <c r="C17">
-        <v>1.853372786523339E-5</v>
+        <v>-7.7364248326043373E-6</v>
       </c>
       <c r="D17">
-        <v>-9.9681143497016471E-6</v>
+        <v>-8.9100406146334498E-6</v>
       </c>
       <c r="E17">
-        <v>8.0177784533272014E-8</v>
+        <v>4.0657622425960691E-8</v>
       </c>
       <c r="F17">
-        <v>-8.4815273089669659E-5</v>
+        <v>-1.8265244248629289E-4</v>
       </c>
       <c r="G17">
-        <v>-4.5113381511268269E-5</v>
+        <v>-1.2569327006975626E-4</v>
       </c>
       <c r="H17">
-        <v>-1.8423688999543429E-4</v>
+        <v>-2.0138015442662744E-4</v>
       </c>
       <c r="I17">
-        <v>2.9181857478508856E-5</v>
+        <v>1.1475949648633461E-4</v>
       </c>
       <c r="J17">
-        <v>-8.2093578560623443E-6</v>
+        <v>-1.796116370937893E-4</v>
       </c>
       <c r="K17">
-        <v>2.1945049200659925E-5</v>
+        <v>-1.9558995899237713E-4</v>
       </c>
       <c r="L17">
-        <v>1.0704930846318339E-4</v>
+        <v>-7.175216639173981E-5</v>
       </c>
       <c r="M17">
-        <v>-2.8329956452071792E-5</v>
+        <v>-5.8933168319049995E-5</v>
       </c>
       <c r="N17">
-        <v>-1.5853808620587141E-5</v>
+        <v>-1.342885853051428E-4</v>
       </c>
       <c r="O17">
-        <v>-7.3760668143682808E-5</v>
+        <v>-4.4638124408031676E-5</v>
       </c>
       <c r="P17">
-        <v>-2.2787272398849744E-5</v>
+        <v>-3.630839127780137E-5</v>
       </c>
       <c r="Q17">
-        <v>-6.9453635294529928E-5</v>
+        <v>5.2417268486885471E-5</v>
       </c>
       <c r="R17">
-        <v>5.3222287681176752E-5</v>
+        <v>7.4359816795321995E-5</v>
       </c>
       <c r="S17">
-        <v>-2.1893922833498452E-4</v>
+        <v>-2.5404293637631227E-4</v>
       </c>
       <c r="T17">
-        <v>-2.6565572423556947E-4</v>
-      </c>
-      <c r="U17">
-        <v>-5.3857560272013868E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A18" s="22" t="s">
+        <v>-6.5750326306059125E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="25">
-        <v>0.10220996443345617</v>
+      <c r="B18">
+        <v>0.35725714638875988</v>
       </c>
       <c r="C18">
-        <v>-4.2006908702979669E-4</v>
+        <v>-6.5627161746209279E-4</v>
       </c>
       <c r="D18">
-        <v>1.4618694956358938E-4</v>
+        <v>-2.7610964267736214E-4</v>
       </c>
       <c r="E18">
-        <v>-1.3498100560635599E-6</v>
+        <v>2.809613806166921E-6</v>
       </c>
       <c r="F18">
-        <v>1.1365746901166136E-3</v>
+        <v>9.9638628181522083E-4</v>
       </c>
       <c r="G18">
-        <v>7.8465208508262947E-4</v>
+        <v>1.6293921218012769E-3</v>
       </c>
       <c r="H18">
-        <v>6.4353004501476819E-4</v>
+        <v>-2.2488595407094917E-3</v>
       </c>
       <c r="I18">
-        <v>-4.6899092450789084E-4</v>
+        <v>-1.2760094487212347E-3</v>
       </c>
       <c r="J18">
-        <v>3.834430402477722E-5</v>
+        <v>7.701805963137155E-4</v>
       </c>
       <c r="K18">
-        <v>4.6118205992950854E-4</v>
+        <v>4.1501640030809249E-4</v>
       </c>
       <c r="L18">
-        <v>-2.7822888421655554E-4</v>
+        <v>9.0241584827686992E-4</v>
       </c>
       <c r="M18">
-        <v>-6.9094923631152856E-5</v>
+        <v>2.0450145324684473E-4</v>
       </c>
       <c r="N18">
-        <v>-9.9972569458589545E-4</v>
+        <v>8.6147130719185197E-4</v>
       </c>
       <c r="O18">
-        <v>-7.2350623490558463E-4</v>
+        <v>2.7131022368467764E-3</v>
       </c>
       <c r="P18">
-        <v>-9.1227289582083071E-4</v>
+        <v>1.7739226137818266E-3</v>
       </c>
       <c r="Q18">
-        <v>-8.2539478785103074E-4</v>
+        <v>2.408071300868096E-5</v>
       </c>
       <c r="R18">
-        <v>-2.1893922833498452E-4</v>
+        <v>-2.5404293637631227E-4</v>
       </c>
       <c r="S18">
-        <v>7.5611992030198824E-3</v>
+        <v>9.7088365425418606E-3</v>
       </c>
       <c r="T18">
-        <v>1.7561362828376577E-3</v>
-      </c>
-      <c r="U18">
-        <v>-5.1247747935289224E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A19" s="23" t="s">
+        <v>8.0095189637951047E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="25">
-        <v>3.5055440316104192E-2</v>
+      <c r="B19">
+        <v>-3.0024156185576474</v>
       </c>
       <c r="C19">
-        <v>-4.6247554095766414E-5</v>
+        <v>-3.3823911252607811E-3</v>
       </c>
       <c r="D19">
-        <v>4.9821301341587774E-5</v>
+        <v>-4.0679282969788861E-3</v>
       </c>
       <c r="E19">
-        <v>-3.4963450553689366E-7</v>
+        <v>4.1336281359242754E-5</v>
       </c>
       <c r="F19">
-        <v>7.2621931669947042E-4</v>
+        <v>-5.3423360247093279E-3</v>
       </c>
       <c r="G19">
-        <v>4.2273139124957221E-4</v>
+        <v>-3.364111670384847E-3</v>
       </c>
       <c r="H19">
-        <v>8.7213267352028584E-4</v>
+        <v>-2.3850308120631505E-2</v>
       </c>
       <c r="I19">
-        <v>-1.4738017969970034E-4</v>
+        <v>-8.592742683163344E-3</v>
       </c>
       <c r="J19">
-        <v>1.6041434895860485E-4</v>
+        <v>-7.3773887527030114E-3</v>
       </c>
       <c r="K19">
-        <v>-1.5580521177432742E-4</v>
+        <v>-1.241450547843256E-2</v>
       </c>
       <c r="L19">
-        <v>-4.3145386955002578E-4</v>
+        <v>-1.0816096040140584E-2</v>
       </c>
       <c r="M19">
-        <v>3.950119462962586E-4</v>
+        <v>-1.2345642577996694E-2</v>
       </c>
       <c r="N19">
-        <v>1.7658378578224755E-4</v>
+        <v>-5.4344618842005609E-4</v>
       </c>
       <c r="O19">
-        <v>2.9206570676786254E-4</v>
+        <v>-4.6980876883268106E-4</v>
       </c>
       <c r="P19">
-        <v>4.1833910480242324E-4</v>
+        <v>1.185415452868357E-3</v>
       </c>
       <c r="Q19">
-        <v>5.9529090450204851E-4</v>
+        <v>3.2451092601432402E-3</v>
       </c>
       <c r="R19">
-        <v>-2.6565572423556947E-4</v>
+        <v>-6.5750326306059125E-4</v>
       </c>
       <c r="S19">
-        <v>1.7561362828376577E-3</v>
+        <v>8.0095189637951047E-3</v>
       </c>
       <c r="T19">
-        <v>6.5278870539961899E-3</v>
-      </c>
-      <c r="U19">
-        <v>1.4530746759693447E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A20" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="25">
-        <v>-3.0473730830758896</v>
-      </c>
-      <c r="C20">
-        <v>-1.3054835906601295E-4</v>
-      </c>
-      <c r="D20">
-        <v>-2.9049888381541748E-3</v>
-      </c>
-      <c r="E20">
-        <v>3.1840598958818253E-5</v>
-      </c>
-      <c r="F20">
-        <v>-5.0880645528419708E-3</v>
-      </c>
-      <c r="G20">
-        <v>-7.2088634383775654E-3</v>
-      </c>
-      <c r="H20">
-        <v>-1.4154796903401622E-2</v>
-      </c>
-      <c r="I20">
-        <v>-3.685556143498778E-3</v>
-      </c>
-      <c r="J20">
-        <v>-5.1087248433580226E-3</v>
-      </c>
-      <c r="K20">
-        <v>-8.1820702395561263E-3</v>
-      </c>
-      <c r="L20">
-        <v>-7.6764820956070909E-3</v>
-      </c>
-      <c r="M20">
-        <v>-6.9698403962961293E-3</v>
-      </c>
-      <c r="N20">
-        <v>1.5570081549651419E-4</v>
-      </c>
-      <c r="O20">
-        <v>-1.101443856693171E-3</v>
-      </c>
-      <c r="P20">
-        <v>-8.056004747605879E-4</v>
-      </c>
-      <c r="Q20">
-        <v>-3.103308346269003E-4</v>
-      </c>
-      <c r="R20">
-        <v>-5.3857560272013868E-4</v>
-      </c>
-      <c r="S20">
-        <v>-5.1247747935289224E-4</v>
-      </c>
-      <c r="T20">
-        <v>1.4530746759693447E-3</v>
-      </c>
-      <c r="U20">
-        <v>8.1580394481030868E-2</v>
-      </c>
+        <v>0.12064604664263855</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input/reg_leaveParentalHome.xlsx
+++ b/input/reg_leaveParentalHome.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E162B441-726B-4DC4-94FE-FEDB0284BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59318DA2-7DDB-4CA0-84C7-6F53D92EB71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,16 +108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -136,14 +127,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -162,11 +146,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,10 +495,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -529,7 +511,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B10" t="s">
@@ -543,8 +525,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="21.86328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -1724,10 +1709,6 @@
         <v>0.12064604664263855</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/input/reg_leaveParentalHome.xlsx
+++ b/input/reg_leaveParentalHome.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59318DA2-7DDB-4CA0-84C7-6F53D92EB71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF267F57-0036-4059-BFD5-C8703053DA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="IT_P1a" sheetId="3" r:id="rId2"/>
+    <sheet name="EL_P1a" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>Description:</t>
   </si>
@@ -89,19 +89,13 @@
     <t>Constant</t>
   </si>
   <si>
-    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
-  </si>
-  <si>
-    <t>ITF</t>
-  </si>
-  <si>
-    <t>ITG</t>
-  </si>
-  <si>
-    <t>ITH</t>
-  </si>
-  <si>
-    <t>ITI</t>
+    <t>Regions: EL3 = Attika (omitted), EL4 = Aegean Islands, EL7 = Central and Northern Greece</t>
+  </si>
+  <si>
+    <t>EL4</t>
+  </si>
+  <si>
+    <t>EL7</t>
   </si>
 </sst>
 </file>
@@ -484,9 +478,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,7 +488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -502,7 +496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -510,7 +504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -525,13 +519,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.86328125" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -578,1135 +572,909 @@
         <v>24</v>
       </c>
       <c r="P1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>-0.11665255243619094</v>
+        <v>-0.11393604583496905</v>
       </c>
       <c r="C2">
-        <v>3.1072053774141048E-3</v>
+        <v>7.7489549560344336E-3</v>
       </c>
       <c r="D2">
-        <v>5.3018779782759603E-5</v>
+        <v>-2.8215442766438926E-4</v>
       </c>
       <c r="E2">
-        <v>-3.8824340580041835E-7</v>
+        <v>3.2735681758690441E-6</v>
       </c>
       <c r="F2">
-        <v>1.9971902367906674E-4</v>
+        <v>-1.5347609326089836E-3</v>
       </c>
       <c r="G2">
-        <v>2.1342907149638491E-4</v>
+        <v>-2.6511799641848362E-3</v>
       </c>
       <c r="H2">
-        <v>6.5297588585840299E-4</v>
+        <v>2.7377980390724073E-3</v>
       </c>
       <c r="I2">
-        <v>2.7761284365612169E-4</v>
+        <v>1.2909561662087755E-3</v>
       </c>
       <c r="J2">
-        <v>1.9996577603494675E-4</v>
+        <v>1.1716383936679828E-3</v>
       </c>
       <c r="K2">
-        <v>2.9751552969763015E-4</v>
+        <v>6.6050970486672097E-4</v>
       </c>
       <c r="L2">
-        <v>-2.9177979542105101E-4</v>
+        <v>-7.0038899934689812E-4</v>
       </c>
       <c r="M2">
-        <v>2.1171902245266101E-4</v>
+        <v>-7.797239069494582E-4</v>
       </c>
       <c r="N2">
-        <v>1.6792533159027054E-4</v>
+        <v>-3.1516198267035871E-4</v>
       </c>
       <c r="O2">
-        <v>-6.6383971844634077E-4</v>
+        <v>-1.4751464401400835E-3</v>
       </c>
       <c r="P2">
-        <v>1.4827892130014485E-4</v>
+        <v>-1.0836520001444264E-4</v>
       </c>
       <c r="Q2">
-        <v>-9.5053186783118391E-5</v>
+        <v>-3.3466507370939758E-4</v>
       </c>
       <c r="R2">
-        <v>-7.7364248326043373E-6</v>
-      </c>
-      <c r="S2">
-        <v>-6.5627161746209279E-4</v>
-      </c>
-      <c r="T2">
-        <v>-3.3823911252607811E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+        <v>4.7173049938376722E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1.5959002028928627E-2</v>
+        <v>3.8482211591740756E-2</v>
       </c>
       <c r="C3">
-        <v>5.3018779782759603E-5</v>
+        <v>-2.8215442766438926E-4</v>
       </c>
       <c r="D3">
-        <v>1.9540707253068695E-4</v>
+        <v>4.4450884815583217E-4</v>
       </c>
       <c r="E3">
-        <v>-2.0384986038459955E-6</v>
+        <v>-4.7772235768318784E-6</v>
       </c>
       <c r="F3">
-        <v>-1.0346847977282412E-5</v>
+        <v>3.063953637296845E-4</v>
       </c>
       <c r="G3">
-        <v>-1.1762252871309431E-4</v>
+        <v>2.1407622493884587E-4</v>
       </c>
       <c r="H3">
-        <v>8.2841807353551419E-4</v>
+        <v>1.4834346174939046E-3</v>
       </c>
       <c r="I3">
-        <v>1.0388297784687966E-4</v>
+        <v>-4.5246932897106528E-4</v>
       </c>
       <c r="J3">
-        <v>1.0366338802755934E-4</v>
+        <v>1.7874113095826247E-4</v>
       </c>
       <c r="K3">
-        <v>2.0805397281212831E-4</v>
+        <v>-3.5551982551349295E-4</v>
       </c>
       <c r="L3">
-        <v>-1.1055136486285214E-5</v>
+        <v>-3.677064740092266E-4</v>
       </c>
       <c r="M3">
-        <v>-9.2400379162897988E-5</v>
+        <v>3.7845676564568151E-5</v>
       </c>
       <c r="N3">
-        <v>-1.3884152318324261E-4</v>
+        <v>-5.5699058760231082E-4</v>
       </c>
       <c r="O3">
-        <v>-2.6588169724675652E-4</v>
+        <v>-3.0856500019985425E-4</v>
       </c>
       <c r="P3">
-        <v>-1.7171163662585268E-4</v>
+        <v>2.0146364281990227E-5</v>
       </c>
       <c r="Q3">
-        <v>-2.6502242576178798E-4</v>
+        <v>1.3248957791701862E-3</v>
       </c>
       <c r="R3">
-        <v>-8.9100406146334498E-6</v>
-      </c>
-      <c r="S3">
-        <v>-2.7610964267736214E-4</v>
-      </c>
-      <c r="T3">
-        <v>-4.0679282969788861E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-9.6179073198524243E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4">
-        <v>2.9471462899883236E-4</v>
+        <v>1.3469942057824357E-4</v>
       </c>
       <c r="C4">
-        <v>-3.8824340580041835E-7</v>
+        <v>3.2735681758690441E-6</v>
       </c>
       <c r="D4">
-        <v>-2.0384986038459955E-6</v>
+        <v>-4.7772235768318784E-6</v>
       </c>
       <c r="E4">
-        <v>2.1896228208100444E-8</v>
+        <v>5.2347312925267616E-8</v>
       </c>
       <c r="F4">
-        <v>5.7084788703991417E-7</v>
+        <v>-3.5316569938889295E-6</v>
       </c>
       <c r="G4">
-        <v>1.316578382667805E-6</v>
+        <v>-2.8814730291068801E-6</v>
       </c>
       <c r="H4">
-        <v>-7.6566532169463463E-6</v>
+        <v>-1.4843144331407232E-5</v>
       </c>
       <c r="I4">
-        <v>-1.3067959153437273E-6</v>
+        <v>4.1138833152178749E-6</v>
       </c>
       <c r="J4">
-        <v>-7.9670026895101053E-7</v>
+        <v>-2.6245668130097566E-6</v>
       </c>
       <c r="K4">
-        <v>-1.6205127887724578E-6</v>
+        <v>3.2449317574659401E-6</v>
       </c>
       <c r="L4">
-        <v>3.7445727839454096E-7</v>
+        <v>3.3798366878817511E-6</v>
       </c>
       <c r="M4">
-        <v>1.1793410995312413E-6</v>
+        <v>-1.1135470244832068E-6</v>
       </c>
       <c r="N4">
-        <v>1.8024596597384412E-6</v>
+        <v>6.5681275104355146E-6</v>
       </c>
       <c r="O4">
-        <v>2.8894378140545946E-6</v>
+        <v>3.3824982748285859E-6</v>
       </c>
       <c r="P4">
-        <v>1.5359142673637339E-6</v>
+        <v>-2.1259597245707897E-7</v>
       </c>
       <c r="Q4">
-        <v>2.438407671292133E-6</v>
+        <v>-1.396862500921772E-5</v>
       </c>
       <c r="R4">
-        <v>4.0657622425960691E-8</v>
-      </c>
-      <c r="S4">
-        <v>2.809613806166921E-6</v>
-      </c>
-      <c r="T4">
-        <v>4.1336281359242754E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+        <v>1.019425455645008E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>8.4153018387571471E-2</v>
+        <v>0.29528297997668695</v>
       </c>
       <c r="C5">
-        <v>1.9971902367906674E-4</v>
+        <v>-1.5347609326089836E-3</v>
       </c>
       <c r="D5">
-        <v>-1.0346847977282412E-5</v>
+        <v>3.063953637296845E-4</v>
       </c>
       <c r="E5">
-        <v>5.7084788703991417E-7</v>
+        <v>-3.5316569938889295E-6</v>
       </c>
       <c r="F5">
-        <v>7.5342832814023807E-3</v>
+        <v>1.1643306771341531E-2</v>
       </c>
       <c r="G5">
-        <v>5.8743758350544382E-3</v>
+        <v>9.4658182134819274E-3</v>
       </c>
       <c r="H5">
-        <v>3.9301068216984368E-4</v>
+        <v>-1.9674634300151103E-3</v>
       </c>
       <c r="I5">
-        <v>-8.147106009014657E-4</v>
+        <v>-8.3568878316672571E-4</v>
       </c>
       <c r="J5">
-        <v>1.8619441540778355E-3</v>
+        <v>-2.9031770789665354E-3</v>
       </c>
       <c r="K5">
-        <v>1.3965063238404558E-3</v>
+        <v>3.7244393780023924E-4</v>
       </c>
       <c r="L5">
-        <v>1.5513213744295208E-3</v>
+        <v>-1.5993801741075208E-3</v>
       </c>
       <c r="M5">
-        <v>2.8476683861385728E-3</v>
+        <v>4.6356856804825484E-3</v>
       </c>
       <c r="N5">
-        <v>1.2628516551870098E-3</v>
+        <v>-4.6855425217653696E-3</v>
       </c>
       <c r="O5">
-        <v>1.7452778991200975E-3</v>
+        <v>-4.0870362733583226E-3</v>
       </c>
       <c r="P5">
-        <v>2.2592037170349449E-4</v>
+        <v>-1.0061650106994697E-4</v>
       </c>
       <c r="Q5">
-        <v>-2.4121382828014358E-4</v>
+        <v>1.1107556451979448E-2</v>
       </c>
       <c r="R5">
-        <v>-1.8265244248629289E-4</v>
-      </c>
-      <c r="S5">
-        <v>9.9638628181522083E-4</v>
-      </c>
-      <c r="T5">
-        <v>-5.3423360247093279E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-1.0361329999183677E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>5.2612775087819218E-2</v>
+        <v>0.33522745536722492</v>
       </c>
       <c r="C6">
-        <v>2.1342907149638491E-4</v>
+        <v>-2.6511799641848362E-3</v>
       </c>
       <c r="D6">
-        <v>-1.1762252871309431E-4</v>
+        <v>2.1407622493884587E-4</v>
       </c>
       <c r="E6">
-        <v>1.316578382667805E-6</v>
+        <v>-2.8814730291068801E-6</v>
       </c>
       <c r="F6">
-        <v>5.8743758350544382E-3</v>
+        <v>9.4658182134819274E-3</v>
       </c>
       <c r="G6">
-        <v>8.4708141667496767E-3</v>
+        <v>1.2760348948721176E-2</v>
       </c>
       <c r="H6">
-        <v>-2.7288204424195939E-4</v>
+        <v>-1.3264958638944434E-3</v>
       </c>
       <c r="I6">
-        <v>-1.8447962727405035E-3</v>
+        <v>-1.4265385680514706E-3</v>
       </c>
       <c r="J6">
-        <v>2.2307637882138564E-3</v>
+        <v>-3.007624038211568E-3</v>
       </c>
       <c r="K6">
-        <v>1.4104440563031469E-3</v>
+        <v>4.3046781176135087E-4</v>
       </c>
       <c r="L6">
-        <v>1.1936431935963047E-3</v>
+        <v>-2.9237219077708933E-4</v>
       </c>
       <c r="M6">
-        <v>3.4099513425915121E-3</v>
+        <v>4.2930882624070809E-3</v>
       </c>
       <c r="N6">
-        <v>1.6574776638180989E-3</v>
+        <v>-3.7078885158066538E-3</v>
       </c>
       <c r="O6">
-        <v>9.495491834324403E-4</v>
+        <v>-2.5905462388995824E-3</v>
       </c>
       <c r="P6">
-        <v>1.2379578923736121E-3</v>
+        <v>-5.5516971335677908E-5</v>
       </c>
       <c r="Q6">
-        <v>4.4738993930741003E-4</v>
+        <v>8.8369813352681039E-3</v>
       </c>
       <c r="R6">
-        <v>-1.2569327006975626E-4</v>
-      </c>
-      <c r="S6">
-        <v>1.6293921218012769E-3</v>
-      </c>
-      <c r="T6">
-        <v>-3.364111670384847E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-8.1509555860503971E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>-0.37650018517925599</v>
+        <v>0.15909748149908723</v>
       </c>
       <c r="C7">
-        <v>6.5297588585840299E-4</v>
+        <v>2.7377980390724073E-3</v>
       </c>
       <c r="D7">
-        <v>8.2841807353551419E-4</v>
+        <v>1.4834346174939046E-3</v>
       </c>
       <c r="E7">
-        <v>-7.6566532169463463E-6</v>
+        <v>-1.4843144331407232E-5</v>
       </c>
       <c r="F7">
-        <v>3.9301068216984368E-4</v>
+        <v>-1.9674634300151103E-3</v>
       </c>
       <c r="G7">
-        <v>-2.7288204424195939E-4</v>
+        <v>-1.3264958638944434E-3</v>
       </c>
       <c r="H7">
-        <v>3.4123409077127728E-2</v>
+        <v>4.8860315108496866E-2</v>
       </c>
       <c r="I7">
-        <v>5.5415939115344443E-3</v>
+        <v>3.1876840016164662E-3</v>
       </c>
       <c r="J7">
-        <v>1.4807351369124221E-3</v>
+        <v>-5.5637697395646479E-3</v>
       </c>
       <c r="K7">
-        <v>5.2732422650741129E-3</v>
+        <v>-5.0551596664057969E-3</v>
       </c>
       <c r="L7">
-        <v>7.105257148090822E-3</v>
+        <v>5.069226035869373E-4</v>
       </c>
       <c r="M7">
-        <v>7.4877982395360997E-3</v>
+        <v>-6.52298430825482E-4</v>
       </c>
       <c r="N7">
-        <v>-1.0158582408914974E-4</v>
+        <v>-3.2564127191624104E-4</v>
       </c>
       <c r="O7">
-        <v>-1.9493040940848092E-3</v>
+        <v>-2.9163271951140879E-5</v>
       </c>
       <c r="P7">
-        <v>-1.6653665831099914E-3</v>
+        <v>4.5171837507327608E-4</v>
       </c>
       <c r="Q7">
-        <v>-2.5592008068141183E-3</v>
+        <v>-1.2415343685808766E-3</v>
       </c>
       <c r="R7">
-        <v>-2.0138015442662744E-4</v>
-      </c>
-      <c r="S7">
-        <v>-2.2488595407094917E-3</v>
-      </c>
-      <c r="T7">
-        <v>-2.3850308120631505E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-4.3199896539518431E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8">
-        <v>-0.10710973726362788</v>
+        <v>-7.8941547075418325E-2</v>
       </c>
       <c r="C8">
-        <v>2.7761284365612169E-4</v>
+        <v>1.2909561662087755E-3</v>
       </c>
       <c r="D8">
-        <v>1.0388297784687966E-4</v>
+        <v>-4.5246932897106528E-4</v>
       </c>
       <c r="E8">
-        <v>-1.3067959153437273E-6</v>
+        <v>4.1138833152178749E-6</v>
       </c>
       <c r="F8">
-        <v>-8.147106009014657E-4</v>
+        <v>-8.3568878316672571E-4</v>
       </c>
       <c r="G8">
-        <v>-1.8447962727405035E-3</v>
+        <v>-1.4265385680514706E-3</v>
       </c>
       <c r="H8">
-        <v>5.5415939115344443E-3</v>
+        <v>3.1876840016164662E-3</v>
       </c>
       <c r="I8">
-        <v>7.4316845415800803E-3</v>
+        <v>1.1167540337020922E-2</v>
       </c>
       <c r="J8">
-        <v>5.3784358319891633E-5</v>
+        <v>1.2596638396637481E-3</v>
       </c>
       <c r="K8">
-        <v>3.1873406689018808E-3</v>
+        <v>5.8052617617816342E-3</v>
       </c>
       <c r="L8">
-        <v>5.3080861455184298E-3</v>
+        <v>9.2928091246304786E-3</v>
       </c>
       <c r="M8">
-        <v>6.0771010436227613E-3</v>
+        <v>9.0823053083061538E-3</v>
       </c>
       <c r="N8">
-        <v>-5.2892941473478474E-4</v>
+        <v>5.8211774263378785E-4</v>
       </c>
       <c r="O8">
-        <v>2.8042670290388588E-4</v>
+        <v>6.0372941565419239E-4</v>
       </c>
       <c r="P8">
-        <v>-1.4460380100188514E-4</v>
+        <v>-1.2967331318152614E-5</v>
       </c>
       <c r="Q8">
-        <v>-8.3485450364707879E-5</v>
+        <v>-1.8771328538540744E-3</v>
       </c>
       <c r="R8">
-        <v>1.1475949648633461E-4</v>
-      </c>
-      <c r="S8">
-        <v>-1.2760094487212347E-3</v>
-      </c>
-      <c r="T8">
-        <v>-8.592742683163344E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+        <v>9.5786317840187984E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9">
-        <v>3.5769616167039116E-2</v>
+        <v>-0.18103540029735291</v>
       </c>
       <c r="C9">
-        <v>1.9996577603494675E-4</v>
+        <v>1.1716383936679828E-3</v>
       </c>
       <c r="D9">
-        <v>1.0366338802755934E-4</v>
+        <v>1.7874113095826247E-4</v>
       </c>
       <c r="E9">
-        <v>-7.9670026895101053E-7</v>
+        <v>-2.6245668130097566E-6</v>
       </c>
       <c r="F9">
-        <v>1.8619441540778355E-3</v>
+        <v>-2.9031770789665354E-3</v>
       </c>
       <c r="G9">
-        <v>2.2307637882138564E-3</v>
+        <v>-3.007624038211568E-3</v>
       </c>
       <c r="H9">
-        <v>1.4807351369124221E-3</v>
+        <v>-5.5637697395646479E-3</v>
       </c>
       <c r="I9">
-        <v>5.3784358319891633E-5</v>
+        <v>1.2596638396637481E-3</v>
       </c>
       <c r="J9">
-        <v>9.3100487869486933E-3</v>
+        <v>1.2722713423747999E-2</v>
       </c>
       <c r="K9">
-        <v>5.6929248491320505E-3</v>
+        <v>4.7472628194184224E-3</v>
       </c>
       <c r="L9">
-        <v>5.7130556620046836E-3</v>
+        <v>4.9629549329938448E-3</v>
       </c>
       <c r="M9">
-        <v>5.9944636699121945E-3</v>
+        <v>3.8748416232493293E-3</v>
       </c>
       <c r="N9">
-        <v>4.1844943811320456E-4</v>
+        <v>-1.1001440045025259E-3</v>
       </c>
       <c r="O9">
-        <v>1.5531217400553126E-3</v>
+        <v>-5.8893333344320342E-4</v>
       </c>
       <c r="P9">
-        <v>5.1974690662834853E-5</v>
+        <v>-4.2537009316695543E-5</v>
       </c>
       <c r="Q9">
-        <v>-9.7095857401441809E-4</v>
+        <v>-5.0012867754745984E-4</v>
       </c>
       <c r="R9">
-        <v>-1.796116370937893E-4</v>
-      </c>
-      <c r="S9">
-        <v>7.701805963137155E-4</v>
-      </c>
-      <c r="T9">
-        <v>-7.3773887527030114E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-4.5658547075397883E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10">
-        <v>3.8106229585599352E-2</v>
+        <v>0.15800130562840087</v>
       </c>
       <c r="C10">
-        <v>2.9751552969763015E-4</v>
+        <v>6.6050970486672097E-4</v>
       </c>
       <c r="D10">
-        <v>2.0805397281212831E-4</v>
+        <v>-3.5551982551349295E-4</v>
       </c>
       <c r="E10">
-        <v>-1.6205127887724578E-6</v>
+        <v>3.2449317574659401E-6</v>
       </c>
       <c r="F10">
-        <v>1.3965063238404558E-3</v>
+        <v>3.7244393780023924E-4</v>
       </c>
       <c r="G10">
-        <v>1.4104440563031469E-3</v>
+        <v>4.3046781176135087E-4</v>
       </c>
       <c r="H10">
-        <v>5.2732422650741129E-3</v>
+        <v>-5.0551596664057969E-3</v>
       </c>
       <c r="I10">
-        <v>3.1873406689018808E-3</v>
+        <v>5.8052617617816342E-3</v>
       </c>
       <c r="J10">
-        <v>5.6929248491320505E-3</v>
+        <v>4.7472628194184224E-3</v>
       </c>
       <c r="K10">
-        <v>1.0549208267044087E-2</v>
+        <v>1.2925971515695635E-2</v>
       </c>
       <c r="L10">
-        <v>8.2866188271756205E-3</v>
+        <v>9.3444641604198617E-3</v>
       </c>
       <c r="M10">
-        <v>9.0756886692523638E-3</v>
+        <v>9.9358240094997701E-3</v>
       </c>
       <c r="N10">
-        <v>4.7405251752729227E-4</v>
+        <v>-9.5082125552503616E-4</v>
       </c>
       <c r="O10">
-        <v>2.1661542361902462E-3</v>
+        <v>-7.3377462973899486E-4</v>
       </c>
       <c r="P10">
-        <v>-2.0619608947031838E-4</v>
+        <v>-2.044245098543395E-4</v>
       </c>
       <c r="Q10">
-        <v>-1.1966821541551983E-3</v>
+        <v>7.7797411614440037E-4</v>
       </c>
       <c r="R10">
-        <v>-1.9558995899237713E-4</v>
-      </c>
-      <c r="S10">
-        <v>4.1501640030809249E-4</v>
-      </c>
-      <c r="T10">
-        <v>-1.241450547843256E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+        <v>2.1790331888380116E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11">
-        <v>1.8820203111344021E-2</v>
+        <v>-2.7655616126871854E-2</v>
       </c>
       <c r="C11">
-        <v>-2.9177979542105101E-4</v>
+        <v>-7.0038899934689812E-4</v>
       </c>
       <c r="D11">
-        <v>-1.1055136486285214E-5</v>
+        <v>-3.677064740092266E-4</v>
       </c>
       <c r="E11">
-        <v>3.7445727839454096E-7</v>
+        <v>3.3798366878817511E-6</v>
       </c>
       <c r="F11">
-        <v>1.5513213744295208E-3</v>
+        <v>-1.5993801741075208E-3</v>
       </c>
       <c r="G11">
-        <v>1.1936431935963047E-3</v>
+        <v>-2.9237219077708933E-4</v>
       </c>
       <c r="H11">
-        <v>7.105257148090822E-3</v>
+        <v>5.069226035869373E-4</v>
       </c>
       <c r="I11">
-        <v>5.3080861455184298E-3</v>
+        <v>9.2928091246304786E-3</v>
       </c>
       <c r="J11">
-        <v>5.7130556620046836E-3</v>
+        <v>4.9629549329938448E-3</v>
       </c>
       <c r="K11">
-        <v>8.2866188271756205E-3</v>
+        <v>9.3444641604198617E-3</v>
       </c>
       <c r="L11">
-        <v>1.3578480439716659E-2</v>
+        <v>1.733589474764894E-2</v>
       </c>
       <c r="M11">
-        <v>1.1400266877747405E-2</v>
+        <v>1.2333668584484446E-2</v>
       </c>
       <c r="N11">
-        <v>6.4350485594438442E-4</v>
+        <v>2.4028295164946201E-4</v>
       </c>
       <c r="O11">
-        <v>3.332664544750548E-3</v>
+        <v>1.5327164508533719E-3</v>
       </c>
       <c r="P11">
-        <v>-5.3155510186194484E-4</v>
+        <v>-4.7491405347423687E-5</v>
       </c>
       <c r="Q11">
-        <v>-1.3963484469953419E-3</v>
+        <v>-2.3568185003525477E-3</v>
       </c>
       <c r="R11">
-        <v>-7.175216639173981E-5</v>
-      </c>
-      <c r="S11">
-        <v>9.0241584827686992E-4</v>
-      </c>
-      <c r="T11">
-        <v>-1.0816096040140584E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-2.6313988096598809E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12">
-        <v>-0.20729245419238287</v>
+        <v>0.19538918029121674</v>
       </c>
       <c r="C12">
-        <v>2.1171902245266101E-4</v>
+        <v>-7.797239069494582E-4</v>
       </c>
       <c r="D12">
-        <v>-9.2400379162897988E-5</v>
+        <v>3.7845676564568151E-5</v>
       </c>
       <c r="E12">
-        <v>1.1793410995312413E-6</v>
+        <v>-1.1135470244832068E-6</v>
       </c>
       <c r="F12">
-        <v>2.8476683861385728E-3</v>
+        <v>4.6356856804825484E-3</v>
       </c>
       <c r="G12">
-        <v>3.4099513425915121E-3</v>
+        <v>4.2930882624070809E-3</v>
       </c>
       <c r="H12">
-        <v>7.4877982395360997E-3</v>
+        <v>-6.52298430825482E-4</v>
       </c>
       <c r="I12">
-        <v>6.0771010436227613E-3</v>
+        <v>9.0823053083061538E-3</v>
       </c>
       <c r="J12">
-        <v>5.9944636699121945E-3</v>
+        <v>3.8748416232493293E-3</v>
       </c>
       <c r="K12">
-        <v>9.0756886692523638E-3</v>
+        <v>9.9358240094997701E-3</v>
       </c>
       <c r="L12">
-        <v>1.1400266877747405E-2</v>
+        <v>1.2333668584484446E-2</v>
       </c>
       <c r="M12">
-        <v>1.7445742320793219E-2</v>
+        <v>2.043503819425033E-2</v>
       </c>
       <c r="N12">
-        <v>1.4287844362998849E-3</v>
+        <v>-5.1735723901076211E-3</v>
       </c>
       <c r="O12">
-        <v>3.0681753543927901E-3</v>
+        <v>-3.2199563110128435E-3</v>
       </c>
       <c r="P12">
-        <v>-7.546836858702481E-5</v>
+        <v>-1.108460694897777E-4</v>
       </c>
       <c r="Q12">
-        <v>1.82046751185376E-4</v>
+        <v>1.042019450191789E-2</v>
       </c>
       <c r="R12">
-        <v>-5.8933168319049995E-5</v>
-      </c>
-      <c r="S12">
-        <v>2.0450145324684473E-4</v>
-      </c>
-      <c r="T12">
-        <v>-1.2345642577996694E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-1.3117976257928422E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13">
-        <v>-0.21137282477383562</v>
+        <v>-0.44051975834799939</v>
       </c>
       <c r="C13">
-        <v>1.6792533159027054E-4</v>
+        <v>-3.1516198267035871E-4</v>
       </c>
       <c r="D13">
-        <v>-1.3884152318324261E-4</v>
+        <v>-5.5699058760231082E-4</v>
       </c>
       <c r="E13">
-        <v>1.8024596597384412E-6</v>
+        <v>6.5681275104355146E-6</v>
       </c>
       <c r="F13">
-        <v>1.2628516551870098E-3</v>
+        <v>-4.6855425217653696E-3</v>
       </c>
       <c r="G13">
-        <v>1.6574776638180989E-3</v>
+        <v>-3.7078885158066538E-3</v>
       </c>
       <c r="H13">
-        <v>-1.0158582408914974E-4</v>
+        <v>-3.2564127191624104E-4</v>
       </c>
       <c r="I13">
-        <v>-5.2892941473478474E-4</v>
+        <v>5.8211774263378785E-4</v>
       </c>
       <c r="J13">
-        <v>4.1844943811320456E-4</v>
+        <v>-1.1001440045025259E-3</v>
       </c>
       <c r="K13">
-        <v>4.7405251752729227E-4</v>
+        <v>-9.5082125552503616E-4</v>
       </c>
       <c r="L13">
-        <v>6.4350485594438442E-4</v>
+        <v>2.4028295164946201E-4</v>
       </c>
       <c r="M13">
-        <v>1.4287844362998849E-3</v>
+        <v>-5.1735723901076211E-3</v>
       </c>
       <c r="N13">
-        <v>6.8279757914291462E-3</v>
+        <v>1.5176393094593857E-2</v>
       </c>
       <c r="O13">
-        <v>3.8230087420125405E-3</v>
+        <v>6.0785809689776118E-3</v>
       </c>
       <c r="P13">
-        <v>3.0587759543058723E-3</v>
+        <v>2.1641988894057277E-5</v>
       </c>
       <c r="Q13">
-        <v>3.2389422085004355E-3</v>
+        <v>-1.0732736406725899E-2</v>
       </c>
       <c r="R13">
-        <v>-1.342885853051428E-4</v>
-      </c>
-      <c r="S13">
-        <v>8.6147130719185197E-4</v>
-      </c>
-      <c r="T13">
-        <v>-5.4344618842005609E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+        <v>1.1057574606980491E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
       <c r="B14">
-        <v>-6.5470798314513967E-2</v>
+        <v>-0.30777237429387388</v>
       </c>
       <c r="C14">
-        <v>-6.6383971844634077E-4</v>
+        <v>-1.4751464401400835E-3</v>
       </c>
       <c r="D14">
-        <v>-2.6588169724675652E-4</v>
+        <v>-3.0856500019985425E-4</v>
       </c>
       <c r="E14">
-        <v>2.8894378140545946E-6</v>
+        <v>3.3824982748285859E-6</v>
       </c>
       <c r="F14">
-        <v>1.7452778991200975E-3</v>
+        <v>-4.0870362733583226E-3</v>
       </c>
       <c r="G14">
-        <v>9.495491834324403E-4</v>
+        <v>-2.5905462388995824E-3</v>
       </c>
       <c r="H14">
-        <v>-1.9493040940848092E-3</v>
+        <v>-2.9163271951140879E-5</v>
       </c>
       <c r="I14">
-        <v>2.8042670290388588E-4</v>
+        <v>6.0372941565419239E-4</v>
       </c>
       <c r="J14">
-        <v>1.5531217400553126E-3</v>
+        <v>-5.8893333344320342E-4</v>
       </c>
       <c r="K14">
-        <v>2.1661542361902462E-3</v>
+        <v>-7.3377462973899486E-4</v>
       </c>
       <c r="L14">
-        <v>3.332664544750548E-3</v>
+        <v>1.5327164508533719E-3</v>
       </c>
       <c r="M14">
-        <v>3.0681753543927901E-3</v>
+        <v>-3.2199563110128435E-3</v>
       </c>
       <c r="N14">
-        <v>3.8230087420125405E-3</v>
+        <v>6.0785809689776118E-3</v>
       </c>
       <c r="O14">
-        <v>1.2431552252368812E-2</v>
+        <v>7.5764183133913837E-3</v>
       </c>
       <c r="P14">
-        <v>3.0951081467115327E-3</v>
+        <v>1.7225648005951964E-4</v>
       </c>
       <c r="Q14">
-        <v>3.2900605473727062E-3</v>
+        <v>-9.8433482570649631E-3</v>
       </c>
       <c r="R14">
-        <v>-4.4638124408031676E-5</v>
-      </c>
-      <c r="S14">
-        <v>2.7131022368467764E-3</v>
-      </c>
-      <c r="T14">
-        <v>-4.6980876883268106E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+        <v>3.3621391847473399E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>-0.10793004989242458</v>
+        <v>-1.0254622771733349E-2</v>
       </c>
       <c r="C15">
-        <v>1.4827892130014485E-4</v>
+        <v>-1.0836520001444264E-4</v>
       </c>
       <c r="D15">
-        <v>-1.7171163662585268E-4</v>
+        <v>2.0146364281990227E-5</v>
       </c>
       <c r="E15">
-        <v>1.5359142673637339E-6</v>
+        <v>-2.1259597245707897E-7</v>
       </c>
       <c r="F15">
-        <v>2.2592037170349449E-4</v>
+        <v>-1.0061650106994697E-4</v>
       </c>
       <c r="G15">
-        <v>1.2379578923736121E-3</v>
+        <v>-5.5516971335677908E-5</v>
       </c>
       <c r="H15">
-        <v>-1.6653665831099914E-3</v>
+        <v>4.5171837507327608E-4</v>
       </c>
       <c r="I15">
-        <v>-1.4460380100188514E-4</v>
+        <v>-1.2967331318152614E-5</v>
       </c>
       <c r="J15">
-        <v>5.1974690662834853E-5</v>
+        <v>-4.2537009316695543E-5</v>
       </c>
       <c r="K15">
-        <v>-2.0619608947031838E-4</v>
+        <v>-2.044245098543395E-4</v>
       </c>
       <c r="L15">
-        <v>-5.3155510186194484E-4</v>
+        <v>-4.7491405347423687E-5</v>
       </c>
       <c r="M15">
-        <v>-7.546836858702481E-5</v>
+        <v>-1.108460694897777E-4</v>
       </c>
       <c r="N15">
-        <v>3.0587759543058723E-3</v>
+        <v>2.1641988894057277E-5</v>
       </c>
       <c r="O15">
-        <v>3.0951081467115327E-3</v>
+        <v>1.7225648005951964E-4</v>
       </c>
       <c r="P15">
-        <v>7.0406869935320431E-3</v>
+        <v>8.9711565213435512E-5</v>
       </c>
       <c r="Q15">
-        <v>3.4106630666730893E-3</v>
+        <v>-3.207359265305753E-4</v>
       </c>
       <c r="R15">
-        <v>-3.630839127780137E-5</v>
-      </c>
-      <c r="S15">
-        <v>1.7739226137818266E-3</v>
-      </c>
-      <c r="T15">
-        <v>1.185415452868357E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-1.8901917911212079E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>-1.4835959876128364E-2</v>
+        <v>0.53874062547355428</v>
       </c>
       <c r="C16">
-        <v>-9.5053186783118391E-5</v>
+        <v>-3.3466507370939758E-4</v>
       </c>
       <c r="D16">
-        <v>-2.6502242576178798E-4</v>
+        <v>1.3248957791701862E-3</v>
       </c>
       <c r="E16">
-        <v>2.438407671292133E-6</v>
+        <v>-1.396862500921772E-5</v>
       </c>
       <c r="F16">
-        <v>-2.4121382828014358E-4</v>
+        <v>1.1107556451979448E-2</v>
       </c>
       <c r="G16">
-        <v>4.4738993930741003E-4</v>
+        <v>8.8369813352681039E-3</v>
       </c>
       <c r="H16">
-        <v>-2.5592008068141183E-3</v>
+        <v>-1.2415343685808766E-3</v>
       </c>
       <c r="I16">
-        <v>-8.3485450364707879E-5</v>
+        <v>-1.8771328538540744E-3</v>
       </c>
       <c r="J16">
-        <v>-9.7095857401441809E-4</v>
+        <v>-5.0012867754745984E-4</v>
       </c>
       <c r="K16">
-        <v>-1.1966821541551983E-3</v>
+        <v>7.7797411614440037E-4</v>
       </c>
       <c r="L16">
-        <v>-1.3963484469953419E-3</v>
+        <v>-2.3568185003525477E-3</v>
       </c>
       <c r="M16">
-        <v>1.82046751185376E-4</v>
+        <v>1.042019450191789E-2</v>
       </c>
       <c r="N16">
-        <v>3.2389422085004355E-3</v>
+        <v>-1.0732736406725899E-2</v>
       </c>
       <c r="O16">
-        <v>3.2900605473727062E-3</v>
+        <v>-9.8433482570649631E-3</v>
       </c>
       <c r="P16">
-        <v>3.4106630666730893E-3</v>
+        <v>-3.207359265305753E-4</v>
       </c>
       <c r="Q16">
-        <v>6.5669970986562522E-3</v>
+        <v>2.9530938273033908E-2</v>
       </c>
       <c r="R16">
-        <v>5.2417268486885471E-5</v>
-      </c>
-      <c r="S16">
-        <v>2.408071300868096E-5</v>
-      </c>
-      <c r="T16">
-        <v>3.2451092601432402E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
+        <v>-2.8884876664336735E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>-1.9921962809700509E-2</v>
+        <v>-3.973096889765916</v>
       </c>
       <c r="C17">
-        <v>-7.7364248326043373E-6</v>
+        <v>4.7173049938376722E-3</v>
       </c>
       <c r="D17">
-        <v>-8.9100406146334498E-6</v>
+        <v>-9.6179073198524243E-3</v>
       </c>
       <c r="E17">
-        <v>4.0657622425960691E-8</v>
+        <v>1.019425455645008E-4</v>
       </c>
       <c r="F17">
-        <v>-1.8265244248629289E-4</v>
+        <v>-1.0361329999183677E-2</v>
       </c>
       <c r="G17">
-        <v>-1.2569327006975626E-4</v>
+        <v>-8.1509555860503971E-3</v>
       </c>
       <c r="H17">
-        <v>-2.0138015442662744E-4</v>
+        <v>-4.3199896539518431E-2</v>
       </c>
       <c r="I17">
-        <v>1.1475949648633461E-4</v>
+        <v>9.5786317840187984E-4</v>
       </c>
       <c r="J17">
-        <v>-1.796116370937893E-4</v>
+        <v>-4.5658547075397883E-3</v>
       </c>
       <c r="K17">
-        <v>-1.9558995899237713E-4</v>
+        <v>2.1790331888380116E-3</v>
       </c>
       <c r="L17">
-        <v>-7.175216639173981E-5</v>
+        <v>-2.6313988096598809E-3</v>
       </c>
       <c r="M17">
-        <v>-5.8933168319049995E-5</v>
+        <v>-1.3117976257928422E-2</v>
       </c>
       <c r="N17">
-        <v>-1.342885853051428E-4</v>
+        <v>1.1057574606980491E-2</v>
       </c>
       <c r="O17">
-        <v>-4.4638124408031676E-5</v>
+        <v>3.3621391847473399E-3</v>
       </c>
       <c r="P17">
-        <v>-3.630839127780137E-5</v>
+        <v>-1.8901917911212079E-3</v>
       </c>
       <c r="Q17">
-        <v>5.2417268486885471E-5</v>
+        <v>-2.8884876664336735E-2</v>
       </c>
       <c r="R17">
-        <v>7.4359816795321995E-5</v>
-      </c>
-      <c r="S17">
-        <v>-2.5404293637631227E-4</v>
-      </c>
-      <c r="T17">
-        <v>-6.5750326306059125E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
-        <v>0.35725714638875988</v>
-      </c>
-      <c r="C18">
-        <v>-6.5627161746209279E-4</v>
-      </c>
-      <c r="D18">
-        <v>-2.7610964267736214E-4</v>
-      </c>
-      <c r="E18">
-        <v>2.809613806166921E-6</v>
-      </c>
-      <c r="F18">
-        <v>9.9638628181522083E-4</v>
-      </c>
-      <c r="G18">
-        <v>1.6293921218012769E-3</v>
-      </c>
-      <c r="H18">
-        <v>-2.2488595407094917E-3</v>
-      </c>
-      <c r="I18">
-        <v>-1.2760094487212347E-3</v>
-      </c>
-      <c r="J18">
-        <v>7.701805963137155E-4</v>
-      </c>
-      <c r="K18">
-        <v>4.1501640030809249E-4</v>
-      </c>
-      <c r="L18">
-        <v>9.0241584827686992E-4</v>
-      </c>
-      <c r="M18">
-        <v>2.0450145324684473E-4</v>
-      </c>
-      <c r="N18">
-        <v>8.6147130719185197E-4</v>
-      </c>
-      <c r="O18">
-        <v>2.7131022368467764E-3</v>
-      </c>
-      <c r="P18">
-        <v>1.7739226137818266E-3</v>
-      </c>
-      <c r="Q18">
-        <v>2.408071300868096E-5</v>
-      </c>
-      <c r="R18">
-        <v>-2.5404293637631227E-4</v>
-      </c>
-      <c r="S18">
-        <v>9.7088365425418606E-3</v>
-      </c>
-      <c r="T18">
-        <v>8.0095189637951047E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
-        <v>-3.0024156185576474</v>
-      </c>
-      <c r="C19">
-        <v>-3.3823911252607811E-3</v>
-      </c>
-      <c r="D19">
-        <v>-4.0679282969788861E-3</v>
-      </c>
-      <c r="E19">
-        <v>4.1336281359242754E-5</v>
-      </c>
-      <c r="F19">
-        <v>-5.3423360247093279E-3</v>
-      </c>
-      <c r="G19">
-        <v>-3.364111670384847E-3</v>
-      </c>
-      <c r="H19">
-        <v>-2.3850308120631505E-2</v>
-      </c>
-      <c r="I19">
-        <v>-8.592742683163344E-3</v>
-      </c>
-      <c r="J19">
-        <v>-7.3773887527030114E-3</v>
-      </c>
-      <c r="K19">
-        <v>-1.241450547843256E-2</v>
-      </c>
-      <c r="L19">
-        <v>-1.0816096040140584E-2</v>
-      </c>
-      <c r="M19">
-        <v>-1.2345642577996694E-2</v>
-      </c>
-      <c r="N19">
-        <v>-5.4344618842005609E-4</v>
-      </c>
-      <c r="O19">
-        <v>-4.6980876883268106E-4</v>
-      </c>
-      <c r="P19">
-        <v>1.185415452868357E-3</v>
-      </c>
-      <c r="Q19">
-        <v>3.2451092601432402E-3</v>
-      </c>
-      <c r="R19">
-        <v>-6.5750326306059125E-4</v>
-      </c>
-      <c r="S19">
-        <v>8.0095189637951047E-3</v>
-      </c>
-      <c r="T19">
-        <v>0.12064604664263855</v>
+        <v>0.254431725689232</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_leaveParentalHome.xlsx
+++ b/input/reg_leaveParentalHome.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="66">
   <si>
     <t>c1</t>
   </si>
@@ -218,7 +218,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -262,6 +262,66 @@
       <b/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -271,7 +331,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -307,11 +367,53 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -326,6 +428,30 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -441,94 +567,94 @@
         <v>31</v>
       </c>
       <c r="B2">
-        <v>-0.28298153112230012</v>
+        <v>-0.24006478690966535</v>
       </c>
       <c r="C2">
-        <v>0.00089110776221820688</v>
+        <v>0.00061781580422100996</v>
       </c>
       <c r="D2">
-        <v>-2.6544044504785201e-005</v>
+        <v>-9.1381269966133271e-006</v>
       </c>
       <c r="E2">
-        <v>3.1465375280620552e-007</v>
+        <v>1.1991167531721498e-007</v>
       </c>
       <c r="F2">
-        <v>-0.00011904561676683809</v>
+        <v>-7.2453395176093135e-005</v>
       </c>
       <c r="G2">
-        <v>-0.00014292808597463319</v>
+        <v>-0.00011268104369426102</v>
       </c>
       <c r="H2">
-        <v>9.6861969303827842e-005</v>
+        <v>3.1397596436123429e-005</v>
       </c>
       <c r="I2">
-        <v>2.408016643033453e-005</v>
+        <v>-6.052830878747174e-006</v>
       </c>
       <c r="J2">
-        <v>0.00013622279815488845</v>
+        <v>7.3152197757537878e-005</v>
       </c>
       <c r="K2">
-        <v>0.00014200205900610137</v>
+        <v>5.7163462538164868e-005</v>
       </c>
       <c r="L2">
-        <v>6.0594948023574949e-005</v>
+        <v>-7.919247390734002e-006</v>
       </c>
       <c r="M2">
-        <v>5.2021065018809095e-006</v>
+        <v>-5.4022410730413241e-005</v>
       </c>
       <c r="N2">
-        <v>-5.8460765848974088e-005</v>
+        <v>-8.7401251444302363e-005</v>
       </c>
       <c r="O2">
-        <v>3.0247009458892162e-005</v>
+        <v>-1.377023523726338e-005</v>
       </c>
       <c r="P2">
-        <v>-3.9283592258444852e-006</v>
+        <v>-4.1504336383314901e-005</v>
       </c>
       <c r="Q2">
-        <v>-6.2379929981665888e-005</v>
+        <v>-6.873988698360891e-005</v>
       </c>
       <c r="R2">
-        <v>3.371067614290426e-005</v>
+        <v>1.7099121102368571e-005</v>
       </c>
       <c r="S2">
-        <v>-7.9844343404750182e-005</v>
+        <v>-3.0328507822277215e-005</v>
       </c>
       <c r="T2">
-        <v>5.0363820741853534e-005</v>
+        <v>8.4534489213047948e-007</v>
       </c>
       <c r="U2">
-        <v>0.00011181013736597909</v>
+        <v>5.0149445914071235e-006</v>
       </c>
       <c r="V2">
-        <v>1.402536366660787e-006</v>
+        <v>-5.0511909620676163e-005</v>
       </c>
       <c r="W2">
-        <v>0.00010647482951627222</v>
+        <v>3.4798197587393009e-005</v>
       </c>
       <c r="X2">
-        <v>3.4137192050686459e-005</v>
+        <v>1.7216175381888854e-006</v>
       </c>
       <c r="Y2">
-        <v>-4.9311556265419157e-006</v>
+        <v>4.3510916668879415e-007</v>
       </c>
       <c r="Z2">
-        <v>-1.0787907954078364e-005</v>
+        <v>2.5992361577565189e-005</v>
       </c>
       <c r="AA2">
-        <v>2.2157136138186527e-005</v>
+        <v>-1.1311925385792038e-005</v>
       </c>
       <c r="AB2">
-        <v>5.4924177902638074e-005</v>
+        <v>2.7035304457427613e-006</v>
       </c>
       <c r="AC2">
-        <v>-3.6713838358304692e-005</v>
+        <v>-4.7155783239187292e-005</v>
       </c>
       <c r="AD2">
-        <v>-2.4540986930661353e-005</v>
+        <v>-1.6650590019150208e-005</v>
       </c>
       <c r="AE2">
-        <v>8.3440410491761433e-005</v>
+        <v>-0.00011185759157943779</v>
       </c>
     </row>
     <row r="3">
@@ -536,94 +662,94 @@
         <v>32</v>
       </c>
       <c r="B3">
-        <v>-0.02160945461231507</v>
+        <v>0.052990591331900233</v>
       </c>
       <c r="C3">
-        <v>-2.6544044504785201e-005</v>
+        <v>-9.1381269966133271e-006</v>
       </c>
       <c r="D3">
-        <v>8.5681188587438805e-005</v>
+        <v>8.6423195813550537e-005</v>
       </c>
       <c r="E3">
-        <v>-1.1154943446824942e-006</v>
+        <v>-1.1688157493505158e-006</v>
       </c>
       <c r="F3">
-        <v>6.3744542601724949e-005</v>
+        <v>5.6817761465568763e-005</v>
       </c>
       <c r="G3">
-        <v>5.5397598361516881e-005</v>
+        <v>5.3654817486314493e-005</v>
       </c>
       <c r="H3">
-        <v>0.00017549860209374393</v>
+        <v>0.00013537064506818444</v>
       </c>
       <c r="I3">
-        <v>0.00012426242944792406</v>
+        <v>8.9159833928564554e-005</v>
       </c>
       <c r="J3">
-        <v>0.00011385949208549752</v>
+        <v>8.6378940490587649e-005</v>
       </c>
       <c r="K3">
-        <v>0.00012552472889933991</v>
+        <v>8.8679852354744954e-005</v>
       </c>
       <c r="L3">
-        <v>8.5027124691176978e-005</v>
+        <v>5.2938173375396939e-005</v>
       </c>
       <c r="M3">
-        <v>9.6174226206568916e-005</v>
+        <v>6.402627187999199e-005</v>
       </c>
       <c r="N3">
-        <v>-1.2476099615596134e-005</v>
+        <v>-2.5070176931737465e-005</v>
       </c>
       <c r="O3">
-        <v>1.6043452185874325e-005</v>
+        <v>5.9334130899898666e-006</v>
       </c>
       <c r="P3">
-        <v>-6.0676156975564911e-006</v>
+        <v>-2.328736363807829e-005</v>
       </c>
       <c r="Q3">
-        <v>-1.1433032268695024e-005</v>
+        <v>1.6413755014633177e-006</v>
       </c>
       <c r="R3">
-        <v>-1.6643981312167935e-005</v>
+        <v>-1.5698619995628402e-005</v>
       </c>
       <c r="S3">
-        <v>5.8307866221793847e-006</v>
+        <v>6.5940972467318243e-006</v>
       </c>
       <c r="T3">
-        <v>-1.9325727017326707e-006</v>
+        <v>-6.6630291446318716e-006</v>
       </c>
       <c r="U3">
-        <v>8.9406633026548055e-007</v>
+        <v>-3.2517303090065877e-006</v>
       </c>
       <c r="V3">
-        <v>-1.2095390647407162e-006</v>
+        <v>-1.3932254770880636e-005</v>
       </c>
       <c r="W3">
-        <v>1.3349872169014538e-005</v>
+        <v>1.1083022285874212e-005</v>
       </c>
       <c r="X3">
-        <v>-1.1630343278863121e-005</v>
+        <v>-2.1259898289665994e-005</v>
       </c>
       <c r="Y3">
-        <v>-7.1365286076810995e-008</v>
+        <v>4.3065940634842053e-007</v>
       </c>
       <c r="Z3">
-        <v>-4.2550648915218493e-006</v>
+        <v>8.3165932298986825e-006</v>
       </c>
       <c r="AA3">
-        <v>-7.2023131823159672e-006</v>
+        <v>-1.0422504174754791e-005</v>
       </c>
       <c r="AB3">
-        <v>-2.1692380901941304e-005</v>
+        <v>-3.2040262132371797e-005</v>
       </c>
       <c r="AC3">
-        <v>-2.6876023877973063e-005</v>
+        <v>-4.6794344274689445e-005</v>
       </c>
       <c r="AD3">
-        <v>-5.2129313585139018e-006</v>
+        <v>-3.1208370834672232e-005</v>
       </c>
       <c r="AE3">
-        <v>-0.0015548025461564691</v>
+        <v>-0.0015051967117010983</v>
       </c>
     </row>
     <row r="4">
@@ -631,94 +757,94 @@
         <v>33</v>
       </c>
       <c r="B4">
-        <v>0.00044385961479229981</v>
+        <v>-0.0005071993203227983</v>
       </c>
       <c r="C4">
-        <v>3.1465375280620552e-007</v>
+        <v>1.1991167531721498e-007</v>
       </c>
       <c r="D4">
-        <v>-1.1154943446824942e-006</v>
+        <v>-1.1688157493505158e-006</v>
       </c>
       <c r="E4">
-        <v>1.4918246609606314e-008</v>
+        <v>1.6164392869831627e-008</v>
       </c>
       <c r="F4">
-        <v>-7.7221376096502976e-007</v>
+        <v>-7.1538476224992062e-007</v>
       </c>
       <c r="G4">
-        <v>-9.6484803822887851e-007</v>
+        <v>-8.8445241499802179e-007</v>
       </c>
       <c r="H4">
-        <v>-2.0849610975567778e-006</v>
+        <v>-1.670132250732765e-006</v>
       </c>
       <c r="I4">
-        <v>-1.6025920581141122e-006</v>
+        <v>-1.1621071095200769e-006</v>
       </c>
       <c r="J4">
-        <v>-1.4070508293908467e-006</v>
+        <v>-1.0475555730449665e-006</v>
       </c>
       <c r="K4">
-        <v>-1.5666899560463831e-006</v>
+        <v>-1.0883343637875806e-006</v>
       </c>
       <c r="L4">
-        <v>-1.1125734132390706e-006</v>
+        <v>-6.6436794499641369e-007</v>
       </c>
       <c r="M4">
-        <v>-1.3396437273161059e-006</v>
+        <v>-8.8165151933171278e-007</v>
       </c>
       <c r="N4">
-        <v>5.2323666850330862e-008</v>
+        <v>2.4870066426681085e-007</v>
       </c>
       <c r="O4">
-        <v>-3.283959955332303e-007</v>
+        <v>-1.2509189861780415e-007</v>
       </c>
       <c r="P4">
-        <v>-3.5020463021728397e-008</v>
+        <v>2.5945568876231059e-007</v>
       </c>
       <c r="Q4">
-        <v>6.3337015300660282e-009</v>
+        <v>-9.219766457570896e-008</v>
       </c>
       <c r="R4">
-        <v>1.2821859060781969e-007</v>
+        <v>1.507211718526614e-007</v>
       </c>
       <c r="S4">
-        <v>-1.9439998583913155e-007</v>
+        <v>-1.6087846390182722e-007</v>
       </c>
       <c r="T4">
-        <v>-8.0307127386476586e-009</v>
+        <v>6.9441089088250667e-008</v>
       </c>
       <c r="U4">
-        <v>-1.5962950008511749e-007</v>
+        <v>-5.8316378676224358e-008</v>
       </c>
       <c r="V4">
-        <v>-1.2355250592429246e-007</v>
+        <v>8.7460398018870337e-008</v>
       </c>
       <c r="W4">
-        <v>-3.5065492590082775e-007</v>
+        <v>-2.6876275158854978e-007</v>
       </c>
       <c r="X4">
-        <v>3.1396265845078558e-008</v>
+        <v>1.9644426974121556e-007</v>
       </c>
       <c r="Y4">
-        <v>4.2307766369329244e-010</v>
+        <v>-5.9031309051208174e-009</v>
       </c>
       <c r="Z4">
-        <v>7.5553596077281995e-008</v>
+        <v>-1.0269590096004158e-007</v>
       </c>
       <c r="AA4">
-        <v>1.0187974634759229e-007</v>
+        <v>1.2941865176107009e-007</v>
       </c>
       <c r="AB4">
-        <v>3.4920146561629916e-007</v>
+        <v>4.7084054655794496e-007</v>
       </c>
       <c r="AC4">
-        <v>3.1108552852123559e-007</v>
+        <v>6.0288966296993887e-007</v>
       </c>
       <c r="AD4">
-        <v>1.0003781509743627e-007</v>
+        <v>4.4046599590351972e-007</v>
       </c>
       <c r="AE4">
-        <v>1.9938384833170706e-005</v>
+        <v>2.0017858671374179e-005</v>
       </c>
     </row>
     <row r="5">
@@ -726,94 +852,94 @@
         <v>34</v>
       </c>
       <c r="B5">
-        <v>-0.27308596608915003</v>
+        <v>-0.23012031027259261</v>
       </c>
       <c r="C5">
-        <v>-0.00011904561676683809</v>
+        <v>-7.2453395176093135e-005</v>
       </c>
       <c r="D5">
-        <v>6.3744542601724949e-005</v>
+        <v>5.6817761465568763e-005</v>
       </c>
       <c r="E5">
-        <v>-7.7221376096502976e-007</v>
+        <v>-7.1538476224992062e-007</v>
       </c>
       <c r="F5">
-        <v>0.0011790775897404465</v>
+        <v>0.00085187139654413458</v>
       </c>
       <c r="G5">
-        <v>0.00082058018436639174</v>
+        <v>0.00060702461896784807</v>
       </c>
       <c r="H5">
-        <v>2.6744849370859467e-005</v>
+        <v>4.834133652759443e-005</v>
       </c>
       <c r="I5">
-        <v>-3.0857159342256938e-005</v>
+        <v>-4.269083402813832e-005</v>
       </c>
       <c r="J5">
-        <v>3.7535320455825286e-005</v>
+        <v>-1.9262445777850369e-005</v>
       </c>
       <c r="K5">
-        <v>-1.5312320586813679e-005</v>
+        <v>-3.009999416805134e-005</v>
       </c>
       <c r="L5">
-        <v>4.3233737276070759e-005</v>
+        <v>2.4376696423380063e-005</v>
       </c>
       <c r="M5">
-        <v>6.9544730385728254e-005</v>
+        <v>8.4587074620094292e-005</v>
       </c>
       <c r="N5">
-        <v>4.956082152354443e-005</v>
+        <v>3.4130283669125895e-005</v>
       </c>
       <c r="O5">
-        <v>-2.7822229458093753e-005</v>
+        <v>-5.5846693670687643e-006</v>
       </c>
       <c r="P5">
-        <v>-0.00010693377281242433</v>
+        <v>-6.8969280331529308e-005</v>
       </c>
       <c r="Q5">
-        <v>-0.00025150836900189312</v>
+        <v>-7.86761760668104e-005</v>
       </c>
       <c r="R5">
-        <v>-3.3272320010768213e-005</v>
+        <v>-6.4056763191177733e-005</v>
       </c>
       <c r="S5">
-        <v>6.7365303395574129e-005</v>
+        <v>4.7535347449882259e-005</v>
       </c>
       <c r="T5">
-        <v>2.6094426833276458e-005</v>
+        <v>3.48365017487001e-005</v>
       </c>
       <c r="U5">
-        <v>-0.0002206694084850991</v>
+        <v>-0.00011435097191886151</v>
       </c>
       <c r="V5">
-        <v>-0.00011589134803618127</v>
+        <v>-4.876120524032444e-005</v>
       </c>
       <c r="W5">
-        <v>-4.8241457278754929e-005</v>
+        <v>4.7359590728425342e-006</v>
       </c>
       <c r="X5">
-        <v>3.0755205554420855e-005</v>
+        <v>2.5108937682334371e-005</v>
       </c>
       <c r="Y5">
-        <v>4.408407015140093e-006</v>
+        <v>3.127331364818152e-006</v>
       </c>
       <c r="Z5">
-        <v>7.6141975321154408e-005</v>
+        <v>7.0155026190269024e-005</v>
       </c>
       <c r="AA5">
-        <v>4.8533594174586368e-005</v>
+        <v>1.3998868761168592e-005</v>
       </c>
       <c r="AB5">
-        <v>0.00037316560902281</v>
+        <v>0.00021664488402021954</v>
       </c>
       <c r="AC5">
-        <v>0.00013942371223252866</v>
+        <v>0.00011817761217204723</v>
       </c>
       <c r="AD5">
-        <v>0.00011456336596575144</v>
+        <v>9.5747053077426328e-005</v>
       </c>
       <c r="AE5">
-        <v>-0.0019188094309747551</v>
+        <v>-0.0015675822255723365</v>
       </c>
     </row>
     <row r="6">
@@ -821,94 +947,94 @@
         <v>35</v>
       </c>
       <c r="B6">
-        <v>-0.3161660199740603</v>
+        <v>-0.2866820083252184</v>
       </c>
       <c r="C6">
-        <v>-0.00014292808597463319</v>
+        <v>-0.00011268104369426102</v>
       </c>
       <c r="D6">
-        <v>5.5397598361516881e-005</v>
+        <v>5.3654817486314493e-005</v>
       </c>
       <c r="E6">
-        <v>-9.6484803822887851e-007</v>
+        <v>-8.8445241499802179e-007</v>
       </c>
       <c r="F6">
-        <v>0.00082058018436639174</v>
+        <v>0.00060702461896784807</v>
       </c>
       <c r="G6">
-        <v>0.004516504072386688</v>
+        <v>0.0032590571373878568</v>
       </c>
       <c r="H6">
-        <v>-4.1007402414743044e-005</v>
+        <v>6.3961454381169388e-005</v>
       </c>
       <c r="I6">
-        <v>-0.00048361038973112415</v>
+        <v>-0.00024513884193898923</v>
       </c>
       <c r="J6">
-        <v>0.00017416652531129702</v>
+        <v>0.00017708423745536124</v>
       </c>
       <c r="K6">
-        <v>0.00017774139871740336</v>
+        <v>0.00012136505108153753</v>
       </c>
       <c r="L6">
-        <v>0.00026291642830834536</v>
+        <v>0.00023678225032663773</v>
       </c>
       <c r="M6">
-        <v>0.00045040330324155268</v>
+        <v>0.00037824842934389808</v>
       </c>
       <c r="N6">
-        <v>0.00054196043158473515</v>
+        <v>0.00026125913836780334</v>
       </c>
       <c r="O6">
-        <v>0.0003127618921197168</v>
+        <v>0.00013926103458147197</v>
       </c>
       <c r="P6">
-        <v>0.00026323417279885047</v>
+        <v>0.00011066113761357984</v>
       </c>
       <c r="Q6">
-        <v>0.00010850463840107411</v>
+        <v>6.3893302556599762e-005</v>
       </c>
       <c r="R6">
-        <v>0.0001576780104881896</v>
+        <v>-1.2063648055053803e-005</v>
       </c>
       <c r="S6">
-        <v>-2.4178292399237043e-005</v>
+        <v>9.0440677329032035e-005</v>
       </c>
       <c r="T6">
-        <v>0.00038106740814587302</v>
+        <v>0.0002627165529270335</v>
       </c>
       <c r="U6">
-        <v>0.00011310756309257089</v>
+        <v>0.00012234323042650217</v>
       </c>
       <c r="V6">
-        <v>0.00010918605240317506</v>
+        <v>7.1748102154313822e-005</v>
       </c>
       <c r="W6">
-        <v>0.00018791140235520796</v>
+        <v>0.00010499126578968995</v>
       </c>
       <c r="X6">
-        <v>9.1101634324794846e-005</v>
+        <v>-7.1899077176939045e-005</v>
       </c>
       <c r="Y6">
-        <v>2.8441285669955818e-005</v>
+        <v>1.7621125931232957e-005</v>
       </c>
       <c r="Z6">
-        <v>-8.8374269448711788e-005</v>
+        <v>6.5167573245184998e-005</v>
       </c>
       <c r="AA6">
-        <v>-9.9243764042209544e-005</v>
+        <v>-9.2359087810389386e-005</v>
       </c>
       <c r="AB6">
-        <v>0.0004015496887424504</v>
+        <v>0.00025872316714480666</v>
       </c>
       <c r="AC6">
-        <v>0.00028220509488973962</v>
+        <v>0.00019792939553307039</v>
       </c>
       <c r="AD6">
-        <v>0.00032305895848009123</v>
+        <v>0.00022374336981168078</v>
       </c>
       <c r="AE6">
-        <v>-0.0022087242446957389</v>
+        <v>-0.001814068450888122</v>
       </c>
     </row>
     <row r="7">
@@ -916,94 +1042,94 @@
         <v>36</v>
       </c>
       <c r="B7">
-        <v>-0.17485756868852073</v>
+        <v>-0.23577470236834086</v>
       </c>
       <c r="C7">
-        <v>9.6861969303827842e-005</v>
+        <v>3.1397596436123429e-005</v>
       </c>
       <c r="D7">
-        <v>0.00017549860209374393</v>
+        <v>0.00013537064506818444</v>
       </c>
       <c r="E7">
-        <v>-2.0849610975567778e-006</v>
+        <v>-1.670132250732765e-006</v>
       </c>
       <c r="F7">
-        <v>2.6744849370859467e-005</v>
+        <v>4.834133652759443e-005</v>
       </c>
       <c r="G7">
-        <v>-4.1007402414743044e-005</v>
+        <v>6.3961454381169388e-005</v>
       </c>
       <c r="H7">
-        <v>0.0021518971114249559</v>
+        <v>0.0016158375115073046</v>
       </c>
       <c r="I7">
-        <v>0.0009693001240384119</v>
+        <v>0.00065984595931369299</v>
       </c>
       <c r="J7">
-        <v>0.00071660760077077424</v>
+        <v>0.00046141763211914928</v>
       </c>
       <c r="K7">
-        <v>0.0009820304924515928</v>
+        <v>0.00070295548558148941</v>
       </c>
       <c r="L7">
-        <v>0.0008330319685443732</v>
+        <v>0.00060996199711353921</v>
       </c>
       <c r="M7">
-        <v>0.00049302754983907287</v>
+        <v>0.0004112354628177587</v>
       </c>
       <c r="N7">
-        <v>-0.0001964961054141325</v>
+        <v>-3.9182482014568686e-005</v>
       </c>
       <c r="O7">
-        <v>-3.8914182525600456e-005</v>
+        <v>-2.360521743324242e-006</v>
       </c>
       <c r="P7">
-        <v>-0.00013125257370743615</v>
+        <v>-6.4300004857138445e-005</v>
       </c>
       <c r="Q7">
-        <v>-0.00011434119118769145</v>
+        <v>6.8072721305048318e-005</v>
       </c>
       <c r="R7">
-        <v>-0.00020507560406223687</v>
+        <v>-0.00013490525612469735</v>
       </c>
       <c r="S7">
-        <v>-0.00018479037067188676</v>
+        <v>-6.255623012722453e-005</v>
       </c>
       <c r="T7">
-        <v>-9.9085484095743476e-005</v>
+        <v>-1.1340074954582996e-005</v>
       </c>
       <c r="U7">
-        <v>-2.5202366787791214e-005</v>
+        <v>-6.6575702848126195e-006</v>
       </c>
       <c r="V7">
-        <v>1.6753080447032276e-005</v>
+        <v>3.0162388696468919e-005</v>
       </c>
       <c r="W7">
-        <v>-4.5216342418121901e-005</v>
+        <v>-2.7520283551164815e-005</v>
       </c>
       <c r="X7">
-        <v>-9.10004407589011e-005</v>
+        <v>-4.6185364710916652e-005</v>
       </c>
       <c r="Y7">
-        <v>1.8184367273823686e-006</v>
+        <v>2.5554626613031136e-006</v>
       </c>
       <c r="Z7">
-        <v>-0.00015674405732034628</v>
+        <v>-5.6753658035689838e-006</v>
       </c>
       <c r="AA7">
-        <v>-0.00011260891038819504</v>
+        <v>-4.354247592255989e-005</v>
       </c>
       <c r="AB7">
-        <v>2.8270173464144902e-005</v>
+        <v>1.9561613223252963e-006</v>
       </c>
       <c r="AC7">
-        <v>2.4024677142782044e-006</v>
+        <v>-2.8951096470484963e-005</v>
       </c>
       <c r="AD7">
-        <v>7.7295078950241321e-005</v>
+        <v>3.6078932133126913e-005</v>
       </c>
       <c r="AE7">
-        <v>-0.0042096053654617407</v>
+        <v>-0.003180940469194306</v>
       </c>
     </row>
     <row r="8">
@@ -1011,94 +1137,94 @@
         <v>37</v>
       </c>
       <c r="B8">
-        <v>-0.15143953574978394</v>
+        <v>-0.22531144861448238</v>
       </c>
       <c r="C8">
-        <v>2.408016643033453e-005</v>
+        <v>-6.052830878747174e-006</v>
       </c>
       <c r="D8">
-        <v>0.00012426242944792406</v>
+        <v>8.9159833928564554e-005</v>
       </c>
       <c r="E8">
-        <v>-1.6025920581141122e-006</v>
+        <v>-1.1621071095200769e-006</v>
       </c>
       <c r="F8">
-        <v>-3.0857159342256938e-005</v>
+        <v>-4.269083402813832e-005</v>
       </c>
       <c r="G8">
-        <v>-0.00048361038973112415</v>
+        <v>-0.00024513884193898923</v>
       </c>
       <c r="H8">
-        <v>0.0009693001240384119</v>
+        <v>0.00065984595931369299</v>
       </c>
       <c r="I8">
-        <v>0.0024356421913506255</v>
+        <v>0.0017588661951455386</v>
       </c>
       <c r="J8">
-        <v>0.0013568239352809625</v>
+        <v>0.00094431782235945448</v>
       </c>
       <c r="K8">
-        <v>0.0015752242186613807</v>
+        <v>0.0011316297818442734</v>
       </c>
       <c r="L8">
-        <v>0.0014222604352087536</v>
+        <v>0.0010468016426920953</v>
       </c>
       <c r="M8">
-        <v>0.0011174131917346905</v>
+        <v>0.00083722569771410961</v>
       </c>
       <c r="N8">
-        <v>-0.00030541338284988378</v>
+        <v>-0.00028524014536085809</v>
       </c>
       <c r="O8">
-        <v>-3.9453299579033946e-005</v>
+        <v>-0.00010749950915600896</v>
       </c>
       <c r="P8">
-        <v>-0.00018665813198023243</v>
+        <v>-0.0001804975702019866</v>
       </c>
       <c r="Q8">
-        <v>-0.00030188682534425205</v>
+        <v>-0.0001598045668305566</v>
       </c>
       <c r="R8">
-        <v>-0.0002448243328716752</v>
+        <v>-0.00016493373991818833</v>
       </c>
       <c r="S8">
-        <v>-4.9582572285289389e-006</v>
+        <v>-7.5177398729195117e-005</v>
       </c>
       <c r="T8">
-        <v>-1.696163585917967e-005</v>
+        <v>-3.7764651263490212e-005</v>
       </c>
       <c r="U8">
-        <v>-0.00018164059965022759</v>
+        <v>-0.00015046189828561739</v>
       </c>
       <c r="V8">
-        <v>-0.0001131500937367972</v>
+        <v>-0.00010391691635463617</v>
       </c>
       <c r="W8">
-        <v>-2.7302839536066633e-006</v>
+        <v>-0.00010291695752616447</v>
       </c>
       <c r="X8">
-        <v>-0.00010408440354341434</v>
+        <v>-8.5188331701035493e-005</v>
       </c>
       <c r="Y8">
-        <v>-1.9514786708447915e-006</v>
+        <v>1.2247320099477611e-006</v>
       </c>
       <c r="Z8">
-        <v>-0.00017436455763986363</v>
+        <v>-9.927257200495628e-005</v>
       </c>
       <c r="AA8">
-        <v>-7.3580414676958905e-005</v>
+        <v>-5.7327223817469632e-005</v>
       </c>
       <c r="AB8">
-        <v>0.00010586853365773504</v>
+        <v>1.973981814903155e-005</v>
       </c>
       <c r="AC8">
-        <v>1.7808302128676477e-005</v>
+        <v>-4.7613551951191952e-005</v>
       </c>
       <c r="AD8">
-        <v>0.00026501419097670845</v>
+        <v>2.5198233826131131e-005</v>
       </c>
       <c r="AE8">
-        <v>-0.0036083293383268635</v>
+        <v>-0.0025518231297193958</v>
       </c>
     </row>
     <row r="9">
@@ -1106,94 +1232,94 @@
         <v>38</v>
       </c>
       <c r="B9">
-        <v>-0.1714112645250187</v>
+        <v>-0.13751377162683975</v>
       </c>
       <c r="C9">
-        <v>0.00013622279815488845</v>
+        <v>7.3152197757537878e-005</v>
       </c>
       <c r="D9">
-        <v>0.00011385949208549752</v>
+        <v>8.6378940490587649e-005</v>
       </c>
       <c r="E9">
-        <v>-1.4070508293908467e-006</v>
+        <v>-1.0475555730449665e-006</v>
       </c>
       <c r="F9">
-        <v>3.7535320455825286e-005</v>
+        <v>-1.9262445777850369e-005</v>
       </c>
       <c r="G9">
-        <v>0.00017416652531129702</v>
+        <v>0.00017708423745536124</v>
       </c>
       <c r="H9">
-        <v>0.00071660760077077424</v>
+        <v>0.00046141763211914928</v>
       </c>
       <c r="I9">
-        <v>0.0013568239352809625</v>
+        <v>0.00094431782235945448</v>
       </c>
       <c r="J9">
-        <v>0.0029231968465299792</v>
+        <v>0.00218485791345848</v>
       </c>
       <c r="K9">
-        <v>0.0019542057228681556</v>
+        <v>0.0014194978277392778</v>
       </c>
       <c r="L9">
-        <v>0.0018345283351852298</v>
+        <v>0.0013394319103806887</v>
       </c>
       <c r="M9">
-        <v>0.0016747211947203192</v>
+        <v>0.0012194157594313357</v>
       </c>
       <c r="N9">
-        <v>0.00028810419402787598</v>
+        <v>2.4712452729131612e-005</v>
       </c>
       <c r="O9">
-        <v>2.4445006637660718e-005</v>
+        <v>5.7726435328481836e-007</v>
       </c>
       <c r="P9">
-        <v>-2.5700361891442026e-005</v>
+        <v>-2.6563419014257058e-005</v>
       </c>
       <c r="Q9">
-        <v>-0.00025237003667107777</v>
+        <v>-0.0001018094242994052</v>
       </c>
       <c r="R9">
-        <v>-0.00028238373315389939</v>
+        <v>-0.00010070621767282838</v>
       </c>
       <c r="S9">
-        <v>-0.00013616593647829611</v>
+        <v>-2.6495174243555426e-005</v>
       </c>
       <c r="T9">
-        <v>4.8198850616078715e-005</v>
+        <v>3.0848422186911502e-006</v>
       </c>
       <c r="U9">
-        <v>-0.00015198363930017059</v>
+        <v>-7.3213144093769392e-005</v>
       </c>
       <c r="V9">
-        <v>1.8933567812122465e-005</v>
+        <v>-3.0082659815623865e-006</v>
       </c>
       <c r="W9">
-        <v>3.7672229702493017e-005</v>
+        <v>-2.6398395451710617e-005</v>
       </c>
       <c r="X9">
-        <v>5.232867210725866e-005</v>
+        <v>-1.2586627845200503e-005</v>
       </c>
       <c r="Y9">
-        <v>4.0059845813835722e-006</v>
+        <v>9.7474185366669804e-006</v>
       </c>
       <c r="Z9">
-        <v>-0.00015350412130647688</v>
+        <v>-7.879259861479944e-005</v>
       </c>
       <c r="AA9">
-        <v>-2.5530667434722922e-005</v>
+        <v>-0.00010586496222526029</v>
       </c>
       <c r="AB9">
-        <v>0.0002592626601205239</v>
+        <v>0.00012648981397700909</v>
       </c>
       <c r="AC9">
-        <v>0.00011721681639982173</v>
+        <v>7.6794854193834843e-005</v>
       </c>
       <c r="AD9">
-        <v>0.00032244911903909134</v>
+        <v>5.8547734280670711e-005</v>
       </c>
       <c r="AE9">
-        <v>-0.004087867188814741</v>
+        <v>-0.0030960396224354834</v>
       </c>
     </row>
     <row r="10">
@@ -1201,94 +1327,94 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>-0.26084705691095755</v>
+        <v>-0.18369682827822281</v>
       </c>
       <c r="C10">
-        <v>0.00014200205900610137</v>
+        <v>5.7163462538164868e-005</v>
       </c>
       <c r="D10">
-        <v>0.00012552472889933991</v>
+        <v>8.8679852354744954e-005</v>
       </c>
       <c r="E10">
-        <v>-1.5666899560463831e-006</v>
+        <v>-1.0883343637875806e-006</v>
       </c>
       <c r="F10">
-        <v>-1.5312320586813679e-005</v>
+        <v>-3.009999416805134e-005</v>
       </c>
       <c r="G10">
-        <v>0.00017774139871740336</v>
+        <v>0.00012136505108153753</v>
       </c>
       <c r="H10">
-        <v>0.0009820304924515928</v>
+        <v>0.00070295548558148941</v>
       </c>
       <c r="I10">
-        <v>0.0015752242186613807</v>
+        <v>0.0011316297818442734</v>
       </c>
       <c r="J10">
-        <v>0.0019542057228681556</v>
+        <v>0.0014194978277392778</v>
       </c>
       <c r="K10">
-        <v>0.0030709791877172915</v>
+        <v>0.0021565239827766747</v>
       </c>
       <c r="L10">
-        <v>0.0019814070626886903</v>
+        <v>0.0014676766868585069</v>
       </c>
       <c r="M10">
-        <v>0.001754723478991806</v>
+        <v>0.0012916025847459209</v>
       </c>
       <c r="N10">
-        <v>0.00012988654967265403</v>
+        <v>-0.0001137432647532481</v>
       </c>
       <c r="O10">
-        <v>-1.8557229465389119e-006</v>
+        <v>-8.1418228234617822e-005</v>
       </c>
       <c r="P10">
-        <v>-8.9947723714290371e-005</v>
+        <v>-0.00013615318021789017</v>
       </c>
       <c r="Q10">
-        <v>-0.00036455343653250404</v>
+        <v>-0.0001270280931774903</v>
       </c>
       <c r="R10">
-        <v>-0.0002771351175657904</v>
+        <v>-0.00024022414306767672</v>
       </c>
       <c r="S10">
-        <v>-0.00023203110102269818</v>
+        <v>-0.00018975483061341424</v>
       </c>
       <c r="T10">
-        <v>-2.5317213062155011e-005</v>
+        <v>-0.00011799478354853178</v>
       </c>
       <c r="U10">
-        <v>-0.0002320829359623218</v>
+        <v>-0.00018907793922641122</v>
       </c>
       <c r="V10">
-        <v>5.2008275478468251e-005</v>
+        <v>-6.5086958698556095e-005</v>
       </c>
       <c r="W10">
-        <v>4.9088773089981004e-006</v>
+        <v>-0.00013909323796086484</v>
       </c>
       <c r="X10">
-        <v>-4.1399863636967186e-005</v>
+        <v>-0.00014582194326230764</v>
       </c>
       <c r="Y10">
-        <v>2.0592966853558731e-005</v>
+        <v>1.0886798474500688e-005</v>
       </c>
       <c r="Z10">
-        <v>-0.00034517134978559211</v>
+        <v>-7.1105620269609564e-005</v>
       </c>
       <c r="AA10">
-        <v>-0.00014415966650339098</v>
+        <v>-7.9942168277313499e-005</v>
       </c>
       <c r="AB10">
-        <v>0.00022971819166165124</v>
+        <v>0.00013654436429704105</v>
       </c>
       <c r="AC10">
-        <v>0.00014697569960548783</v>
+        <v>3.154922896337958e-005</v>
       </c>
       <c r="AD10">
-        <v>0.0002898025676345414</v>
+        <v>6.7423512803300523e-005</v>
       </c>
       <c r="AE10">
-        <v>-0.0046480309574214243</v>
+        <v>-0.0031985002276480167</v>
       </c>
     </row>
     <row r="11">
@@ -1296,94 +1422,94 @@
         <v>40</v>
       </c>
       <c r="B11">
-        <v>-0.11409040314158277</v>
+        <v>-0.10280073290249862</v>
       </c>
       <c r="C11">
-        <v>6.0594948023574949e-005</v>
+        <v>-7.919247390734002e-006</v>
       </c>
       <c r="D11">
-        <v>8.5027124691176978e-005</v>
+        <v>5.2938173375396939e-005</v>
       </c>
       <c r="E11">
-        <v>-1.1125734132390706e-006</v>
+        <v>-6.6436794499641369e-007</v>
       </c>
       <c r="F11">
-        <v>4.3233737276070759e-005</v>
+        <v>2.4376696423380063e-005</v>
       </c>
       <c r="G11">
-        <v>0.00026291642830834536</v>
+        <v>0.00023678225032663773</v>
       </c>
       <c r="H11">
-        <v>0.0008330319685443732</v>
+        <v>0.00060996199711353921</v>
       </c>
       <c r="I11">
-        <v>0.0014222604352087536</v>
+        <v>0.0010468016426920953</v>
       </c>
       <c r="J11">
-        <v>0.0018345283351852298</v>
+        <v>0.0013394319103806887</v>
       </c>
       <c r="K11">
-        <v>0.0019814070626886903</v>
+        <v>0.0014676766868585069</v>
       </c>
       <c r="L11">
-        <v>0.0027100000207989925</v>
+        <v>0.0019740951501461702</v>
       </c>
       <c r="M11">
-        <v>0.0016597846300744183</v>
+        <v>0.0012721686734738723</v>
       </c>
       <c r="N11">
-        <v>3.0311181187234692e-005</v>
+        <v>-7.1591598934668869e-005</v>
       </c>
       <c r="O11">
-        <v>3.7273955116987826e-005</v>
+        <v>3.3249119537213955e-005</v>
       </c>
       <c r="P11">
-        <v>6.6303089200821729e-005</v>
+        <v>6.3366268925852428e-005</v>
       </c>
       <c r="Q11">
-        <v>-0.00021782162351067461</v>
+        <v>-3.0434464864308479e-005</v>
       </c>
       <c r="R11">
-        <v>-0.00025159069364695481</v>
+        <v>-0.00013063667400963256</v>
       </c>
       <c r="S11">
-        <v>-3.6497441578182439e-005</v>
+        <v>-9.5690091485296606e-006</v>
       </c>
       <c r="T11">
-        <v>4.8213566854139116e-005</v>
+        <v>3.7120588287913579e-005</v>
       </c>
       <c r="U11">
-        <v>-0.00016727729067834366</v>
+        <v>-7.8096255359465933e-005</v>
       </c>
       <c r="V11">
-        <v>0.00014444590519336817</v>
+        <v>0.0001258339832742564</v>
       </c>
       <c r="W11">
-        <v>7.069809087567006e-005</v>
+        <v>2.7864556993159768e-005</v>
       </c>
       <c r="X11">
-        <v>8.0542994243797822e-005</v>
+        <v>2.6230457302646622e-005</v>
       </c>
       <c r="Y11">
-        <v>3.7457318080623897e-006</v>
+        <v>2.1599491292225131e-006</v>
       </c>
       <c r="Z11">
-        <v>-0.00013816069335462628</v>
+        <v>-2.6241413020190838e-005</v>
       </c>
       <c r="AA11">
-        <v>5.0804757637224737e-005</v>
+        <v>-2.9939554312191023e-005</v>
       </c>
       <c r="AB11">
-        <v>0.0002119024471781087</v>
+        <v>0.00018114464637901395</v>
       </c>
       <c r="AC11">
-        <v>0.0001430421418352648</v>
+        <v>0.00012472314377554288</v>
       </c>
       <c r="AD11">
-        <v>0.00031481929150526506</v>
+        <v>0.00013637031996509025</v>
       </c>
       <c r="AE11">
-        <v>-0.0036081682074562819</v>
+        <v>-0.0025087688747968012</v>
       </c>
     </row>
     <row r="12">
@@ -1391,94 +1517,94 @@
         <v>41</v>
       </c>
       <c r="B12">
-        <v>-0.0095437182677831391</v>
+        <v>-0.00096117878584955473</v>
       </c>
       <c r="C12">
-        <v>5.2021065018809095e-006</v>
+        <v>-5.4022410730413241e-005</v>
       </c>
       <c r="D12">
-        <v>9.6174226206568916e-005</v>
+        <v>6.402627187999199e-005</v>
       </c>
       <c r="E12">
-        <v>-1.3396437273161059e-006</v>
+        <v>-8.8165151933171278e-007</v>
       </c>
       <c r="F12">
-        <v>6.9544730385728254e-005</v>
+        <v>8.4587074620094292e-005</v>
       </c>
       <c r="G12">
-        <v>0.00045040330324155268</v>
+        <v>0.00037824842934389808</v>
       </c>
       <c r="H12">
-        <v>0.00049302754983907287</v>
+        <v>0.0004112354628177587</v>
       </c>
       <c r="I12">
-        <v>0.0011174131917346905</v>
+        <v>0.00083722569771410961</v>
       </c>
       <c r="J12">
-        <v>0.0016747211947203192</v>
+        <v>0.0012194157594313357</v>
       </c>
       <c r="K12">
-        <v>0.001754723478991806</v>
+        <v>0.0012916025847459209</v>
       </c>
       <c r="L12">
-        <v>0.0016597846300744183</v>
+        <v>0.0012721686734738723</v>
       </c>
       <c r="M12">
-        <v>0.0037121200573981472</v>
+        <v>0.0027760121552121162</v>
       </c>
       <c r="N12">
-        <v>0.00046595982112609697</v>
+        <v>0.00021014117664750365</v>
       </c>
       <c r="O12">
-        <v>0.0003590809415783317</v>
+        <v>0.00023526768422863853</v>
       </c>
       <c r="P12">
-        <v>0.00023991050728174856</v>
+        <v>0.00019161740311951915</v>
       </c>
       <c r="Q12">
-        <v>-5.5796989506346427e-005</v>
+        <v>8.1139062559040451e-005</v>
       </c>
       <c r="R12">
-        <v>0.00012882058694468668</v>
+        <v>0.00012084038355714664</v>
       </c>
       <c r="S12">
-        <v>3.6943146817129961e-005</v>
+        <v>0.00012922150030050665</v>
       </c>
       <c r="T12">
-        <v>0.00014092799565458759</v>
+        <v>0.00010383510948237991</v>
       </c>
       <c r="U12">
-        <v>-4.7977738492479237e-005</v>
+        <v>2.9972044603723022e-005</v>
       </c>
       <c r="V12">
-        <v>0.00030198831036498349</v>
+        <v>0.00022510642538022094</v>
       </c>
       <c r="W12">
-        <v>0.00023770638890161628</v>
+        <v>0.00015809072673620957</v>
       </c>
       <c r="X12">
-        <v>0.00031828192757619826</v>
+        <v>0.00019816776173935818</v>
       </c>
       <c r="Y12">
-        <v>5.8126364268046803e-007</v>
+        <v>4.6991094893658603e-006</v>
       </c>
       <c r="Z12">
-        <v>-9.4030945990691115e-005</v>
+        <v>1.0752889510549847e-005</v>
       </c>
       <c r="AA12">
-        <v>4.9218357950740272e-005</v>
+        <v>-8.6676086461380043e-005</v>
       </c>
       <c r="AB12">
-        <v>4.9829191017414492e-005</v>
+        <v>9.3443646703452636e-005</v>
       </c>
       <c r="AC12">
-        <v>0.00019549808676047609</v>
+        <v>0.00015168487481170378</v>
       </c>
       <c r="AD12">
-        <v>0.00055622552068529971</v>
+        <v>0.0002757550620857373</v>
       </c>
       <c r="AE12">
-        <v>-0.0035837109712486522</v>
+        <v>-0.0026495570997936914</v>
       </c>
     </row>
     <row r="13">
@@ -1486,94 +1612,94 @@
         <v>42</v>
       </c>
       <c r="B13">
-        <v>-0.017826784980051111</v>
+        <v>-0.056265885250607731</v>
       </c>
       <c r="C13">
-        <v>-5.8460765848974088e-005</v>
+        <v>-8.7401251444302363e-005</v>
       </c>
       <c r="D13">
-        <v>-1.2476099615596134e-005</v>
+        <v>-2.5070176931737465e-005</v>
       </c>
       <c r="E13">
-        <v>5.2323666850330862e-008</v>
+        <v>2.4870066426681085e-007</v>
       </c>
       <c r="F13">
-        <v>4.956082152354443e-005</v>
+        <v>3.4130283669125895e-005</v>
       </c>
       <c r="G13">
-        <v>0.00054196043158473515</v>
+        <v>0.00026125913836780334</v>
       </c>
       <c r="H13">
-        <v>-0.0001964961054141325</v>
+        <v>-3.9182482014568686e-005</v>
       </c>
       <c r="I13">
-        <v>-0.00030541338284988378</v>
+        <v>-0.00028524014536085809</v>
       </c>
       <c r="J13">
-        <v>0.00028810419402787598</v>
+        <v>2.4712452729131612e-005</v>
       </c>
       <c r="K13">
-        <v>0.00012988654967265403</v>
+        <v>-0.0001137432647532481</v>
       </c>
       <c r="L13">
-        <v>3.0311181187234692e-005</v>
+        <v>-7.1591598934668869e-005</v>
       </c>
       <c r="M13">
-        <v>0.00046595982112609697</v>
+        <v>0.00021014117664750365</v>
       </c>
       <c r="N13">
-        <v>0.0072128530938373823</v>
+        <v>0.0057806550997103155</v>
       </c>
       <c r="O13">
-        <v>0.0023444834954829165</v>
+        <v>0.0019185525401796005</v>
       </c>
       <c r="P13">
-        <v>0.0023773555100335534</v>
+        <v>0.0019315860192200775</v>
       </c>
       <c r="Q13">
-        <v>0.0023952414123721306</v>
+        <v>0.0019429547586827679</v>
       </c>
       <c r="R13">
-        <v>0.0022503269229464306</v>
+        <v>0.0018340347529120743</v>
       </c>
       <c r="S13">
-        <v>0.0022710689083376562</v>
+        <v>0.0018725835791016201</v>
       </c>
       <c r="T13">
-        <v>0.0023500422317761292</v>
+        <v>0.0019238644309188719</v>
       </c>
       <c r="U13">
-        <v>0.0024160756257084982</v>
+        <v>0.0019803172633022555</v>
       </c>
       <c r="V13">
-        <v>0.0024703939841392332</v>
+        <v>0.002018441294097461</v>
       </c>
       <c r="W13">
-        <v>0.002424054473727991</v>
+        <v>0.0019890429611168635</v>
       </c>
       <c r="X13">
-        <v>0.0024694059302184674</v>
+        <v>0.0020046205080913432</v>
       </c>
       <c r="Y13">
-        <v>3.0748892442776713e-006</v>
+        <v>4.129064415616071e-006</v>
       </c>
       <c r="Z13">
-        <v>-0.0001827363655809362</v>
+        <v>-2.3470979477307737e-006</v>
       </c>
       <c r="AA13">
-        <v>-6.9913850603355959e-005</v>
+        <v>0.00011765798045203346</v>
       </c>
       <c r="AB13">
-        <v>0.0011140082769774341</v>
+        <v>0.00080254037552375133</v>
       </c>
       <c r="AC13">
-        <v>0.0022254238923909379</v>
+        <v>0.0017092684925013599</v>
       </c>
       <c r="AD13">
-        <v>0.0010622122850906931</v>
+        <v>0.00086570109065174606</v>
       </c>
       <c r="AE13">
-        <v>-0.0022679666119874643</v>
+        <v>-0.0015156817753532682</v>
       </c>
     </row>
     <row r="14">
@@ -1581,94 +1707,94 @@
         <v>43</v>
       </c>
       <c r="B14">
-        <v>0.16455601037135331</v>
+        <v>0.17361876534223836</v>
       </c>
       <c r="C14">
-        <v>3.0247009458892162e-005</v>
+        <v>-1.377023523726338e-005</v>
       </c>
       <c r="D14">
-        <v>1.6043452185874325e-005</v>
+        <v>5.9334130899898666e-006</v>
       </c>
       <c r="E14">
-        <v>-3.283959955332303e-007</v>
+        <v>-1.2509189861780415e-007</v>
       </c>
       <c r="F14">
-        <v>-2.7822229458093753e-005</v>
+        <v>-5.5846693670687643e-006</v>
       </c>
       <c r="G14">
-        <v>0.0003127618921197168</v>
+        <v>0.00013926103458147197</v>
       </c>
       <c r="H14">
-        <v>-3.8914182525600456e-005</v>
+        <v>-2.360521743324242e-006</v>
       </c>
       <c r="I14">
-        <v>-3.9453299579033946e-005</v>
+        <v>-0.00010749950915600896</v>
       </c>
       <c r="J14">
-        <v>2.4445006637660718e-005</v>
+        <v>5.7726435328481836e-007</v>
       </c>
       <c r="K14">
-        <v>-1.8557229465389119e-006</v>
+        <v>-8.1418228234617822e-005</v>
       </c>
       <c r="L14">
-        <v>3.7273955116987826e-005</v>
+        <v>3.3249119537213955e-005</v>
       </c>
       <c r="M14">
-        <v>0.0003590809415783317</v>
+        <v>0.00023526768422863853</v>
       </c>
       <c r="N14">
-        <v>0.0023444834954829165</v>
+        <v>0.0019185525401796005</v>
       </c>
       <c r="O14">
-        <v>0.0040964822450468685</v>
+        <v>0.0032300764544634041</v>
       </c>
       <c r="P14">
-        <v>0.0022668280748347905</v>
+        <v>0.0018550603496835163</v>
       </c>
       <c r="Q14">
-        <v>0.0023006640784174383</v>
+        <v>0.0018683951477599199</v>
       </c>
       <c r="R14">
-        <v>0.002199639520438289</v>
+        <v>0.0017861380338508532</v>
       </c>
       <c r="S14">
-        <v>0.0022059064598339115</v>
+        <v>0.0018092565681819403</v>
       </c>
       <c r="T14">
-        <v>0.0022439203929961685</v>
+        <v>0.0018457705974611487</v>
       </c>
       <c r="U14">
-        <v>0.0023192034308985522</v>
+        <v>0.0018994078046249232</v>
       </c>
       <c r="V14">
-        <v>0.0023516834042621318</v>
+        <v>0.0019215069192266613</v>
       </c>
       <c r="W14">
-        <v>0.0023409811520170806</v>
+        <v>0.0019145477730492535</v>
       </c>
       <c r="X14">
-        <v>0.0023395557341882129</v>
+        <v>0.0019116902677907173</v>
       </c>
       <c r="Y14">
-        <v>-8.8155477690423267e-007</v>
+        <v>2.6762695430093583e-006</v>
       </c>
       <c r="Z14">
-        <v>-0.00023289918249270994</v>
+        <v>-1.1188786660084731e-005</v>
       </c>
       <c r="AA14">
-        <v>6.5058756591275592e-005</v>
+        <v>9.4007546094012021e-005</v>
       </c>
       <c r="AB14">
-        <v>0.00076409314393045</v>
+        <v>0.00059206281865317593</v>
       </c>
       <c r="AC14">
-        <v>0.001884026264625467</v>
+        <v>0.0014903548817045602</v>
       </c>
       <c r="AD14">
-        <v>0.00078573604171323713</v>
+        <v>0.0006765657899571268</v>
       </c>
       <c r="AE14">
-        <v>-0.0025184587412703367</v>
+        <v>-0.0020088504065586899</v>
       </c>
     </row>
     <row r="15">
@@ -1676,94 +1802,94 @@
         <v>44</v>
       </c>
       <c r="B15">
-        <v>0.18978867918877076</v>
+        <v>0.17537137789235521</v>
       </c>
       <c r="C15">
-        <v>-3.9283592258444852e-006</v>
+        <v>-4.1504336383314901e-005</v>
       </c>
       <c r="D15">
-        <v>-6.0676156975564911e-006</v>
+        <v>-2.328736363807829e-005</v>
       </c>
       <c r="E15">
-        <v>-3.5020463021728397e-008</v>
+        <v>2.5945568876231059e-007</v>
       </c>
       <c r="F15">
-        <v>-0.00010693377281242433</v>
+        <v>-6.8969280331529308e-005</v>
       </c>
       <c r="G15">
-        <v>0.00026323417279885047</v>
+        <v>0.00011066113761357984</v>
       </c>
       <c r="H15">
-        <v>-0.00013125257370743615</v>
+        <v>-6.4300004857138445e-005</v>
       </c>
       <c r="I15">
-        <v>-0.00018665813198023243</v>
+        <v>-0.0001804975702019866</v>
       </c>
       <c r="J15">
-        <v>-2.5700361891442026e-005</v>
+        <v>-2.6563419014257058e-005</v>
       </c>
       <c r="K15">
-        <v>-8.9947723714290371e-005</v>
+        <v>-0.00013615318021789017</v>
       </c>
       <c r="L15">
-        <v>6.6303089200821729e-005</v>
+        <v>6.3366268925852428e-005</v>
       </c>
       <c r="M15">
-        <v>0.00023991050728174856</v>
+        <v>0.00019161740311951915</v>
       </c>
       <c r="N15">
-        <v>0.0023773555100335534</v>
+        <v>0.0019315860192200775</v>
       </c>
       <c r="O15">
-        <v>0.0022668280748347905</v>
+        <v>0.0018550603496835163</v>
       </c>
       <c r="P15">
-        <v>0.0045962180279628768</v>
+        <v>0.0034980328569387369</v>
       </c>
       <c r="Q15">
-        <v>0.0023332545114379305</v>
+        <v>0.0018795640150201243</v>
       </c>
       <c r="R15">
-        <v>0.0021956071828246348</v>
+        <v>0.0017854293469072237</v>
       </c>
       <c r="S15">
-        <v>0.0021853965545233752</v>
+        <v>0.0018073753641673839</v>
       </c>
       <c r="T15">
-        <v>0.0022546484689437581</v>
+        <v>0.0018483342467368971</v>
       </c>
       <c r="U15">
-        <v>0.0023349185794742408</v>
+        <v>0.0019072967697103531</v>
       </c>
       <c r="V15">
-        <v>0.0023766806181526141</v>
+        <v>0.001934025180458228</v>
       </c>
       <c r="W15">
-        <v>0.0023421768120842849</v>
+        <v>0.001909813566726223</v>
       </c>
       <c r="X15">
-        <v>0.0023502862408103444</v>
+        <v>0.0019161393515072062</v>
       </c>
       <c r="Y15">
-        <v>-4.4625313866024168e-006</v>
+        <v>-3.0973295030152533e-006</v>
       </c>
       <c r="Z15">
-        <v>-0.0002511081884967822</v>
+        <v>-2.3869197445764746e-005</v>
       </c>
       <c r="AA15">
-        <v>0.00029947993281955886</v>
+        <v>0.00017577533780991045</v>
       </c>
       <c r="AB15">
-        <v>0.00075453485633682953</v>
+        <v>0.00060363137553947591</v>
       </c>
       <c r="AC15">
-        <v>0.0018407872377880709</v>
+        <v>0.0014376435382701508</v>
       </c>
       <c r="AD15">
-        <v>0.0010340295999819056</v>
+        <v>0.00087048826639843325</v>
       </c>
       <c r="AE15">
-        <v>-0.0019820275231181082</v>
+        <v>-0.0013529242598980637</v>
       </c>
     </row>
     <row r="16">
@@ -1771,94 +1897,94 @@
         <v>45</v>
       </c>
       <c r="B16">
-        <v>0.072479293891244675</v>
+        <v>0.11811306601601416</v>
       </c>
       <c r="C16">
-        <v>-6.2379929981665888e-005</v>
+        <v>-6.873988698360891e-005</v>
       </c>
       <c r="D16">
-        <v>-1.1433032268695024e-005</v>
+        <v>1.6413755014633177e-006</v>
       </c>
       <c r="E16">
-        <v>6.3337015300660282e-009</v>
+        <v>-9.219766457570896e-008</v>
       </c>
       <c r="F16">
-        <v>-0.00025150836900189312</v>
+        <v>-7.86761760668104e-005</v>
       </c>
       <c r="G16">
-        <v>0.00010850463840107411</v>
+        <v>6.3893302556599762e-005</v>
       </c>
       <c r="H16">
-        <v>-0.00011434119118769145</v>
+        <v>6.8072721305048318e-005</v>
       </c>
       <c r="I16">
-        <v>-0.00030188682534425205</v>
+        <v>-0.0001598045668305566</v>
       </c>
       <c r="J16">
-        <v>-0.00025237003667107777</v>
+        <v>-0.0001018094242994052</v>
       </c>
       <c r="K16">
-        <v>-0.00036455343653250404</v>
+        <v>-0.0001270280931774903</v>
       </c>
       <c r="L16">
-        <v>-0.00021782162351067461</v>
+        <v>-3.0434464864308479e-005</v>
       </c>
       <c r="M16">
-        <v>-5.5796989506346427e-005</v>
+        <v>8.1139062559040451e-005</v>
       </c>
       <c r="N16">
-        <v>0.0023952414123721306</v>
+        <v>0.0019429547586827679</v>
       </c>
       <c r="O16">
-        <v>0.0023006640784174383</v>
+        <v>0.0018683951477599199</v>
       </c>
       <c r="P16">
-        <v>0.0023332545114379305</v>
+        <v>0.0018795640150201243</v>
       </c>
       <c r="Q16">
-        <v>0.0050220032680155079</v>
+        <v>0.0038382683508307374</v>
       </c>
       <c r="R16">
-        <v>0.0022365263444139682</v>
+        <v>0.001798450560788298</v>
       </c>
       <c r="S16">
-        <v>0.0022457477768828556</v>
+        <v>0.0018243710793423864</v>
       </c>
       <c r="T16">
-        <v>0.0022945497834549002</v>
+        <v>0.0018717626228667299</v>
       </c>
       <c r="U16">
-        <v>0.0024078495046351922</v>
+        <v>0.0019370075428943655</v>
       </c>
       <c r="V16">
-        <v>0.0024218993067849819</v>
+        <v>0.0019535847112462862</v>
       </c>
       <c r="W16">
-        <v>0.0023986616794864656</v>
+        <v>0.0019398401413710941</v>
       </c>
       <c r="X16">
-        <v>0.0023901993389608594</v>
+        <v>0.0019384866396817027</v>
       </c>
       <c r="Y16">
-        <v>1.5968090396671248e-005</v>
+        <v>6.3145433704369096e-006</v>
       </c>
       <c r="Z16">
-        <v>-0.00029757047602522503</v>
+        <v>0.00016328784365597128</v>
       </c>
       <c r="AA16">
-        <v>-0.0001306359182356536</v>
+        <v>9.7168174261729262e-005</v>
       </c>
       <c r="AB16">
-        <v>0.00087842371300339821</v>
+        <v>0.00067557568898510062</v>
       </c>
       <c r="AC16">
-        <v>0.0017707378709228166</v>
+        <v>0.0014550183227278718</v>
       </c>
       <c r="AD16">
-        <v>0.00088833534944392429</v>
+        <v>0.00071826402334882551</v>
       </c>
       <c r="AE16">
-        <v>-0.0018535689733727673</v>
+        <v>-0.0018778864500470847</v>
       </c>
     </row>
     <row r="17">
@@ -1866,94 +1992,94 @@
         <v>46</v>
       </c>
       <c r="B17">
-        <v>0.0030311534920225503</v>
+        <v>0.083430512868320011</v>
       </c>
       <c r="C17">
-        <v>3.371067614290426e-005</v>
+        <v>1.7099121102368571e-005</v>
       </c>
       <c r="D17">
-        <v>-1.6643981312167935e-005</v>
+        <v>-1.5698619995628402e-005</v>
       </c>
       <c r="E17">
-        <v>1.2821859060781969e-007</v>
+        <v>1.507211718526614e-007</v>
       </c>
       <c r="F17">
-        <v>-3.3272320010768213e-005</v>
+        <v>-6.4056763191177733e-005</v>
       </c>
       <c r="G17">
-        <v>0.0001576780104881896</v>
+        <v>-1.2063648055053803e-005</v>
       </c>
       <c r="H17">
-        <v>-0.00020507560406223687</v>
+        <v>-0.00013490525612469735</v>
       </c>
       <c r="I17">
-        <v>-0.0002448243328716752</v>
+        <v>-0.00016493373991818833</v>
       </c>
       <c r="J17">
-        <v>-0.00028238373315389939</v>
+        <v>-0.00010070621767282838</v>
       </c>
       <c r="K17">
-        <v>-0.0002771351175657904</v>
+        <v>-0.00024022414306767672</v>
       </c>
       <c r="L17">
-        <v>-0.00025159069364695481</v>
+        <v>-0.00013063667400963256</v>
       </c>
       <c r="M17">
-        <v>0.00012882058694468668</v>
+        <v>0.00012084038355714664</v>
       </c>
       <c r="N17">
-        <v>0.0022503269229464306</v>
+        <v>0.0018340347529120743</v>
       </c>
       <c r="O17">
-        <v>0.002199639520438289</v>
+        <v>0.0017861380338508532</v>
       </c>
       <c r="P17">
-        <v>0.0021956071828246348</v>
+        <v>0.0017854293469072237</v>
       </c>
       <c r="Q17">
-        <v>0.0022365263444139682</v>
+        <v>0.001798450560788298</v>
       </c>
       <c r="R17">
-        <v>0.0050893390245263584</v>
+        <v>0.0035663398016754192</v>
       </c>
       <c r="S17">
-        <v>0.0021190929733722308</v>
+        <v>0.001739678930516151</v>
       </c>
       <c r="T17">
-        <v>0.0021862910279679638</v>
+        <v>0.0017782428570494017</v>
       </c>
       <c r="U17">
-        <v>0.0022516074075661194</v>
+        <v>0.001829699845684881</v>
       </c>
       <c r="V17">
-        <v>0.0022584602951255554</v>
+        <v>0.001837382040412794</v>
       </c>
       <c r="W17">
-        <v>0.002254751833246897</v>
+        <v>0.0018362574114476967</v>
       </c>
       <c r="X17">
-        <v>0.0022441461683670541</v>
+        <v>0.001837029668770467</v>
       </c>
       <c r="Y17">
-        <v>1.3723115086770813e-005</v>
+        <v>1.4089730128735995e-005</v>
       </c>
       <c r="Z17">
-        <v>-0.00011562808942733968</v>
+        <v>-4.5059995650800918e-005</v>
       </c>
       <c r="AA17">
-        <v>0.00012086393746250557</v>
+        <v>-1.5300692397164146e-005</v>
       </c>
       <c r="AB17">
-        <v>0.00056622743970303688</v>
+        <v>0.00040403724686922417</v>
       </c>
       <c r="AC17">
-        <v>0.0017240727322733278</v>
+        <v>0.0013912701132070184</v>
       </c>
       <c r="AD17">
-        <v>0.00048769848131170767</v>
+        <v>0.00044628487521253631</v>
       </c>
       <c r="AE17">
-        <v>-0.0018856426168847146</v>
+        <v>-0.0015644681178019959</v>
       </c>
     </row>
     <row r="18">
@@ -1961,94 +2087,94 @@
         <v>47</v>
       </c>
       <c r="B18">
-        <v>-0.10968321251233076</v>
+        <v>0.01375897331466143</v>
       </c>
       <c r="C18">
-        <v>-7.9844343404750182e-005</v>
+        <v>-3.0328507822277215e-005</v>
       </c>
       <c r="D18">
-        <v>5.8307866221793847e-006</v>
+        <v>6.5940972467318243e-006</v>
       </c>
       <c r="E18">
-        <v>-1.9439998583913155e-007</v>
+        <v>-1.6087846390182722e-007</v>
       </c>
       <c r="F18">
-        <v>6.7365303395574129e-005</v>
+        <v>4.7535347449882259e-005</v>
       </c>
       <c r="G18">
-        <v>-2.4178292399237043e-005</v>
+        <v>9.0440677329032035e-005</v>
       </c>
       <c r="H18">
-        <v>-0.00018479037067188676</v>
+        <v>-6.255623012722453e-005</v>
       </c>
       <c r="I18">
-        <v>-4.9582572285289389e-006</v>
+        <v>-7.5177398729195117e-005</v>
       </c>
       <c r="J18">
-        <v>-0.00013616593647829611</v>
+        <v>-2.6495174243555426e-005</v>
       </c>
       <c r="K18">
-        <v>-0.00023203110102269818</v>
+        <v>-0.00018975483061341424</v>
       </c>
       <c r="L18">
-        <v>-3.6497441578182439e-005</v>
+        <v>-9.5690091485296606e-006</v>
       </c>
       <c r="M18">
-        <v>3.6943146817129961e-005</v>
+        <v>0.00012922150030050665</v>
       </c>
       <c r="N18">
-        <v>0.0022710689083376562</v>
+        <v>0.0018725835791016201</v>
       </c>
       <c r="O18">
-        <v>0.0022059064598339115</v>
+        <v>0.0018092565681819403</v>
       </c>
       <c r="P18">
-        <v>0.0021853965545233752</v>
+        <v>0.0018073753641673839</v>
       </c>
       <c r="Q18">
-        <v>0.0022457477768828556</v>
+        <v>0.0018243710793423864</v>
       </c>
       <c r="R18">
-        <v>0.0021190929733722308</v>
+        <v>0.001739678930516151</v>
       </c>
       <c r="S18">
-        <v>0.0053262038021693004</v>
+        <v>0.0037095616779116891</v>
       </c>
       <c r="T18">
-        <v>0.0022262666216429413</v>
+        <v>0.00182399791386061</v>
       </c>
       <c r="U18">
-        <v>0.0022776245691880641</v>
+        <v>0.0018662757412578907</v>
       </c>
       <c r="V18">
-        <v>0.00228875944307939</v>
+        <v>0.0018785095631817534</v>
       </c>
       <c r="W18">
-        <v>0.0022907244623124878</v>
+        <v>0.0018822879770907354</v>
       </c>
       <c r="X18">
-        <v>0.0022916245428352242</v>
+        <v>0.0018787792796622689</v>
       </c>
       <c r="Y18">
-        <v>-1.7424654538458882e-005</v>
+        <v>-2.2513379163553615e-006</v>
       </c>
       <c r="Z18">
-        <v>-0.00012639591127056114</v>
+        <v>0.00011314794377810628</v>
       </c>
       <c r="AA18">
-        <v>0.00016946380782861646</v>
+        <v>0.00016491585443121259</v>
       </c>
       <c r="AB18">
-        <v>0.00087656963168953835</v>
+        <v>0.00064400981060616755</v>
       </c>
       <c r="AC18">
-        <v>0.0016623791013318113</v>
+        <v>0.0013388299758837949</v>
       </c>
       <c r="AD18">
-        <v>0.00059793389975717765</v>
+        <v>0.00058790059018297403</v>
       </c>
       <c r="AE18">
-        <v>-0.0018805984434090289</v>
+        <v>-0.0018646643802990926</v>
       </c>
     </row>
     <row r="19">
@@ -2056,94 +2182,94 @@
         <v>48</v>
       </c>
       <c r="B19">
-        <v>-0.061035660867585474</v>
+        <v>0.00087323625668051473</v>
       </c>
       <c r="C19">
-        <v>5.0363820741853534e-005</v>
+        <v>8.4534489213047948e-007</v>
       </c>
       <c r="D19">
-        <v>-1.9325727017326707e-006</v>
+        <v>-6.6630291446318716e-006</v>
       </c>
       <c r="E19">
-        <v>-8.0307127386476586e-009</v>
+        <v>6.9441089088250667e-008</v>
       </c>
       <c r="F19">
-        <v>2.6094426833276458e-005</v>
+        <v>3.48365017487001e-005</v>
       </c>
       <c r="G19">
-        <v>0.00038106740814587302</v>
+        <v>0.0002627165529270335</v>
       </c>
       <c r="H19">
-        <v>-9.9085484095743476e-005</v>
+        <v>-1.1340074954582996e-005</v>
       </c>
       <c r="I19">
-        <v>-1.696163585917967e-005</v>
+        <v>-3.7764651263490212e-005</v>
       </c>
       <c r="J19">
-        <v>4.8198850616078715e-005</v>
+        <v>3.0848422186911502e-006</v>
       </c>
       <c r="K19">
-        <v>-2.5317213062155011e-005</v>
+        <v>-0.00011799478354853178</v>
       </c>
       <c r="L19">
-        <v>4.8213566854139116e-005</v>
+        <v>3.7120588287913579e-005</v>
       </c>
       <c r="M19">
-        <v>0.00014092799565458759</v>
+        <v>0.00010383510948237991</v>
       </c>
       <c r="N19">
-        <v>0.0023500422317761292</v>
+        <v>0.0019238644309188719</v>
       </c>
       <c r="O19">
-        <v>0.0022439203929961685</v>
+        <v>0.0018457705974611487</v>
       </c>
       <c r="P19">
-        <v>0.0022546484689437581</v>
+        <v>0.0018483342467368971</v>
       </c>
       <c r="Q19">
-        <v>0.0022945497834549002</v>
+        <v>0.0018717626228667299</v>
       </c>
       <c r="R19">
-        <v>0.0021862910279679638</v>
+        <v>0.0017782428570494017</v>
       </c>
       <c r="S19">
-        <v>0.0022262666216429413</v>
+        <v>0.00182399791386061</v>
       </c>
       <c r="T19">
-        <v>0.0040430071569087043</v>
+        <v>0.0030867368860210648</v>
       </c>
       <c r="U19">
-        <v>0.0023217182155871032</v>
+        <v>0.001912059002658985</v>
       </c>
       <c r="V19">
-        <v>0.0023376851475078383</v>
+        <v>0.0019212699725627831</v>
       </c>
       <c r="W19">
-        <v>0.0023319078747728343</v>
+        <v>0.0019190164208186741</v>
       </c>
       <c r="X19">
-        <v>0.0023440211281454248</v>
+        <v>0.0019153738915727659</v>
       </c>
       <c r="Y19">
-        <v>-1.2297362592883067e-005</v>
+        <v>6.368026468001582e-007</v>
       </c>
       <c r="Z19">
-        <v>-0.00017518121049973291</v>
+        <v>3.5082384028551229e-005</v>
       </c>
       <c r="AA19">
-        <v>1.9128976807980378e-005</v>
+        <v>3.8049296525610613e-006</v>
       </c>
       <c r="AB19">
-        <v>0.0010206844507923544</v>
+        <v>0.00072414005970208167</v>
       </c>
       <c r="AC19">
-        <v>0.0018909598129262456</v>
+        <v>0.0015284252008668465</v>
       </c>
       <c r="AD19">
-        <v>0.0008509515812796703</v>
+        <v>0.00073624005854755004</v>
       </c>
       <c r="AE19">
-        <v>-0.0021533469062982036</v>
+        <v>-0.0018408083790633642</v>
       </c>
     </row>
     <row r="20">
@@ -2151,94 +2277,94 @@
         <v>49</v>
       </c>
       <c r="B20">
-        <v>0.080700412232011479</v>
+        <v>0.12026412158903714</v>
       </c>
       <c r="C20">
-        <v>0.00011181013736597909</v>
+        <v>5.0149445914071235e-006</v>
       </c>
       <c r="D20">
-        <v>8.9406633026548055e-007</v>
+        <v>-3.2517303090065877e-006</v>
       </c>
       <c r="E20">
-        <v>-1.5962950008511749e-007</v>
+        <v>-5.8316378676224358e-008</v>
       </c>
       <c r="F20">
-        <v>-0.0002206694084850991</v>
+        <v>-0.00011435097191886151</v>
       </c>
       <c r="G20">
-        <v>0.00011310756309257089</v>
+        <v>0.00012234323042650217</v>
       </c>
       <c r="H20">
-        <v>-2.5202366787791214e-005</v>
+        <v>-6.6575702848126195e-006</v>
       </c>
       <c r="I20">
-        <v>-0.00018164059965022759</v>
+        <v>-0.00015046189828561739</v>
       </c>
       <c r="J20">
-        <v>-0.00015198363930017059</v>
+        <v>-7.3213144093769392e-005</v>
       </c>
       <c r="K20">
-        <v>-0.0002320829359623218</v>
+        <v>-0.00018907793922641122</v>
       </c>
       <c r="L20">
-        <v>-0.00016727729067834366</v>
+        <v>-7.8096255359465933e-005</v>
       </c>
       <c r="M20">
-        <v>-4.7977738492479237e-005</v>
+        <v>2.9972044603723022e-005</v>
       </c>
       <c r="N20">
-        <v>0.0024160756257084982</v>
+        <v>0.0019803172633022555</v>
       </c>
       <c r="O20">
-        <v>0.0023192034308985522</v>
+        <v>0.0018994078046249232</v>
       </c>
       <c r="P20">
-        <v>0.0023349185794742408</v>
+        <v>0.0019072967697103531</v>
       </c>
       <c r="Q20">
-        <v>0.0024078495046351922</v>
+        <v>0.0019370075428943655</v>
       </c>
       <c r="R20">
-        <v>0.0022516074075661194</v>
+        <v>0.001829699845684881</v>
       </c>
       <c r="S20">
-        <v>0.0022776245691880641</v>
+        <v>0.0018662757412578907</v>
       </c>
       <c r="T20">
-        <v>0.0023217182155871032</v>
+        <v>0.001912059002658985</v>
       </c>
       <c r="U20">
-        <v>0.0053355167310207311</v>
+        <v>0.0037904995446163391</v>
       </c>
       <c r="V20">
-        <v>0.0024335694644551042</v>
+        <v>0.0019900058134962851</v>
       </c>
       <c r="W20">
-        <v>0.0024214952238894227</v>
+        <v>0.0019840436114912765</v>
       </c>
       <c r="X20">
-        <v>0.0024223248990294767</v>
+        <v>0.0019779826068696701</v>
       </c>
       <c r="Y20">
-        <v>-8.9728252839167076e-006</v>
+        <v>-5.0754029938472107e-007</v>
       </c>
       <c r="Z20">
-        <v>-0.00016740583698949949</v>
+        <v>1.6352757766505328e-005</v>
       </c>
       <c r="AA20">
-        <v>0.00023988605909825258</v>
+        <v>0.00011462089406322319</v>
       </c>
       <c r="AB20">
-        <v>0.00096221091321998338</v>
+        <v>0.00073632410566774257</v>
       </c>
       <c r="AC20">
-        <v>0.001915420241291029</v>
+        <v>0.001548235868791928</v>
       </c>
       <c r="AD20">
-        <v>0.0010919000695680347</v>
+        <v>0.00087546481282404793</v>
       </c>
       <c r="AE20">
-        <v>-0.0019120563790466266</v>
+        <v>-0.0016740438784194501</v>
       </c>
     </row>
     <row r="21">
@@ -2246,94 +2372,94 @@
         <v>50</v>
       </c>
       <c r="B21">
-        <v>-0.051506093769564408</v>
+        <v>-0.052654009287698401</v>
       </c>
       <c r="C21">
-        <v>1.402536366660787e-006</v>
+        <v>-5.0511909620676163e-005</v>
       </c>
       <c r="D21">
-        <v>-1.2095390647407162e-006</v>
+        <v>-1.3932254770880636e-005</v>
       </c>
       <c r="E21">
-        <v>-1.2355250592429246e-007</v>
+        <v>8.7460398018870337e-008</v>
       </c>
       <c r="F21">
-        <v>-0.00011589134803618127</v>
+        <v>-4.876120524032444e-005</v>
       </c>
       <c r="G21">
-        <v>0.00010918605240317506</v>
+        <v>7.1748102154313822e-005</v>
       </c>
       <c r="H21">
-        <v>1.6753080447032276e-005</v>
+        <v>3.0162388696468919e-005</v>
       </c>
       <c r="I21">
-        <v>-0.0001131500937367972</v>
+        <v>-0.00010391691635463617</v>
       </c>
       <c r="J21">
-        <v>1.8933567812122465e-005</v>
+        <v>-3.0082659815623865e-006</v>
       </c>
       <c r="K21">
-        <v>5.2008275478468251e-005</v>
+        <v>-6.5086958698556095e-005</v>
       </c>
       <c r="L21">
-        <v>0.00014444590519336817</v>
+        <v>0.0001258339832742564</v>
       </c>
       <c r="M21">
-        <v>0.00030198831036498349</v>
+        <v>0.00022510642538022094</v>
       </c>
       <c r="N21">
-        <v>0.0024703939841392332</v>
+        <v>0.002018441294097461</v>
       </c>
       <c r="O21">
-        <v>0.0023516834042621318</v>
+        <v>0.0019215069192266613</v>
       </c>
       <c r="P21">
-        <v>0.0023766806181526141</v>
+        <v>0.001934025180458228</v>
       </c>
       <c r="Q21">
-        <v>0.0024218993067849819</v>
+        <v>0.0019535847112462862</v>
       </c>
       <c r="R21">
-        <v>0.0022584602951255554</v>
+        <v>0.001837382040412794</v>
       </c>
       <c r="S21">
-        <v>0.00228875944307939</v>
+        <v>0.0018785095631817534</v>
       </c>
       <c r="T21">
-        <v>0.0023376851475078383</v>
+        <v>0.0019212699725627831</v>
       </c>
       <c r="U21">
-        <v>0.0024335694644551042</v>
+        <v>0.0019900058134962851</v>
       </c>
       <c r="V21">
-        <v>0.0053873697323260118</v>
+        <v>0.0038260819724496888</v>
       </c>
       <c r="W21">
-        <v>0.0024465071428011382</v>
+        <v>0.0020048815867309937</v>
       </c>
       <c r="X21">
-        <v>0.0024737820077519587</v>
+        <v>0.0020162680250712574</v>
       </c>
       <c r="Y21">
-        <v>-1.4306694862061765e-006</v>
+        <v>1.9422227837762455e-006</v>
       </c>
       <c r="Z21">
-        <v>-0.00011224418114208143</v>
+        <v>5.4232835966447086e-005</v>
       </c>
       <c r="AA21">
-        <v>-5.1395325397734614e-006</v>
+        <v>1.766392955714214e-005</v>
       </c>
       <c r="AB21">
-        <v>0.0010457836207411063</v>
+        <v>0.00080179920816460552</v>
       </c>
       <c r="AC21">
-        <v>0.0019936190015478589</v>
+        <v>0.0015953165708555532</v>
       </c>
       <c r="AD21">
-        <v>0.001054379256513218</v>
+        <v>0.00087030887093566276</v>
       </c>
       <c r="AE21">
-        <v>-0.0022749513191838806</v>
+        <v>-0.0017070273869676088</v>
       </c>
     </row>
     <row r="22">
@@ -2341,94 +2467,94 @@
         <v>51</v>
       </c>
       <c r="B22">
-        <v>0.12254009603103537</v>
+        <v>0.11290088281738649</v>
       </c>
       <c r="C22">
-        <v>0.00010647482951627222</v>
+        <v>3.4798197587393009e-005</v>
       </c>
       <c r="D22">
-        <v>1.3349872169014538e-005</v>
+        <v>1.1083022285874212e-005</v>
       </c>
       <c r="E22">
-        <v>-3.5065492590082775e-007</v>
+        <v>-2.6876275158854978e-007</v>
       </c>
       <c r="F22">
-        <v>-4.8241457278754929e-005</v>
+        <v>4.7359590728425342e-006</v>
       </c>
       <c r="G22">
-        <v>0.00018791140235520796</v>
+        <v>0.00010499126578968995</v>
       </c>
       <c r="H22">
-        <v>-4.5216342418121901e-005</v>
+        <v>-2.7520283551164815e-005</v>
       </c>
       <c r="I22">
-        <v>-2.7302839536066633e-006</v>
+        <v>-0.00010291695752616447</v>
       </c>
       <c r="J22">
-        <v>3.7672229702493017e-005</v>
+        <v>-2.6398395451710617e-005</v>
       </c>
       <c r="K22">
-        <v>4.9088773089981004e-006</v>
+        <v>-0.00013909323796086484</v>
       </c>
       <c r="L22">
-        <v>7.069809087567006e-005</v>
+        <v>2.7864556993159768e-005</v>
       </c>
       <c r="M22">
-        <v>0.00023770638890161628</v>
+        <v>0.00015809072673620957</v>
       </c>
       <c r="N22">
-        <v>0.002424054473727991</v>
+        <v>0.0019890429611168635</v>
       </c>
       <c r="O22">
-        <v>0.0023409811520170806</v>
+        <v>0.0019145477730492535</v>
       </c>
       <c r="P22">
-        <v>0.0023421768120842849</v>
+        <v>0.001909813566726223</v>
       </c>
       <c r="Q22">
-        <v>0.0023986616794864656</v>
+        <v>0.0019398401413710941</v>
       </c>
       <c r="R22">
-        <v>0.002254751833246897</v>
+        <v>0.0018362574114476967</v>
       </c>
       <c r="S22">
-        <v>0.0022907244623124878</v>
+        <v>0.0018822879770907354</v>
       </c>
       <c r="T22">
-        <v>0.0023319078747728343</v>
+        <v>0.0019190164208186741</v>
       </c>
       <c r="U22">
-        <v>0.0024214952238894227</v>
+        <v>0.0019840436114912765</v>
       </c>
       <c r="V22">
-        <v>0.0024465071428011382</v>
+        <v>0.0020048815867309937</v>
       </c>
       <c r="W22">
-        <v>0.0047221972899465494</v>
+        <v>0.0036943915078950684</v>
       </c>
       <c r="X22">
-        <v>0.0024545073133004102</v>
+        <v>0.0020093419448924512</v>
       </c>
       <c r="Y22">
-        <v>7.5782696733750216e-006</v>
+        <v>1.3645074303485147e-005</v>
       </c>
       <c r="Z22">
-        <v>-0.00012997078706766162</v>
+        <v>2.9061857313193999e-005</v>
       </c>
       <c r="AA22">
-        <v>4.3240879558507542e-005</v>
+        <v>8.982112718316441e-007</v>
       </c>
       <c r="AB22">
-        <v>0.0011133018826939927</v>
+        <v>0.00079715791127299093</v>
       </c>
       <c r="AC22">
-        <v>0.0019484267750705783</v>
+        <v>0.0015365380698195137</v>
       </c>
       <c r="AD22">
-        <v>0.0010319981829071002</v>
+        <v>0.00088274146430406312</v>
       </c>
       <c r="AE22">
-        <v>-0.0026943890463013466</v>
+        <v>-0.0022835670060588112</v>
       </c>
     </row>
     <row r="23">
@@ -2436,94 +2562,94 @@
         <v>52</v>
       </c>
       <c r="B23">
-        <v>-0.11648585936585516</v>
+        <v>-0.14193987537281774</v>
       </c>
       <c r="C23">
-        <v>3.4137192050686459e-005</v>
+        <v>1.7216175381888854e-006</v>
       </c>
       <c r="D23">
-        <v>-1.1630343278863121e-005</v>
+        <v>-2.1259898289665994e-005</v>
       </c>
       <c r="E23">
-        <v>3.1396265845078558e-008</v>
+        <v>1.9644426974121556e-007</v>
       </c>
       <c r="F23">
-        <v>3.0755205554420855e-005</v>
+        <v>2.5108937682334371e-005</v>
       </c>
       <c r="G23">
-        <v>9.1101634324794846e-005</v>
+        <v>-7.1899077176939045e-005</v>
       </c>
       <c r="H23">
-        <v>-9.10004407589011e-005</v>
+        <v>-4.6185364710916652e-005</v>
       </c>
       <c r="I23">
-        <v>-0.00010408440354341434</v>
+        <v>-8.5188331701035493e-005</v>
       </c>
       <c r="J23">
-        <v>5.232867210725866e-005</v>
+        <v>-1.2586627845200503e-005</v>
       </c>
       <c r="K23">
-        <v>-4.1399863636967186e-005</v>
+        <v>-0.00014582194326230764</v>
       </c>
       <c r="L23">
-        <v>8.0542994243797822e-005</v>
+        <v>2.6230457302646622e-005</v>
       </c>
       <c r="M23">
-        <v>0.00031828192757619826</v>
+        <v>0.00019816776173935818</v>
       </c>
       <c r="N23">
-        <v>0.0024694059302184674</v>
+        <v>0.0020046205080913432</v>
       </c>
       <c r="O23">
-        <v>0.0023395557341882129</v>
+        <v>0.0019116902677907173</v>
       </c>
       <c r="P23">
-        <v>0.0023502862408103444</v>
+        <v>0.0019161393515072062</v>
       </c>
       <c r="Q23">
-        <v>0.0023901993389608594</v>
+        <v>0.0019384866396817027</v>
       </c>
       <c r="R23">
-        <v>0.0022441461683670541</v>
+        <v>0.001837029668770467</v>
       </c>
       <c r="S23">
-        <v>0.0022916245428352242</v>
+        <v>0.0018787792796622689</v>
       </c>
       <c r="T23">
-        <v>0.0023440211281454248</v>
+        <v>0.0019153738915727659</v>
       </c>
       <c r="U23">
-        <v>0.0024223248990294767</v>
+        <v>0.0019779826068696701</v>
       </c>
       <c r="V23">
-        <v>0.0024737820077519587</v>
+        <v>0.0020162680250712574</v>
       </c>
       <c r="W23">
-        <v>0.0024545073133004102</v>
+        <v>0.0020093419448924512</v>
       </c>
       <c r="X23">
-        <v>0.004987326808915977</v>
+        <v>0.0039010194698893136</v>
       </c>
       <c r="Y23">
-        <v>-1.1229574756527118e-006</v>
+        <v>3.9444742720466316e-006</v>
       </c>
       <c r="Z23">
-        <v>-0.0002069333340413066</v>
+        <v>-1.8932598842984601e-005</v>
       </c>
       <c r="AA23">
-        <v>4.9921226968485454e-005</v>
+        <v>0.00014806287211524644</v>
       </c>
       <c r="AB23">
-        <v>0.0011263123856762949</v>
+        <v>0.00082604732839622655</v>
       </c>
       <c r="AC23">
-        <v>0.0020138036249790613</v>
+        <v>0.0015990996126208459</v>
       </c>
       <c r="AD23">
-        <v>0.0010770280307167326</v>
+        <v>0.00087295009005951946</v>
       </c>
       <c r="AE23">
-        <v>-0.0021877738494345011</v>
+        <v>-0.0016385416624912653</v>
       </c>
     </row>
     <row r="24">
@@ -2531,94 +2657,94 @@
         <v>53</v>
       </c>
       <c r="B24">
-        <v>-0.00024604709787195614</v>
+        <v>-0.014371352468363248</v>
       </c>
       <c r="C24">
-        <v>-4.9311556265419157e-006</v>
+        <v>4.3510916668879415e-007</v>
       </c>
       <c r="D24">
-        <v>-7.1365286076810995e-008</v>
+        <v>4.3065940634842053e-007</v>
       </c>
       <c r="E24">
-        <v>4.2307766369329244e-010</v>
+        <v>-5.9031309051208174e-009</v>
       </c>
       <c r="F24">
-        <v>4.408407015140093e-006</v>
+        <v>3.127331364818152e-006</v>
       </c>
       <c r="G24">
-        <v>2.8441285669955818e-005</v>
+        <v>1.7621125931232957e-005</v>
       </c>
       <c r="H24">
-        <v>1.8184367273823686e-006</v>
+        <v>2.5554626613031136e-006</v>
       </c>
       <c r="I24">
-        <v>-1.9514786708447915e-006</v>
+        <v>1.2247320099477611e-006</v>
       </c>
       <c r="J24">
-        <v>4.0059845813835722e-006</v>
+        <v>9.7474185366669804e-006</v>
       </c>
       <c r="K24">
-        <v>2.0592966853558731e-005</v>
+        <v>1.0886798474500688e-005</v>
       </c>
       <c r="L24">
-        <v>3.7457318080623897e-006</v>
+        <v>2.1599491292225131e-006</v>
       </c>
       <c r="M24">
-        <v>5.8126364268046803e-007</v>
+        <v>4.6991094893658603e-006</v>
       </c>
       <c r="N24">
-        <v>3.0748892442776713e-006</v>
+        <v>4.129064415616071e-006</v>
       </c>
       <c r="O24">
-        <v>-8.8155477690423267e-007</v>
+        <v>2.6762695430093583e-006</v>
       </c>
       <c r="P24">
-        <v>-4.4625313866024168e-006</v>
+        <v>-3.0973295030152533e-006</v>
       </c>
       <c r="Q24">
-        <v>1.5968090396671248e-005</v>
+        <v>6.3145433704369096e-006</v>
       </c>
       <c r="R24">
-        <v>1.3723115086770813e-005</v>
+        <v>1.4089730128735995e-005</v>
       </c>
       <c r="S24">
-        <v>-1.7424654538458882e-005</v>
+        <v>-2.2513379163553615e-006</v>
       </c>
       <c r="T24">
-        <v>-1.2297362592883067e-005</v>
+        <v>6.368026468001582e-007</v>
       </c>
       <c r="U24">
-        <v>-8.9728252839167076e-006</v>
+        <v>-5.0754029938472107e-007</v>
       </c>
       <c r="V24">
-        <v>-1.4306694862061765e-006</v>
+        <v>1.9422227837762455e-006</v>
       </c>
       <c r="W24">
-        <v>7.5782696733750216e-006</v>
+        <v>1.3645074303485147e-005</v>
       </c>
       <c r="X24">
-        <v>-1.1229574756527118e-006</v>
+        <v>3.9444742720466316e-006</v>
       </c>
       <c r="Y24">
-        <v>2.5413896785198515e-005</v>
+        <v>1.8027511475919922e-005</v>
       </c>
       <c r="Z24">
-        <v>-0.00011057154138606457</v>
+        <v>-8.4660726645259987e-005</v>
       </c>
       <c r="AA24">
-        <v>-0.00013304427233899914</v>
+        <v>-0.0001015508511481018</v>
       </c>
       <c r="AB24">
-        <v>-7.7920272591807077e-006</v>
+        <v>-7.4846921501205415e-006</v>
       </c>
       <c r="AC24">
-        <v>-1.1253326945393145e-005</v>
+        <v>-1.8065873992352934e-006</v>
       </c>
       <c r="AD24">
-        <v>-1.6836646099729354e-005</v>
+        <v>-1.3824487141929871e-005</v>
       </c>
       <c r="AE24">
-        <v>-0.00040411488211068556</v>
+        <v>-0.00029457879358745463</v>
       </c>
     </row>
     <row r="25">
@@ -2626,94 +2752,94 @@
         <v>54</v>
       </c>
       <c r="B25">
-        <v>0.13874857548682401</v>
+        <v>0.10378211570126752</v>
       </c>
       <c r="C25">
-        <v>-1.0787907954078364e-005</v>
+        <v>2.5992361577565189e-005</v>
       </c>
       <c r="D25">
-        <v>-4.2550648915218493e-006</v>
+        <v>8.3165932298986825e-006</v>
       </c>
       <c r="E25">
-        <v>7.5553596077281995e-008</v>
+        <v>-1.0269590096004158e-007</v>
       </c>
       <c r="F25">
-        <v>7.6141975321154408e-005</v>
+        <v>7.0155026190269024e-005</v>
       </c>
       <c r="G25">
-        <v>-8.8374269448711788e-005</v>
+        <v>6.5167573245184998e-005</v>
       </c>
       <c r="H25">
-        <v>-0.00015674405732034628</v>
+        <v>-5.6753658035689838e-006</v>
       </c>
       <c r="I25">
-        <v>-0.00017436455763986363</v>
+        <v>-9.927257200495628e-005</v>
       </c>
       <c r="J25">
-        <v>-0.00015350412130647688</v>
+        <v>-7.879259861479944e-005</v>
       </c>
       <c r="K25">
-        <v>-0.00034517134978559211</v>
+        <v>-7.1105620269609564e-005</v>
       </c>
       <c r="L25">
-        <v>-0.00013816069335462628</v>
+        <v>-2.6241413020190838e-005</v>
       </c>
       <c r="M25">
-        <v>-9.4030945990691115e-005</v>
+        <v>1.0752889510549847e-005</v>
       </c>
       <c r="N25">
-        <v>-0.0001827363655809362</v>
+        <v>-2.3470979477307737e-006</v>
       </c>
       <c r="O25">
-        <v>-0.00023289918249270994</v>
+        <v>-1.1188786660084731e-005</v>
       </c>
       <c r="P25">
-        <v>-0.0002511081884967822</v>
+        <v>-2.3869197445764746e-005</v>
       </c>
       <c r="Q25">
-        <v>-0.00029757047602522503</v>
+        <v>0.00016328784365597128</v>
       </c>
       <c r="R25">
-        <v>-0.00011562808942733968</v>
+        <v>-4.5059995650800918e-005</v>
       </c>
       <c r="S25">
-        <v>-0.00012639591127056114</v>
+        <v>0.00011314794377810628</v>
       </c>
       <c r="T25">
-        <v>-0.00017518121049973291</v>
+        <v>3.5082384028551229e-005</v>
       </c>
       <c r="U25">
-        <v>-0.00016740583698949949</v>
+        <v>1.6352757766505328e-005</v>
       </c>
       <c r="V25">
-        <v>-0.00011224418114208143</v>
+        <v>5.4232835966447086e-005</v>
       </c>
       <c r="W25">
-        <v>-0.00012997078706766162</v>
+        <v>2.9061857313193999e-005</v>
       </c>
       <c r="X25">
-        <v>-0.0002069333340413066</v>
+        <v>-1.8932598842984601e-005</v>
       </c>
       <c r="Y25">
-        <v>-0.00011057154138606457</v>
+        <v>-8.4660726645259987e-005</v>
       </c>
       <c r="Z25">
-        <v>0.0031623523352178285</v>
+        <v>0.0027775111192345557</v>
       </c>
       <c r="AA25">
-        <v>0.00080212533320053541</v>
+        <v>0.00064287090736212698</v>
       </c>
       <c r="AB25">
-        <v>-7.4614833269879503e-005</v>
+        <v>9.9414999214088133e-006</v>
       </c>
       <c r="AC25">
-        <v>-8.0756431916998556e-005</v>
+        <v>-2.2760602843111617e-005</v>
       </c>
       <c r="AD25">
-        <v>0.00029099560502216361</v>
+        <v>0.00010981391961407792</v>
       </c>
       <c r="AE25">
-        <v>0.0018795641470831887</v>
+        <v>0.00095215130571860954</v>
       </c>
     </row>
     <row r="26">
@@ -2721,94 +2847,94 @@
         <v>55</v>
       </c>
       <c r="B26">
-        <v>0.10785657860263786</v>
+        <v>0.11318186006237782</v>
       </c>
       <c r="C26">
-        <v>2.2157136138186527e-005</v>
+        <v>-1.1311925385792038e-005</v>
       </c>
       <c r="D26">
-        <v>-7.2023131823159672e-006</v>
+        <v>-1.0422504174754791e-005</v>
       </c>
       <c r="E26">
-        <v>1.0187974634759229e-007</v>
+        <v>1.2941865176107009e-007</v>
       </c>
       <c r="F26">
-        <v>4.8533594174586368e-005</v>
+        <v>1.3998868761168592e-005</v>
       </c>
       <c r="G26">
-        <v>-9.9243764042209544e-005</v>
+        <v>-9.2359087810389386e-005</v>
       </c>
       <c r="H26">
-        <v>-0.00011260891038819504</v>
+        <v>-4.354247592255989e-005</v>
       </c>
       <c r="I26">
-        <v>-7.3580414676958905e-005</v>
+        <v>-5.7327223817469632e-005</v>
       </c>
       <c r="J26">
-        <v>-2.5530667434722922e-005</v>
+        <v>-0.00010586496222526029</v>
       </c>
       <c r="K26">
-        <v>-0.00014415966650339098</v>
+        <v>-7.9942168277313499e-005</v>
       </c>
       <c r="L26">
-        <v>5.0804757637224737e-005</v>
+        <v>-2.9939554312191023e-005</v>
       </c>
       <c r="M26">
-        <v>4.9218357950740272e-005</v>
+        <v>-8.6676086461380043e-005</v>
       </c>
       <c r="N26">
-        <v>-6.9913850603355959e-005</v>
+        <v>0.00011765798045203346</v>
       </c>
       <c r="O26">
-        <v>6.5058756591275592e-005</v>
+        <v>9.4007546094012021e-005</v>
       </c>
       <c r="P26">
-        <v>0.00029947993281955886</v>
+        <v>0.00017577533780991045</v>
       </c>
       <c r="Q26">
-        <v>-0.0001306359182356536</v>
+        <v>9.7168174261729262e-005</v>
       </c>
       <c r="R26">
-        <v>0.00012086393746250557</v>
+        <v>-1.5300692397164146e-005</v>
       </c>
       <c r="S26">
-        <v>0.00016946380782861646</v>
+        <v>0.00016491585443121259</v>
       </c>
       <c r="T26">
-        <v>1.9128976807980378e-005</v>
+        <v>3.8049296525610613e-006</v>
       </c>
       <c r="U26">
-        <v>0.00023988605909825258</v>
+        <v>0.00011462089406322319</v>
       </c>
       <c r="V26">
-        <v>-5.1395325397734614e-006</v>
+        <v>1.766392955714214e-005</v>
       </c>
       <c r="W26">
-        <v>4.3240879558507542e-005</v>
+        <v>8.982112718316441e-007</v>
       </c>
       <c r="X26">
-        <v>4.9921226968485454e-005</v>
+        <v>0.00014806287211524644</v>
       </c>
       <c r="Y26">
-        <v>-0.00013304427233899914</v>
+        <v>-0.0001015508511481018</v>
       </c>
       <c r="Z26">
-        <v>0.00080212533320053541</v>
+        <v>0.00064287090736212698</v>
       </c>
       <c r="AA26">
-        <v>0.0039361846467669713</v>
+        <v>0.003210355064493949</v>
       </c>
       <c r="AB26">
-        <v>-3.0594902941428114e-005</v>
+        <v>-1.9899305123151443e-005</v>
       </c>
       <c r="AC26">
-        <v>-8.8227677405194622e-005</v>
+        <v>-8.4009994281104079e-005</v>
       </c>
       <c r="AD26">
-        <v>-0.00013231673637799704</v>
+        <v>-0.00010669412571991392</v>
       </c>
       <c r="AE26">
-        <v>0.0019078209628953212</v>
+        <v>0.0015768513489849362</v>
       </c>
     </row>
     <row r="27">
@@ -2816,94 +2942,94 @@
         <v>56</v>
       </c>
       <c r="B27">
-        <v>-0.4121080261905975</v>
+        <v>-0.31069495622013166</v>
       </c>
       <c r="C27">
-        <v>5.4924177902638074e-005</v>
+        <v>2.7035304457427613e-006</v>
       </c>
       <c r="D27">
-        <v>-2.1692380901941304e-005</v>
+        <v>-3.2040262132371797e-005</v>
       </c>
       <c r="E27">
-        <v>3.4920146561629916e-007</v>
+        <v>4.7084054655794496e-007</v>
       </c>
       <c r="F27">
-        <v>0.00037316560902281</v>
+        <v>0.00021664488402021954</v>
       </c>
       <c r="G27">
-        <v>0.0004015496887424504</v>
+        <v>0.00025872316714480666</v>
       </c>
       <c r="H27">
-        <v>2.8270173464144902e-005</v>
+        <v>1.9561613223252963e-006</v>
       </c>
       <c r="I27">
-        <v>0.00010586853365773504</v>
+        <v>1.973981814903155e-005</v>
       </c>
       <c r="J27">
-        <v>0.0002592626601205239</v>
+        <v>0.00012648981397700909</v>
       </c>
       <c r="K27">
-        <v>0.00022971819166165124</v>
+        <v>0.00013654436429704105</v>
       </c>
       <c r="L27">
-        <v>0.0002119024471781087</v>
+        <v>0.00018114464637901395</v>
       </c>
       <c r="M27">
-        <v>4.9829191017414492e-005</v>
+        <v>9.3443646703452636e-005</v>
       </c>
       <c r="N27">
-        <v>0.0011140082769774341</v>
+        <v>0.00080254037552375133</v>
       </c>
       <c r="O27">
-        <v>0.00076409314393045</v>
+        <v>0.00059206281865317593</v>
       </c>
       <c r="P27">
-        <v>0.00075453485633682953</v>
+        <v>0.00060363137553947591</v>
       </c>
       <c r="Q27">
-        <v>0.00087842371300339821</v>
+        <v>0.00067557568898510062</v>
       </c>
       <c r="R27">
-        <v>0.00056622743970303688</v>
+        <v>0.00040403724686922417</v>
       </c>
       <c r="S27">
-        <v>0.00087656963168953835</v>
+        <v>0.00064400981060616755</v>
       </c>
       <c r="T27">
-        <v>0.0010206844507923544</v>
+        <v>0.00072414005970208167</v>
       </c>
       <c r="U27">
-        <v>0.00096221091321998338</v>
+        <v>0.00073632410566774257</v>
       </c>
       <c r="V27">
-        <v>0.0010457836207411063</v>
+        <v>0.00080179920816460552</v>
       </c>
       <c r="W27">
-        <v>0.0011133018826939927</v>
+        <v>0.00079715791127299093</v>
       </c>
       <c r="X27">
-        <v>0.0011263123856762949</v>
+        <v>0.00082604732839622655</v>
       </c>
       <c r="Y27">
-        <v>-7.7920272591807077e-006</v>
+        <v>-7.4846921501205415e-006</v>
       </c>
       <c r="Z27">
-        <v>-7.4614833269879503e-005</v>
+        <v>9.9414999214088133e-006</v>
       </c>
       <c r="AA27">
-        <v>-3.0594902941428114e-005</v>
+        <v>-1.9899305123151443e-005</v>
       </c>
       <c r="AB27">
-        <v>0.0031444734154494418</v>
+        <v>0.0020426987801256593</v>
       </c>
       <c r="AC27">
-        <v>0.0010481394483260284</v>
+        <v>0.00076994114663971741</v>
       </c>
       <c r="AD27">
-        <v>0.00072173979381726506</v>
+        <v>0.00053916853526174446</v>
       </c>
       <c r="AE27">
-        <v>-0.00116608861737214</v>
+        <v>-0.00050228298388007935</v>
       </c>
     </row>
     <row r="28">
@@ -2911,94 +3037,94 @@
         <v>57</v>
       </c>
       <c r="B28">
-        <v>-0.23613900227476614</v>
+        <v>-0.31343578890542889</v>
       </c>
       <c r="C28">
-        <v>-3.6713838358304692e-005</v>
+        <v>-4.7155783239187292e-005</v>
       </c>
       <c r="D28">
-        <v>-2.6876023877973063e-005</v>
+        <v>-4.6794344274689445e-005</v>
       </c>
       <c r="E28">
-        <v>3.1108552852123559e-007</v>
+        <v>6.0288966296993887e-007</v>
       </c>
       <c r="F28">
-        <v>0.00013942371223252866</v>
+        <v>0.00011817761217204723</v>
       </c>
       <c r="G28">
-        <v>0.00028220509488973962</v>
+        <v>0.00019792939553307039</v>
       </c>
       <c r="H28">
-        <v>2.4024677142782044e-006</v>
+        <v>-2.8951096470484963e-005</v>
       </c>
       <c r="I28">
-        <v>1.7808302128676477e-005</v>
+        <v>-4.7613551951191952e-005</v>
       </c>
       <c r="J28">
-        <v>0.00011721681639982173</v>
+        <v>7.6794854193834843e-005</v>
       </c>
       <c r="K28">
-        <v>0.00014697569960548783</v>
+        <v>3.154922896337958e-005</v>
       </c>
       <c r="L28">
-        <v>0.0001430421418352648</v>
+        <v>0.00012472314377554288</v>
       </c>
       <c r="M28">
-        <v>0.00019549808676047609</v>
+        <v>0.00015168487481170378</v>
       </c>
       <c r="N28">
-        <v>0.0022254238923909379</v>
+        <v>0.0017092684925013599</v>
       </c>
       <c r="O28">
-        <v>0.001884026264625467</v>
+        <v>0.0014903548817045602</v>
       </c>
       <c r="P28">
-        <v>0.0018407872377880709</v>
+        <v>0.0014376435382701508</v>
       </c>
       <c r="Q28">
-        <v>0.0017707378709228166</v>
+        <v>0.0014550183227278718</v>
       </c>
       <c r="R28">
-        <v>0.0017240727322733278</v>
+        <v>0.0013912701132070184</v>
       </c>
       <c r="S28">
-        <v>0.0016623791013318113</v>
+        <v>0.0013388299758837949</v>
       </c>
       <c r="T28">
-        <v>0.0018909598129262456</v>
+        <v>0.0015284252008668465</v>
       </c>
       <c r="U28">
-        <v>0.001915420241291029</v>
+        <v>0.001548235868791928</v>
       </c>
       <c r="V28">
-        <v>0.0019936190015478589</v>
+        <v>0.0015953165708555532</v>
       </c>
       <c r="W28">
-        <v>0.0019484267750705783</v>
+        <v>0.0015365380698195137</v>
       </c>
       <c r="X28">
-        <v>0.0020138036249790613</v>
+        <v>0.0015990996126208459</v>
       </c>
       <c r="Y28">
-        <v>-1.1253326945393145e-005</v>
+        <v>-1.8065873992352934e-006</v>
       </c>
       <c r="Z28">
-        <v>-8.0756431916998556e-005</v>
+        <v>-2.2760602843111617e-005</v>
       </c>
       <c r="AA28">
-        <v>-8.8227677405194622e-005</v>
+        <v>-8.4009994281104079e-005</v>
       </c>
       <c r="AB28">
-        <v>0.0010481394483260284</v>
+        <v>0.00076994114663971741</v>
       </c>
       <c r="AC28">
-        <v>0.0067294054282205406</v>
+        <v>0.0052345333337595959</v>
       </c>
       <c r="AD28">
-        <v>0.00098456111335186967</v>
+        <v>0.0007810954214260285</v>
       </c>
       <c r="AE28">
-        <v>-0.0015355488791964633</v>
+        <v>-0.0009054431432408284</v>
       </c>
     </row>
     <row r="29">
@@ -3006,94 +3132,94 @@
         <v>58</v>
       </c>
       <c r="B29">
-        <v>-0.13878565493523215</v>
+        <v>-0.17084986824409409</v>
       </c>
       <c r="C29">
-        <v>-2.4540986930661353e-005</v>
+        <v>-1.6650590019150208e-005</v>
       </c>
       <c r="D29">
-        <v>-5.2129313585139018e-006</v>
+        <v>-3.1208370834672232e-005</v>
       </c>
       <c r="E29">
-        <v>1.0003781509743627e-007</v>
+        <v>4.4046599590351972e-007</v>
       </c>
       <c r="F29">
-        <v>0.00011456336596575144</v>
+        <v>9.5747053077426328e-005</v>
       </c>
       <c r="G29">
-        <v>0.00032305895848009123</v>
+        <v>0.00022374336981168078</v>
       </c>
       <c r="H29">
-        <v>7.7295078950241321e-005</v>
+        <v>3.6078932133126913e-005</v>
       </c>
       <c r="I29">
-        <v>0.00026501419097670845</v>
+        <v>2.5198233826131131e-005</v>
       </c>
       <c r="J29">
-        <v>0.00032244911903909134</v>
+        <v>5.8547734280670711e-005</v>
       </c>
       <c r="K29">
-        <v>0.0002898025676345414</v>
+        <v>6.7423512803300523e-005</v>
       </c>
       <c r="L29">
-        <v>0.00031481929150526506</v>
+        <v>0.00013637031996509025</v>
       </c>
       <c r="M29">
-        <v>0.00055622552068529971</v>
+        <v>0.0002757550620857373</v>
       </c>
       <c r="N29">
-        <v>0.0010622122850906931</v>
+        <v>0.00086570109065174606</v>
       </c>
       <c r="O29">
-        <v>0.00078573604171323713</v>
+        <v>0.0006765657899571268</v>
       </c>
       <c r="P29">
-        <v>0.0010340295999819056</v>
+        <v>0.00087048826639843325</v>
       </c>
       <c r="Q29">
-        <v>0.00088833534944392429</v>
+        <v>0.00071826402334882551</v>
       </c>
       <c r="R29">
-        <v>0.00048769848131170767</v>
+        <v>0.00044628487521253631</v>
       </c>
       <c r="S29">
-        <v>0.00059793389975717765</v>
+        <v>0.00058790059018297403</v>
       </c>
       <c r="T29">
-        <v>0.0008509515812796703</v>
+        <v>0.00073624005854755004</v>
       </c>
       <c r="U29">
-        <v>0.0010919000695680347</v>
+        <v>0.00087546481282404793</v>
       </c>
       <c r="V29">
-        <v>0.001054379256513218</v>
+        <v>0.00087030887093566276</v>
       </c>
       <c r="W29">
-        <v>0.0010319981829071002</v>
+        <v>0.00088274146430406312</v>
       </c>
       <c r="X29">
-        <v>0.0010770280307167326</v>
+        <v>0.00087295009005951946</v>
       </c>
       <c r="Y29">
-        <v>-1.6836646099729354e-005</v>
+        <v>-1.3824487141929871e-005</v>
       </c>
       <c r="Z29">
-        <v>0.00029099560502216361</v>
+        <v>0.00010981391961407792</v>
       </c>
       <c r="AA29">
-        <v>-0.00013231673637799704</v>
+        <v>-0.00010669412571991392</v>
       </c>
       <c r="AB29">
-        <v>0.00072173979381726506</v>
+        <v>0.00053916853526174446</v>
       </c>
       <c r="AC29">
-        <v>0.00098456111335186967</v>
+        <v>0.0007810954214260285</v>
       </c>
       <c r="AD29">
-        <v>0.0063095662950000018</v>
+        <v>0.0046198763915225689</v>
       </c>
       <c r="AE29">
-        <v>-0.0011863085508093745</v>
+        <v>-0.00035358616190592782</v>
       </c>
     </row>
     <row r="30">
@@ -3101,94 +3227,94 @@
         <v>59</v>
       </c>
       <c r="B30">
-        <v>-0.9839830291038183</v>
+        <v>-1.7781786124960086</v>
       </c>
       <c r="C30">
-        <v>8.3440410491761433e-005</v>
+        <v>-0.00011185759157943779</v>
       </c>
       <c r="D30">
-        <v>-0.0015548025461564691</v>
+        <v>-0.0015051967117010983</v>
       </c>
       <c r="E30">
-        <v>1.9938384833170706e-005</v>
+        <v>2.0017858671374179e-005</v>
       </c>
       <c r="F30">
-        <v>-0.0019188094309747551</v>
+        <v>-0.0015675822255723365</v>
       </c>
       <c r="G30">
-        <v>-0.0022087242446957389</v>
+        <v>-0.001814068450888122</v>
       </c>
       <c r="H30">
-        <v>-0.0042096053654617407</v>
+        <v>-0.003180940469194306</v>
       </c>
       <c r="I30">
-        <v>-0.0036083293383268635</v>
+        <v>-0.0025518231297193958</v>
       </c>
       <c r="J30">
-        <v>-0.004087867188814741</v>
+        <v>-0.0030960396224354834</v>
       </c>
       <c r="K30">
-        <v>-0.0046480309574214243</v>
+        <v>-0.0031985002276480167</v>
       </c>
       <c r="L30">
-        <v>-0.0036081682074562819</v>
+        <v>-0.0025087688747968012</v>
       </c>
       <c r="M30">
-        <v>-0.0035837109712486522</v>
+        <v>-0.0026495570997936914</v>
       </c>
       <c r="N30">
-        <v>-0.0022679666119874643</v>
+        <v>-0.0015156817753532682</v>
       </c>
       <c r="O30">
-        <v>-0.0025184587412703367</v>
+        <v>-0.0020088504065586899</v>
       </c>
       <c r="P30">
-        <v>-0.0019820275231181082</v>
+        <v>-0.0013529242598980637</v>
       </c>
       <c r="Q30">
-        <v>-0.0018535689733727673</v>
+        <v>-0.0018778864500470847</v>
       </c>
       <c r="R30">
-        <v>-0.0018856426168847146</v>
+        <v>-0.0015644681178019959</v>
       </c>
       <c r="S30">
-        <v>-0.0018805984434090289</v>
+        <v>-0.0018646643802990926</v>
       </c>
       <c r="T30">
-        <v>-0.0021533469062982036</v>
+        <v>-0.0018408083790633642</v>
       </c>
       <c r="U30">
-        <v>-0.0019120563790466266</v>
+        <v>-0.0016740438784194501</v>
       </c>
       <c r="V30">
-        <v>-0.0022749513191838806</v>
+        <v>-0.0017070273869676088</v>
       </c>
       <c r="W30">
-        <v>-0.0026943890463013466</v>
+        <v>-0.0022835670060588112</v>
       </c>
       <c r="X30">
-        <v>-0.0021877738494345011</v>
+        <v>-0.0016385416624912653</v>
       </c>
       <c r="Y30">
-        <v>-0.00040411488211068556</v>
+        <v>-0.00029457879358745463</v>
       </c>
       <c r="Z30">
-        <v>0.0018795641470831887</v>
+        <v>0.00095215130571860954</v>
       </c>
       <c r="AA30">
-        <v>0.0019078209628953212</v>
+        <v>0.0015768513489849362</v>
       </c>
       <c r="AB30">
-        <v>-0.00116608861737214</v>
+        <v>-0.00050228298388007935</v>
       </c>
       <c r="AC30">
-        <v>-0.0015355488791964633</v>
+        <v>-0.0009054431432408284</v>
       </c>
       <c r="AD30">
-        <v>-0.0011863085508093745</v>
+        <v>-0.00035358616190592782</v>
       </c>
       <c r="AE30">
-        <v>0.040025960466584465</v>
+        <v>0.035026109143305735</v>
       </c>
     </row>
   </sheetData>
@@ -3201,7 +3327,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="10" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3210,13 +3336,13 @@
         <v>62</v>
       </c>
       <c r="B5">
-        <v>0.043286872598459425</v>
+        <v>0.042896705576424776</v>
       </c>
       <c r="E5" t="s">
         <v>64</v>
       </c>
       <c r="F5">
-        <v>403.3238013905825</v>
+        <v>662.07520677264995</v>
       </c>
     </row>
     <row r="6">
@@ -3224,13 +3350,13 @@
         <v>63</v>
       </c>
       <c r="B6">
-        <v>28955</v>
+        <v>29463</v>
       </c>
       <c r="E6" t="s">
         <v>65</v>
       </c>
       <c r="F6">
-        <v>-6386.7241757287529</v>
+        <v>-9483.0240280221242</v>
       </c>
     </row>
   </sheetData>
